--- a/training.xlsx
+++ b/training.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Salt-Creek-Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2133D204-D0B5-4D45-A3E4-F0E443497E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5595B3E9-23F6-440A-A243-169A2D3EF32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="27390" yWindow="255" windowWidth="21930" windowHeight="14985" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
+    <workbookView xWindow="2730" yWindow="2730" windowWidth="43200" windowHeight="11235" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3564" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3566" uniqueCount="78">
   <si>
     <t>Company Name</t>
   </si>
@@ -19757,7 +19757,7 @@
         <v>17</v>
       </c>
       <c r="G678" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H678" s="2">
         <v>0</v>
@@ -19773,32 +19773,12 @@
       </c>
     </row>
     <row r="679" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B679" t="s">
-        <v>38</v>
-      </c>
-      <c r="C679">
-        <v>995</v>
-      </c>
-      <c r="D679" t="s">
-        <v>48</v>
-      </c>
-      <c r="F679" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G679" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H679" s="2">
-        <v>0</v>
-      </c>
-      <c r="I679" s="1">
-        <v>46146.72314814815</v>
-      </c>
-      <c r="J679">
-        <v>4</v>
-      </c>
+      <c r="F679" s="2"/>
+      <c r="G679" s="1"/>
+      <c r="H679" s="2"/>
+      <c r="I679" s="1"/>
       <c r="K679" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="680" spans="2:11" x14ac:dyDescent="0.25">
@@ -19806,25 +19786,25 @@
         <v>38</v>
       </c>
       <c r="C680">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="D680" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F680" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G680" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H680" s="2">
-        <v>1.1840277777777778E-2</v>
+        <v>0</v>
       </c>
       <c r="I680" s="1">
-        <v>46146.72384259259</v>
+        <v>46146.72314814815</v>
       </c>
       <c r="J680">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K680" t="s">
         <v>11</v>
@@ -19835,10 +19815,10 @@
         <v>38</v>
       </c>
       <c r="C681">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D681" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F681" s="2" t="s">
         <v>17</v>
@@ -19847,7 +19827,7 @@
         <v>10</v>
       </c>
       <c r="H681" s="2">
-        <v>4.6643518518518518E-3</v>
+        <v>1.1840277777777778E-2</v>
       </c>
       <c r="I681" s="1">
         <v>46146.72384259259</v>
@@ -19864,25 +19844,25 @@
         <v>38</v>
       </c>
       <c r="C682">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D682" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F682" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G682" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H682" s="2">
+        <v>4.6643518518518518E-3</v>
+      </c>
+      <c r="I682" s="1">
+        <v>46146.72384259259</v>
+      </c>
+      <c r="J682">
         <v>0</v>
-      </c>
-      <c r="I682" s="1">
-        <v>46146.724537037036</v>
-      </c>
-      <c r="J682">
-        <v>4</v>
       </c>
       <c r="K682" t="s">
         <v>11</v>
@@ -19893,10 +19873,10 @@
         <v>38</v>
       </c>
       <c r="C683">
-        <v>3301</v>
+        <v>1005</v>
       </c>
       <c r="D683" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="F683" s="2" t="s">
         <v>17</v>
@@ -19908,7 +19888,7 @@
         <v>0</v>
       </c>
       <c r="I683" s="1">
-        <v>46146.725231481483</v>
+        <v>46146.724537037036</v>
       </c>
       <c r="J683">
         <v>4</v>
@@ -19922,10 +19902,10 @@
         <v>38</v>
       </c>
       <c r="C684">
-        <v>3304</v>
+        <v>3301</v>
       </c>
       <c r="D684" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F684" s="2" t="s">
         <v>17</v>
@@ -19951,13 +19931,10 @@
         <v>38</v>
       </c>
       <c r="C685">
-        <v>991</v>
+        <v>3304</v>
       </c>
       <c r="D685" t="s">
-        <v>56</v>
-      </c>
-      <c r="E685" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="F685" s="2" t="s">
         <v>17</v>
@@ -19969,7 +19946,7 @@
         <v>0</v>
       </c>
       <c r="I685" s="1">
-        <v>46146.725925925923</v>
+        <v>46146.725231481483</v>
       </c>
       <c r="J685">
         <v>4</v>
@@ -19983,10 +19960,13 @@
         <v>38</v>
       </c>
       <c r="C686">
-        <v>3307</v>
+        <v>991</v>
       </c>
       <c r="D686" t="s">
-        <v>73</v>
+        <v>56</v>
+      </c>
+      <c r="E686" t="s">
+        <v>45</v>
       </c>
       <c r="F686" s="2" t="s">
         <v>17</v>
@@ -19998,7 +19978,7 @@
         <v>0</v>
       </c>
       <c r="I686" s="1">
-        <v>46146.726620370369</v>
+        <v>46146.725925925923</v>
       </c>
       <c r="J686">
         <v>4</v>
@@ -20012,10 +19992,10 @@
         <v>38</v>
       </c>
       <c r="C687">
-        <v>3306</v>
+        <v>3307</v>
       </c>
       <c r="D687" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F687" s="2" t="s">
         <v>17</v>
@@ -20041,10 +20021,10 @@
         <v>38</v>
       </c>
       <c r="C688">
-        <v>3308</v>
+        <v>3306</v>
       </c>
       <c r="D688" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F688" s="2" t="s">
         <v>17</v>
@@ -20056,7 +20036,7 @@
         <v>0</v>
       </c>
       <c r="I688" s="1">
-        <v>46146.727314814816</v>
+        <v>46146.726620370369</v>
       </c>
       <c r="J688">
         <v>4</v>
@@ -20070,25 +20050,25 @@
         <v>38</v>
       </c>
       <c r="C689">
-        <v>2238</v>
+        <v>3308</v>
       </c>
       <c r="D689" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F689" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G689" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H689" s="2">
-        <v>9.9884259259259266E-3</v>
+        <v>0</v>
       </c>
       <c r="I689" s="1">
-        <v>46146.728009259263</v>
+        <v>46146.727314814816</v>
       </c>
       <c r="J689">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K689" t="s">
         <v>11</v>
@@ -20099,7 +20079,7 @@
         <v>38</v>
       </c>
       <c r="C690">
-        <v>3299</v>
+        <v>2238</v>
       </c>
       <c r="D690" t="s">
         <v>67</v>
@@ -20111,13 +20091,13 @@
         <v>10</v>
       </c>
       <c r="H690" s="2">
-        <v>4.5717592592592589E-3</v>
+        <v>9.9884259259259266E-3</v>
       </c>
       <c r="I690" s="1">
         <v>46146.728009259263</v>
       </c>
       <c r="J690">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K690" t="s">
         <v>11</v>
@@ -20128,25 +20108,25 @@
         <v>38</v>
       </c>
       <c r="C691">
-        <v>3302</v>
+        <v>3299</v>
       </c>
       <c r="D691" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F691" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G691" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H691" s="2">
+        <v>4.5717592592592589E-3</v>
+      </c>
+      <c r="I691" s="1">
+        <v>46146.728009259263</v>
+      </c>
+      <c r="J691">
         <v>0</v>
-      </c>
-      <c r="I691" s="1">
-        <v>46146.728703703702</v>
-      </c>
-      <c r="J691">
-        <v>4</v>
       </c>
       <c r="K691" t="s">
         <v>11</v>
@@ -20157,10 +20137,10 @@
         <v>38</v>
       </c>
       <c r="C692">
-        <v>1001</v>
+        <v>3302</v>
       </c>
       <c r="D692" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="F692" s="2" t="s">
         <v>17</v>
@@ -20172,7 +20152,7 @@
         <v>0</v>
       </c>
       <c r="I692" s="1">
-        <v>46146.729398148149</v>
+        <v>46146.728703703702</v>
       </c>
       <c r="J692">
         <v>4</v>
@@ -20186,10 +20166,10 @@
         <v>38</v>
       </c>
       <c r="C693">
-        <v>3298</v>
+        <v>1001</v>
       </c>
       <c r="D693" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="F693" s="2" t="s">
         <v>17</v>
@@ -20215,10 +20195,10 @@
         <v>38</v>
       </c>
       <c r="C694">
-        <v>996</v>
+        <v>3298</v>
       </c>
       <c r="D694" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="F694" s="2" t="s">
         <v>17</v>
@@ -20230,7 +20210,7 @@
         <v>0</v>
       </c>
       <c r="I694" s="1">
-        <v>46146.730092592596</v>
+        <v>46146.729398148149</v>
       </c>
       <c r="J694">
         <v>4</v>
@@ -20244,13 +20224,10 @@
         <v>38</v>
       </c>
       <c r="C695">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="D695" t="s">
-        <v>61</v>
-      </c>
-      <c r="E695" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F695" s="2" t="s">
         <v>17</v>
@@ -20262,7 +20239,7 @@
         <v>0</v>
       </c>
       <c r="I695" s="1">
-        <v>46146.730787037035</v>
+        <v>46146.730092592596</v>
       </c>
       <c r="J695">
         <v>4</v>
@@ -20276,10 +20253,13 @@
         <v>38</v>
       </c>
       <c r="C696">
-        <v>1003</v>
+        <v>990</v>
       </c>
       <c r="D696" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="E696" t="s">
+        <v>45</v>
       </c>
       <c r="F696" s="2" t="s">
         <v>17</v>
@@ -20305,13 +20285,13 @@
         <v>38</v>
       </c>
       <c r="C697">
-        <v>3305</v>
+        <v>1003</v>
       </c>
       <c r="D697" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F697" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G697" s="1" t="s">
         <v>13</v>
@@ -20320,10 +20300,10 @@
         <v>0</v>
       </c>
       <c r="I697" s="1">
-        <v>46176.419212962966</v>
+        <v>46146.730787037035</v>
       </c>
       <c r="J697">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K697" t="s">
         <v>11</v>
@@ -20334,10 +20314,10 @@
         <v>38</v>
       </c>
       <c r="C698">
-        <v>2250</v>
+        <v>3305</v>
       </c>
       <c r="D698" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F698" s="2" t="s">
         <v>22</v>
@@ -20349,10 +20329,10 @@
         <v>0</v>
       </c>
       <c r="I698" s="1">
-        <v>46176.419907407406</v>
+        <v>46176.419212962966</v>
       </c>
       <c r="J698">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K698" t="s">
         <v>11</v>
@@ -20363,25 +20343,25 @@
         <v>38</v>
       </c>
       <c r="C699">
-        <v>3300</v>
+        <v>2250</v>
       </c>
       <c r="D699" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F699" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G699" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H699" s="2">
-        <v>7.7199074074074071E-3</v>
+        <v>0</v>
       </c>
       <c r="I699" s="1">
         <v>46176.419907407406</v>
       </c>
       <c r="J699">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K699" t="s">
         <v>11</v>
@@ -20392,19 +20372,19 @@
         <v>38</v>
       </c>
       <c r="C700">
-        <v>1979</v>
+        <v>3300</v>
       </c>
       <c r="D700" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F700" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G700" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H700" s="2">
-        <v>0</v>
+        <v>7.7199074074074071E-3</v>
       </c>
       <c r="I700" s="1">
         <v>46176.419907407406</v>
@@ -20421,25 +20401,25 @@
         <v>38</v>
       </c>
       <c r="C701">
-        <v>1006</v>
+        <v>1979</v>
       </c>
       <c r="D701" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="F701" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G701" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H701" s="2">
-        <v>1.2129629629629629E-2</v>
+        <v>0</v>
       </c>
       <c r="I701" s="1">
-        <v>46176.420601851853</v>
+        <v>46176.419907407406</v>
       </c>
       <c r="J701">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K701" t="s">
         <v>11</v>
@@ -20450,10 +20430,10 @@
         <v>38</v>
       </c>
       <c r="C702">
-        <v>3303</v>
+        <v>1006</v>
       </c>
       <c r="D702" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="F702" s="2" t="s">
         <v>22</v>
@@ -20462,7 +20442,7 @@
         <v>10</v>
       </c>
       <c r="H702" s="2">
-        <v>7.1759259259259259E-3</v>
+        <v>1.2129629629629629E-2</v>
       </c>
       <c r="I702" s="1">
         <v>46176.420601851853</v>
@@ -20479,25 +20459,25 @@
         <v>38</v>
       </c>
       <c r="C703">
-        <v>1004</v>
+        <v>3303</v>
       </c>
       <c r="D703" t="s">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="F703" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G703" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H703" s="2">
+        <v>7.1759259259259259E-3</v>
+      </c>
+      <c r="I703" s="1">
+        <v>46176.420601851853</v>
+      </c>
+      <c r="J703">
         <v>0</v>
-      </c>
-      <c r="I703" s="1">
-        <v>46176.421296296299</v>
-      </c>
-      <c r="J703">
-        <v>1</v>
       </c>
       <c r="K703" t="s">
         <v>11</v>
@@ -20508,10 +20488,10 @@
         <v>38</v>
       </c>
       <c r="C704">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="D704" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F704" s="2" t="s">
         <v>22</v>
@@ -20526,7 +20506,7 @@
         <v>46176.421296296299</v>
       </c>
       <c r="J704">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K704" t="s">
         <v>11</v>
@@ -20537,13 +20517,10 @@
         <v>38</v>
       </c>
       <c r="C705">
-        <v>993</v>
+        <v>1002</v>
       </c>
       <c r="D705" t="s">
-        <v>44</v>
-      </c>
-      <c r="E705" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F705" s="2" t="s">
         <v>22</v>
@@ -20555,10 +20532,10 @@
         <v>0</v>
       </c>
       <c r="I705" s="1">
-        <v>46176.421990740739</v>
+        <v>46176.421296296299</v>
       </c>
       <c r="J705">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K705" t="s">
         <v>11</v>
@@ -20569,10 +20546,10 @@
         <v>38</v>
       </c>
       <c r="C706">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="D706" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E706" t="s">
         <v>45</v>
@@ -20590,7 +20567,7 @@
         <v>46176.421990740739</v>
       </c>
       <c r="J706">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K706" t="s">
         <v>11</v>
@@ -20601,10 +20578,13 @@
         <v>38</v>
       </c>
       <c r="C707">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="D707" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="E707" t="s">
+        <v>45</v>
       </c>
       <c r="F707" s="2" t="s">
         <v>22</v>
@@ -20616,10 +20596,10 @@
         <v>0</v>
       </c>
       <c r="I707" s="1">
-        <v>46176.422685185185</v>
+        <v>46176.421990740739</v>
       </c>
       <c r="J707">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K707" t="s">
         <v>11</v>
@@ -20630,10 +20610,10 @@
         <v>38</v>
       </c>
       <c r="C708">
-        <v>1008</v>
+        <v>995</v>
       </c>
       <c r="D708" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F708" s="2" t="s">
         <v>22</v>
@@ -20648,7 +20628,7 @@
         <v>46176.422685185185</v>
       </c>
       <c r="J708">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K708" t="s">
         <v>11</v>
@@ -20659,10 +20639,10 @@
         <v>38</v>
       </c>
       <c r="C709">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D709" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F709" s="2" t="s">
         <v>22</v>
@@ -20677,7 +20657,7 @@
         <v>46176.422685185185</v>
       </c>
       <c r="J709">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K709" t="s">
         <v>11</v>
@@ -20688,57 +20668,37 @@
         <v>38</v>
       </c>
       <c r="C710">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="D710" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F710" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G710" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H710" s="2">
-        <v>0</v>
+        <v>9.4907407407407408E-4</v>
       </c>
       <c r="I710" s="1">
-        <v>46176.423379629632</v>
+        <v>46176.422685185185</v>
       </c>
       <c r="J710">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K710" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="711" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B711" t="s">
-        <v>38</v>
-      </c>
-      <c r="C711">
-        <v>3301</v>
-      </c>
-      <c r="D711" t="s">
-        <v>71</v>
-      </c>
-      <c r="F711" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G711" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H711" s="2">
-        <v>0</v>
-      </c>
-      <c r="I711" s="1">
-        <v>46176.423379629632</v>
-      </c>
-      <c r="J711">
-        <v>1</v>
-      </c>
+      <c r="F711" s="2"/>
+      <c r="G711" s="1"/>
+      <c r="H711" s="2"/>
+      <c r="I711" s="1"/>
       <c r="K711" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="712" spans="2:11" x14ac:dyDescent="0.25">
@@ -20746,10 +20706,10 @@
         <v>38</v>
       </c>
       <c r="C712">
-        <v>3304</v>
+        <v>1005</v>
       </c>
       <c r="D712" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="F712" s="2" t="s">
         <v>22</v>
@@ -20761,10 +20721,10 @@
         <v>0</v>
       </c>
       <c r="I712" s="1">
-        <v>46176.424074074072</v>
+        <v>46176.423379629632</v>
       </c>
       <c r="J712">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K712" t="s">
         <v>11</v>
@@ -20775,13 +20735,10 @@
         <v>38</v>
       </c>
       <c r="C713">
-        <v>991</v>
+        <v>3301</v>
       </c>
       <c r="D713" t="s">
-        <v>56</v>
-      </c>
-      <c r="E713" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="F713" s="2" t="s">
         <v>22</v>
@@ -20793,10 +20750,10 @@
         <v>0</v>
       </c>
       <c r="I713" s="1">
-        <v>46176.424074074072</v>
+        <v>46176.423379629632</v>
       </c>
       <c r="J713">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K713" t="s">
         <v>11</v>
@@ -20807,10 +20764,10 @@
         <v>38</v>
       </c>
       <c r="C714">
-        <v>3307</v>
+        <v>3304</v>
       </c>
       <c r="D714" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F714" s="2" t="s">
         <v>22</v>
@@ -20825,7 +20782,7 @@
         <v>46176.424074074072</v>
       </c>
       <c r="J714">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K714" t="s">
         <v>11</v>
@@ -20836,10 +20793,13 @@
         <v>38</v>
       </c>
       <c r="C715">
-        <v>3306</v>
+        <v>991</v>
       </c>
       <c r="D715" t="s">
-        <v>74</v>
+        <v>56</v>
+      </c>
+      <c r="E715" t="s">
+        <v>45</v>
       </c>
       <c r="F715" s="2" t="s">
         <v>22</v>
@@ -20851,10 +20811,10 @@
         <v>0</v>
       </c>
       <c r="I715" s="1">
-        <v>46176.424768518518</v>
+        <v>46176.424074074072</v>
       </c>
       <c r="J715">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K715" t="s">
         <v>11</v>
@@ -20865,10 +20825,10 @@
         <v>38</v>
       </c>
       <c r="C716">
-        <v>3308</v>
+        <v>3307</v>
       </c>
       <c r="D716" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F716" s="2" t="s">
         <v>22</v>
@@ -20880,10 +20840,10 @@
         <v>0</v>
       </c>
       <c r="I716" s="1">
-        <v>46176.424768518518</v>
+        <v>46176.424074074072</v>
       </c>
       <c r="J716">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K716" t="s">
         <v>11</v>
@@ -20894,10 +20854,10 @@
         <v>38</v>
       </c>
       <c r="C717">
-        <v>2238</v>
+        <v>3306</v>
       </c>
       <c r="D717" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F717" s="2" t="s">
         <v>22</v>
@@ -20909,10 +20869,10 @@
         <v>0</v>
       </c>
       <c r="I717" s="1">
-        <v>46176.425462962965</v>
+        <v>46176.424768518518</v>
       </c>
       <c r="J717">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K717" t="s">
         <v>11</v>
@@ -20923,10 +20883,10 @@
         <v>38</v>
       </c>
       <c r="C718">
-        <v>3299</v>
+        <v>3308</v>
       </c>
       <c r="D718" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="F718" s="2" t="s">
         <v>22</v>
@@ -20938,10 +20898,10 @@
         <v>0</v>
       </c>
       <c r="I718" s="1">
-        <v>46176.425462962965</v>
+        <v>46176.424768518518</v>
       </c>
       <c r="J718">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K718" t="s">
         <v>11</v>
@@ -20952,10 +20912,10 @@
         <v>38</v>
       </c>
       <c r="C719">
-        <v>3302</v>
+        <v>2238</v>
       </c>
       <c r="D719" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F719" s="2" t="s">
         <v>22</v>
@@ -20970,7 +20930,7 @@
         <v>46176.425462962965</v>
       </c>
       <c r="J719">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K719" t="s">
         <v>11</v>
@@ -20981,22 +20941,22 @@
         <v>38</v>
       </c>
       <c r="C720">
-        <v>1001</v>
+        <v>3299</v>
       </c>
       <c r="D720" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F720" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G720" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H720" s="2">
-        <v>0</v>
+        <v>2.4861111111111112E-2</v>
       </c>
       <c r="I720" s="1">
-        <v>46176.426157407404</v>
+        <v>46176.425462962965</v>
       </c>
       <c r="J720">
         <v>1</v>
@@ -21010,10 +20970,10 @@
         <v>38</v>
       </c>
       <c r="C721">
-        <v>3298</v>
+        <v>3302</v>
       </c>
       <c r="D721" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F721" s="2" t="s">
         <v>22</v>
@@ -21025,10 +20985,10 @@
         <v>0</v>
       </c>
       <c r="I721" s="1">
-        <v>46176.426157407404</v>
+        <v>46176.425462962965</v>
       </c>
       <c r="J721">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K721" t="s">
         <v>11</v>
@@ -21039,10 +20999,10 @@
         <v>38</v>
       </c>
       <c r="C722">
-        <v>996</v>
+        <v>1001</v>
       </c>
       <c r="D722" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F722" s="2" t="s">
         <v>22</v>
@@ -21054,10 +21014,10 @@
         <v>0</v>
       </c>
       <c r="I722" s="1">
-        <v>46176.426851851851</v>
+        <v>46176.426157407404</v>
       </c>
       <c r="J722">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K722" t="s">
         <v>11</v>
@@ -21068,13 +21028,10 @@
         <v>38</v>
       </c>
       <c r="C723">
-        <v>990</v>
+        <v>3298</v>
       </c>
       <c r="D723" t="s">
-        <v>61</v>
-      </c>
-      <c r="E723" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="F723" s="2" t="s">
         <v>22</v>
@@ -21086,10 +21043,10 @@
         <v>0</v>
       </c>
       <c r="I723" s="1">
-        <v>46176.426851851851</v>
+        <v>46176.426157407404</v>
       </c>
       <c r="J723">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K723" t="s">
         <v>11</v>
@@ -21100,10 +21057,10 @@
         <v>38</v>
       </c>
       <c r="C724">
-        <v>1003</v>
+        <v>996</v>
       </c>
       <c r="D724" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F724" t="s">
         <v>22</v>
@@ -21118,23 +21075,72 @@
         <v>46176.426851851851</v>
       </c>
       <c r="J724">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K724" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="725" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F725" s="2"/>
-      <c r="G725" s="1"/>
-      <c r="H725" s="2"/>
-      <c r="I725" s="1"/>
+      <c r="B725" t="s">
+        <v>38</v>
+      </c>
+      <c r="C725">
+        <v>990</v>
+      </c>
+      <c r="D725" t="s">
+        <v>61</v>
+      </c>
+      <c r="E725" t="s">
+        <v>45</v>
+      </c>
+      <c r="F725" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G725" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H725" s="2">
+        <v>0</v>
+      </c>
+      <c r="I725" s="1">
+        <v>46176.426851851851</v>
+      </c>
+      <c r="J725">
+        <v>2</v>
+      </c>
+      <c r="K725" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="726" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F726" s="2"/>
-      <c r="G726" s="1"/>
-      <c r="H726" s="2"/>
-      <c r="I726" s="1"/>
+      <c r="B726" t="s">
+        <v>38</v>
+      </c>
+      <c r="C726">
+        <v>1003</v>
+      </c>
+      <c r="D726" t="s">
+        <v>62</v>
+      </c>
+      <c r="F726" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G726" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H726" s="2">
+        <v>0</v>
+      </c>
+      <c r="I726" s="1">
+        <v>46176.426851851851</v>
+      </c>
+      <c r="J726">
+        <v>2</v>
+      </c>
+      <c r="K726" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="727" spans="2:11" x14ac:dyDescent="0.25">
       <c r="F727" s="2"/>

--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Salt-Creek-Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A395081-BEB4-4095-ADCF-196E11292D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E68F706-A8CD-4C47-B291-ECAB29266EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3566" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3711" uniqueCount="78">
   <si>
     <t>Company Name</t>
   </si>
@@ -86,6 +86,9 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Winter Weather</t>
   </si>
   <si>
@@ -95,10 +98,19 @@
     <t>Rules for Safe Driving</t>
   </si>
   <si>
+    <t>Distracted Driving</t>
+  </si>
+  <si>
+    <t>Driver Health</t>
+  </si>
+  <si>
     <t>Drowsy Driving</t>
   </si>
   <si>
     <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>Fire Extinguisher Training for CDL</t>
   </si>
   <si>
     <t>Alert Driving: Big Three</t>
@@ -110,13 +122,7 @@
     <t>Speed Mangement-C</t>
   </si>
   <si>
-    <t>Safe Lifting for Commercial Drivers</t>
-  </si>
-  <si>
     <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>DNU-Scene of an Accident</t>
@@ -125,34 +131,28 @@
     <t>DNU-NEW-Vehicle Inspections</t>
   </si>
   <si>
-    <t>Vehicle Inspections</t>
+    <t>Work Zone Safety</t>
   </si>
   <si>
-    <t>Distracted Driving</t>
+    <t>Micro-Learn Speed</t>
+  </si>
+  <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Dangers of Aggressive Driving for CMV Drivers</t>
+  </si>
+  <si>
+    <t>3 points of contact</t>
+  </si>
+  <si>
+    <t>Hazcom for CDL Drivers</t>
   </si>
   <si>
     <t>Safe RR Crossing</t>
   </si>
   <si>
-    <t>3 points of contact</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Driver Health</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Dangers of Aggressive Driving for CMV Drivers</t>
-  </si>
-  <si>
-    <t>Fire Extinguisher Training for CDL</t>
-  </si>
-  <si>
-    <t>Hazcom for CDL Drivers</t>
+    <t>DNU-Fatigue</t>
   </si>
   <si>
     <t>Salt Creek Logistics</t>
@@ -646,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M6919"/>
+  <dimension ref="D1:M7172"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -704,7 +704,7 @@
         <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -733,7 +733,7 @@
         <v>40</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -762,7 +762,7 @@
         <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -791,7 +791,7 @@
         <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -820,7 +820,7 @@
         <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -852,7 +852,7 @@
         <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -884,7 +884,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -945,7 +945,7 @@
         <v>48</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>49</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -1003,7 +1003,7 @@
         <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -1035,7 +1035,7 @@
         <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -1064,7 +1064,7 @@
         <v>52</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>53</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>12</v>
@@ -1117,7 +1117,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="1"/>
       <c r="M16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
@@ -1131,7 +1131,7 @@
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1160,7 +1160,7 @@
         <v>55</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1192,7 +1192,7 @@
         <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1221,7 +1221,7 @@
         <v>57</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1250,7 +1250,7 @@
         <v>58</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         <v>59</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1308,7 +1308,7 @@
         <v>60</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1340,7 +1340,7 @@
         <v>45</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1369,7 +1369,7 @@
         <v>62</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1398,7 +1398,7 @@
         <v>39</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>10</v>
@@ -1427,7 +1427,7 @@
         <v>40</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>10</v>
@@ -1456,7 +1456,7 @@
         <v>41</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>10</v>
@@ -1485,7 +1485,7 @@
         <v>42</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>10</v>
@@ -1514,7 +1514,7 @@
         <v>43</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>10</v>
@@ -1546,7 +1546,7 @@
         <v>45</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>10</v>
@@ -1578,7 +1578,7 @@
         <v>45</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>13</v>
@@ -1610,7 +1610,7 @@
         <v>45</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>13</v>
@@ -1639,7 +1639,7 @@
         <v>48</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>10</v>
@@ -1668,7 +1668,7 @@
         <v>49</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I35" s="1" t="s">
         <v>13</v>
@@ -1697,7 +1697,7 @@
         <v>50</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I36" s="1" t="s">
         <v>10</v>
@@ -1729,7 +1729,7 @@
         <v>45</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I37" s="1" t="s">
         <v>12</v>
@@ -1753,7 +1753,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="1"/>
       <c r="M38" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
@@ -1767,7 +1767,7 @@
         <v>52</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>10</v>
@@ -1796,7 +1796,7 @@
         <v>53</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>12</v>
@@ -1820,7 +1820,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="1"/>
       <c r="M41" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
@@ -1834,7 +1834,7 @@
         <v>54</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>13</v>
@@ -1863,7 +1863,7 @@
         <v>55</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>10</v>
@@ -1895,7 +1895,7 @@
         <v>45</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>10</v>
@@ -1924,7 +1924,7 @@
         <v>57</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>10</v>
@@ -1953,7 +1953,7 @@
         <v>58</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>12</v>
@@ -1977,7 +1977,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="1"/>
       <c r="M47" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
@@ -1991,7 +1991,7 @@
         <v>59</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I48" s="1" t="s">
         <v>10</v>
@@ -2020,7 +2020,7 @@
         <v>60</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I49" s="1" t="s">
         <v>12</v>
@@ -2044,7 +2044,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="1"/>
       <c r="M50" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
@@ -2061,7 +2061,7 @@
         <v>45</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>13</v>
@@ -2090,7 +2090,7 @@
         <v>62</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>10</v>
@@ -2119,7 +2119,7 @@
         <v>39</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>12</v>
@@ -2143,7 +2143,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="1"/>
       <c r="M54" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
@@ -2157,7 +2157,7 @@
         <v>40</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2186,7 +2186,7 @@
         <v>41</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2215,7 +2215,7 @@
         <v>42</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2244,7 +2244,7 @@
         <v>43</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>12</v>
@@ -2268,7 +2268,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="1"/>
       <c r="M59" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
@@ -2285,7 +2285,7 @@
         <v>45</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2317,7 +2317,7 @@
         <v>45</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2346,7 +2346,7 @@
         <v>48</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>12</v>
@@ -2370,7 +2370,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="1"/>
       <c r="M63" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>13</v>
@@ -2413,7 +2413,7 @@
         <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2445,7 +2445,7 @@
         <v>45</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>12</v>
@@ -2469,7 +2469,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="1"/>
       <c r="M67" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
@@ -2483,7 +2483,7 @@
         <v>52</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>12</v>
@@ -2507,7 +2507,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="1"/>
       <c r="M69" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
@@ -2521,7 +2521,7 @@
         <v>53</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2550,7 +2550,7 @@
         <v>55</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>12</v>
@@ -2574,7 +2574,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
@@ -2591,7 +2591,7 @@
         <v>45</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>57</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2649,7 +2649,7 @@
         <v>58</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2678,7 +2678,7 @@
         <v>59</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2707,7 +2707,7 @@
         <v>60</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>12</v>
@@ -2731,7 +2731,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="1"/>
       <c r="M78" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
@@ -2748,7 +2748,7 @@
         <v>45</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2777,7 +2777,7 @@
         <v>63</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -2806,7 +2806,7 @@
         <v>62</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>12</v>
@@ -2830,7 +2830,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="1"/>
       <c r="M82" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
@@ -2844,7 +2844,7 @@
         <v>39</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2873,7 +2873,7 @@
         <v>64</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2902,7 +2902,7 @@
         <v>40</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2931,7 +2931,7 @@
         <v>41</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>10</v>
@@ -2960,7 +2960,7 @@
         <v>42</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -2989,7 +2989,7 @@
         <v>43</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3021,7 +3021,7 @@
         <v>45</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3053,7 +3053,7 @@
         <v>45</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -3082,7 +3082,7 @@
         <v>48</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3111,7 +3111,7 @@
         <v>49</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3140,7 +3140,7 @@
         <v>50</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3172,7 +3172,7 @@
         <v>45</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3201,7 +3201,7 @@
         <v>52</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>53</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>12</v>
@@ -3254,7 +3254,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
       <c r="M97" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
@@ -3268,7 +3268,7 @@
         <v>65</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3297,7 +3297,7 @@
         <v>55</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3329,7 +3329,7 @@
         <v>45</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3358,7 +3358,7 @@
         <v>57</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3387,7 +3387,7 @@
         <v>58</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3416,7 +3416,7 @@
         <v>59</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3445,7 +3445,7 @@
         <v>60</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>13</v>
@@ -3477,7 +3477,7 @@
         <v>45</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>13</v>
@@ -3506,7 +3506,7 @@
         <v>63</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>13</v>
@@ -3535,7 +3535,7 @@
         <v>62</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3564,7 +3564,7 @@
         <v>39</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>13</v>
@@ -3593,7 +3593,7 @@
         <v>43</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3625,7 +3625,7 @@
         <v>45</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3657,7 +3657,7 @@
         <v>45</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>12</v>
@@ -3681,7 +3681,7 @@
       <c r="J112" s="2"/>
       <c r="K112" s="1"/>
       <c r="M112" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
@@ -3695,7 +3695,7 @@
         <v>48</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3724,7 +3724,7 @@
         <v>49</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3753,7 +3753,7 @@
         <v>53</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3782,7 +3782,7 @@
         <v>58</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3811,7 +3811,7 @@
         <v>59</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -3840,7 +3840,7 @@
         <v>60</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3872,7 +3872,7 @@
         <v>45</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>13</v>
@@ -3901,7 +3901,7 @@
         <v>63</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3930,7 +3930,7 @@
         <v>66</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -3959,7 +3959,7 @@
         <v>64</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3988,7 +3988,7 @@
         <v>40</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -4017,7 +4017,7 @@
         <v>41</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4046,7 +4046,7 @@
         <v>42</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4075,7 +4075,7 @@
         <v>43</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4107,7 +4107,7 @@
         <v>45</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4139,7 +4139,7 @@
         <v>45</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4168,7 +4168,7 @@
         <v>48</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4197,7 +4197,7 @@
         <v>49</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4226,7 +4226,7 @@
         <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4258,7 +4258,7 @@
         <v>45</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4287,7 +4287,7 @@
         <v>52</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>10</v>
@@ -4316,7 +4316,7 @@
         <v>53</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>13</v>
@@ -4345,7 +4345,7 @@
         <v>65</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4374,7 +4374,7 @@
         <v>55</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4406,7 +4406,7 @@
         <v>45</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4435,7 +4435,7 @@
         <v>67</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4464,7 +4464,7 @@
         <v>57</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>10</v>
@@ -4493,7 +4493,7 @@
         <v>58</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>13</v>
@@ -4522,7 +4522,7 @@
         <v>59</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>10</v>
@@ -4551,7 +4551,7 @@
         <v>60</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>10</v>
@@ -4583,7 +4583,7 @@
         <v>45</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4612,7 +4612,7 @@
         <v>63</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>12</v>
@@ -4636,7 +4636,7 @@
       <c r="J145" s="2"/>
       <c r="K145" s="1"/>
       <c r="M145" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
@@ -4650,7 +4650,7 @@
         <v>62</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4679,7 +4679,7 @@
         <v>66</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -4708,7 +4708,7 @@
         <v>64</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>10</v>
@@ -4737,7 +4737,7 @@
         <v>40</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -4766,7 +4766,7 @@
         <v>41</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>12</v>
@@ -4790,7 +4790,7 @@
       <c r="J151" s="2"/>
       <c r="K151" s="1"/>
       <c r="M151" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
@@ -4804,7 +4804,7 @@
         <v>42</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>10</v>
@@ -4833,7 +4833,7 @@
         <v>43</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>12</v>
@@ -4857,7 +4857,7 @@
       <c r="J154" s="2"/>
       <c r="K154" s="1"/>
       <c r="M154" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
@@ -4874,7 +4874,7 @@
         <v>45</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>12</v>
@@ -4898,7 +4898,7 @@
       <c r="J156" s="2"/>
       <c r="K156" s="1"/>
       <c r="M156" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
@@ -4915,7 +4915,7 @@
         <v>45</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>13</v>
@@ -4944,7 +4944,7 @@
         <v>48</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4973,7 +4973,7 @@
         <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -5002,7 +5002,7 @@
         <v>50</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -5034,7 +5034,7 @@
         <v>45</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -5063,7 +5063,7 @@
         <v>52</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>12</v>
@@ -5087,7 +5087,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
       <c r="M163" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -5101,7 +5101,7 @@
         <v>53</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>12</v>
@@ -5125,7 +5125,7 @@
       <c r="J165" s="2"/>
       <c r="K165" s="1"/>
       <c r="M165" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
@@ -5139,7 +5139,7 @@
         <v>65</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5168,7 +5168,7 @@
         <v>55</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>10</v>
@@ -5200,7 +5200,7 @@
         <v>45</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5229,7 +5229,7 @@
         <v>67</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5258,7 +5258,7 @@
         <v>57</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>13</v>
@@ -5287,7 +5287,7 @@
         <v>58</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>10</v>
@@ -5316,7 +5316,7 @@
         <v>59</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5345,7 +5345,7 @@
         <v>60</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>12</v>
@@ -5369,7 +5369,7 @@
       <c r="J174" s="2"/>
       <c r="K174" s="1"/>
       <c r="M174" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
@@ -5386,7 +5386,7 @@
         <v>45</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>13</v>
@@ -5415,7 +5415,7 @@
         <v>63</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>13</v>
@@ -5444,7 +5444,7 @@
         <v>62</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -5473,7 +5473,7 @@
         <v>66</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>13</v>
@@ -5502,7 +5502,7 @@
         <v>64</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5531,7 +5531,7 @@
         <v>40</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>10</v>
@@ -5560,7 +5560,7 @@
         <v>41</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>10</v>
@@ -5589,7 +5589,7 @@
         <v>42</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -5618,7 +5618,7 @@
         <v>43</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -5650,7 +5650,7 @@
         <v>45</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5682,7 +5682,7 @@
         <v>45</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5711,7 +5711,7 @@
         <v>48</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5740,7 +5740,7 @@
         <v>49</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>13</v>
@@ -5769,7 +5769,7 @@
         <v>50</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>12</v>
@@ -5793,7 +5793,7 @@
       <c r="J189" s="2"/>
       <c r="K189" s="1"/>
       <c r="M189" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
@@ -5807,7 +5807,7 @@
         <v>52</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -5836,7 +5836,7 @@
         <v>53</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>12</v>
@@ -5860,7 +5860,7 @@
       <c r="J192" s="2"/>
       <c r="K192" s="1"/>
       <c r="M192" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
@@ -5874,7 +5874,7 @@
         <v>55</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -5906,7 +5906,7 @@
         <v>45</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -5935,7 +5935,7 @@
         <v>67</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -5964,7 +5964,7 @@
         <v>58</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -5993,7 +5993,7 @@
         <v>60</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>10</v>
@@ -6025,7 +6025,7 @@
         <v>45</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>10</v>
@@ -6054,7 +6054,7 @@
         <v>63</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6083,7 +6083,7 @@
         <v>62</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6112,7 +6112,7 @@
         <v>66</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>13</v>
@@ -6141,7 +6141,7 @@
         <v>64</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6170,7 +6170,7 @@
         <v>40</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6199,7 +6199,7 @@
         <v>41</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6228,7 +6228,7 @@
         <v>42</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>10</v>
@@ -6257,7 +6257,7 @@
         <v>43</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>10</v>
@@ -6289,7 +6289,7 @@
         <v>45</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6321,7 +6321,7 @@
         <v>45</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>13</v>
@@ -6350,7 +6350,7 @@
         <v>48</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>10</v>
@@ -6379,7 +6379,7 @@
         <v>49</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>13</v>
@@ -6408,7 +6408,7 @@
         <v>50</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6437,7 +6437,7 @@
         <v>52</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6466,7 +6466,7 @@
         <v>53</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>13</v>
@@ -6495,7 +6495,7 @@
         <v>55</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6527,7 +6527,7 @@
         <v>45</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6556,7 +6556,7 @@
         <v>67</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6585,7 +6585,7 @@
         <v>58</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>13</v>
@@ -6614,7 +6614,7 @@
         <v>60</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>13</v>
@@ -6646,7 +6646,7 @@
         <v>45</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6675,7 +6675,7 @@
         <v>63</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>13</v>
@@ -6704,7 +6704,7 @@
         <v>62</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>10</v>
@@ -6733,7 +6733,7 @@
         <v>66</v>
       </c>
       <c r="H222" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>13</v>
@@ -6762,7 +6762,7 @@
         <v>64</v>
       </c>
       <c r="H223" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I223" s="1" t="s">
         <v>10</v>
@@ -6791,7 +6791,7 @@
         <v>40</v>
       </c>
       <c r="H224" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I224" s="1" t="s">
         <v>10</v>
@@ -6820,7 +6820,7 @@
         <v>41</v>
       </c>
       <c r="H225" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I225" s="1" t="s">
         <v>13</v>
@@ -6849,7 +6849,7 @@
         <v>42</v>
       </c>
       <c r="H226" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I226" s="1" t="s">
         <v>13</v>
@@ -6878,7 +6878,7 @@
         <v>43</v>
       </c>
       <c r="H227" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I227" s="1" t="s">
         <v>10</v>
@@ -6910,7 +6910,7 @@
         <v>45</v>
       </c>
       <c r="H228" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I228" s="1" t="s">
         <v>13</v>
@@ -6942,7 +6942,7 @@
         <v>45</v>
       </c>
       <c r="H229" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I229" s="1" t="s">
         <v>13</v>
@@ -6971,7 +6971,7 @@
         <v>48</v>
       </c>
       <c r="H230" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I230" s="1" t="s">
         <v>10</v>
@@ -7000,7 +7000,7 @@
         <v>49</v>
       </c>
       <c r="H231" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I231" s="1" t="s">
         <v>13</v>
@@ -7029,7 +7029,7 @@
         <v>50</v>
       </c>
       <c r="H232" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I232" s="1" t="s">
         <v>10</v>
@@ -7058,7 +7058,7 @@
         <v>52</v>
       </c>
       <c r="H233" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I233" s="1" t="s">
         <v>10</v>
@@ -7087,7 +7087,7 @@
         <v>53</v>
       </c>
       <c r="H234" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I234" s="1" t="s">
         <v>13</v>
@@ -7116,7 +7116,7 @@
         <v>55</v>
       </c>
       <c r="H235" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I235" s="1" t="s">
         <v>10</v>
@@ -7148,7 +7148,7 @@
         <v>45</v>
       </c>
       <c r="H236" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I236" s="1" t="s">
         <v>10</v>
@@ -7177,7 +7177,7 @@
         <v>67</v>
       </c>
       <c r="H237" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I237" s="1" t="s">
         <v>10</v>
@@ -7206,7 +7206,7 @@
         <v>58</v>
       </c>
       <c r="H238" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I238" s="1" t="s">
         <v>10</v>
@@ -7235,7 +7235,7 @@
         <v>60</v>
       </c>
       <c r="H239" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I239" s="1" t="s">
         <v>10</v>
@@ -7267,7 +7267,7 @@
         <v>45</v>
       </c>
       <c r="H240" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I240" s="1" t="s">
         <v>13</v>
@@ -7296,7 +7296,7 @@
         <v>63</v>
       </c>
       <c r="H241" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I241" s="1" t="s">
         <v>13</v>
@@ -7325,7 +7325,7 @@
         <v>62</v>
       </c>
       <c r="H242" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I242" s="1" t="s">
         <v>10</v>
@@ -7354,7 +7354,7 @@
         <v>66</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7383,7 +7383,7 @@
         <v>64</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7412,7 +7412,7 @@
         <v>40</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -7441,7 +7441,7 @@
         <v>41</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7470,7 +7470,7 @@
         <v>42</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>13</v>
@@ -7499,7 +7499,7 @@
         <v>43</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7531,7 +7531,7 @@
         <v>45</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -7563,7 +7563,7 @@
         <v>45</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7592,7 +7592,7 @@
         <v>48</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -7621,7 +7621,7 @@
         <v>49</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7650,7 +7650,7 @@
         <v>50</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -7679,7 +7679,7 @@
         <v>52</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7708,7 +7708,7 @@
         <v>53</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>13</v>
@@ -7737,7 +7737,7 @@
         <v>55</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -7769,7 +7769,7 @@
         <v>45</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7798,7 +7798,7 @@
         <v>67</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -7827,7 +7827,7 @@
         <v>58</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>10</v>
@@ -7856,7 +7856,7 @@
         <v>60</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>10</v>
@@ -7888,7 +7888,7 @@
         <v>45</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>13</v>
@@ -7917,7 +7917,7 @@
         <v>63</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -7946,7 +7946,7 @@
         <v>62</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>10</v>
@@ -7975,7 +7975,7 @@
         <v>66</v>
       </c>
       <c r="H264" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I264" s="1" t="s">
         <v>13</v>
@@ -8004,7 +8004,7 @@
         <v>64</v>
       </c>
       <c r="H265" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I265" s="1" t="s">
         <v>13</v>
@@ -8033,7 +8033,7 @@
         <v>40</v>
       </c>
       <c r="H266" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I266" s="1" t="s">
         <v>10</v>
@@ -8062,7 +8062,7 @@
         <v>41</v>
       </c>
       <c r="H267" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I267" s="1" t="s">
         <v>13</v>
@@ -8091,7 +8091,7 @@
         <v>42</v>
       </c>
       <c r="H268" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I268" s="1" t="s">
         <v>13</v>
@@ -8120,7 +8120,7 @@
         <v>43</v>
       </c>
       <c r="H269" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I269" s="1" t="s">
         <v>10</v>
@@ -8152,7 +8152,7 @@
         <v>45</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I270" s="1" t="s">
         <v>13</v>
@@ -8184,7 +8184,7 @@
         <v>45</v>
       </c>
       <c r="H271" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I271" s="1" t="s">
         <v>13</v>
@@ -8213,7 +8213,7 @@
         <v>48</v>
       </c>
       <c r="H272" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I272" s="1" t="s">
         <v>10</v>
@@ -8242,7 +8242,7 @@
         <v>49</v>
       </c>
       <c r="H273" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I273" s="1" t="s">
         <v>13</v>
@@ -8271,7 +8271,7 @@
         <v>50</v>
       </c>
       <c r="H274" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I274" s="1" t="s">
         <v>10</v>
@@ -8300,7 +8300,7 @@
         <v>52</v>
       </c>
       <c r="H275" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I275" s="1" t="s">
         <v>10</v>
@@ -8329,7 +8329,7 @@
         <v>53</v>
       </c>
       <c r="H276" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I276" s="1" t="s">
         <v>13</v>
@@ -8358,7 +8358,7 @@
         <v>55</v>
       </c>
       <c r="H277" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I277" s="1" t="s">
         <v>10</v>
@@ -8390,7 +8390,7 @@
         <v>45</v>
       </c>
       <c r="H278" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I278" s="1" t="s">
         <v>10</v>
@@ -8419,7 +8419,7 @@
         <v>67</v>
       </c>
       <c r="H279" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I279" s="1" t="s">
         <v>10</v>
@@ -8448,7 +8448,7 @@
         <v>58</v>
       </c>
       <c r="H280" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I280" s="1" t="s">
         <v>10</v>
@@ -8477,7 +8477,7 @@
         <v>60</v>
       </c>
       <c r="H281" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>10</v>
@@ -8509,7 +8509,7 @@
         <v>45</v>
       </c>
       <c r="H282" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -8538,7 +8538,7 @@
         <v>63</v>
       </c>
       <c r="H283" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>13</v>
@@ -8567,7 +8567,7 @@
         <v>62</v>
       </c>
       <c r="H284" s="2" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>10</v>
@@ -8596,7 +8596,7 @@
         <v>68</v>
       </c>
       <c r="H285" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I285" s="1" t="s">
         <v>13</v>
@@ -8625,7 +8625,7 @@
         <v>66</v>
       </c>
       <c r="H286" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I286" s="1" t="s">
         <v>13</v>
@@ -8654,7 +8654,7 @@
         <v>69</v>
       </c>
       <c r="H287" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>10</v>
@@ -8683,7 +8683,7 @@
         <v>64</v>
       </c>
       <c r="H288" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I288" s="1" t="s">
         <v>10</v>
@@ -8712,7 +8712,7 @@
         <v>40</v>
       </c>
       <c r="H289" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I289" s="1" t="s">
         <v>12</v>
@@ -8736,7 +8736,7 @@
       <c r="J290" s="2"/>
       <c r="K290" s="1"/>
       <c r="M290" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
@@ -8750,7 +8750,7 @@
         <v>70</v>
       </c>
       <c r="H291" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I291" s="1" t="s">
         <v>10</v>
@@ -8779,7 +8779,7 @@
         <v>41</v>
       </c>
       <c r="H292" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I292" s="1" t="s">
         <v>10</v>
@@ -8808,7 +8808,7 @@
         <v>43</v>
       </c>
       <c r="H293" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I293" s="1" t="s">
         <v>10</v>
@@ -8840,7 +8840,7 @@
         <v>45</v>
       </c>
       <c r="H294" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I294" s="1" t="s">
         <v>13</v>
@@ -8872,7 +8872,7 @@
         <v>45</v>
       </c>
       <c r="H295" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I295" s="1" t="s">
         <v>13</v>
@@ -8901,7 +8901,7 @@
         <v>48</v>
       </c>
       <c r="H296" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I296" s="1" t="s">
         <v>10</v>
@@ -8930,7 +8930,7 @@
         <v>49</v>
       </c>
       <c r="H297" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I297" s="1" t="s">
         <v>13</v>
@@ -8959,7 +8959,7 @@
         <v>50</v>
       </c>
       <c r="H298" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I298" s="1" t="s">
         <v>10</v>
@@ -8988,7 +8988,7 @@
         <v>52</v>
       </c>
       <c r="H299" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I299" s="1" t="s">
         <v>10</v>
@@ -9017,7 +9017,7 @@
         <v>71</v>
       </c>
       <c r="H300" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I300" s="1" t="s">
         <v>10</v>
@@ -9046,7 +9046,7 @@
         <v>72</v>
       </c>
       <c r="H301" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I301" s="1" t="s">
         <v>10</v>
@@ -9078,7 +9078,7 @@
         <v>45</v>
       </c>
       <c r="H302" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I302" s="1" t="s">
         <v>10</v>
@@ -9107,7 +9107,7 @@
         <v>73</v>
       </c>
       <c r="H303" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I303" s="1" t="s">
         <v>13</v>
@@ -9136,7 +9136,7 @@
         <v>74</v>
       </c>
       <c r="H304" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I304" s="1" t="s">
         <v>10</v>
@@ -9165,7 +9165,7 @@
         <v>75</v>
       </c>
       <c r="H305" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I305" s="1" t="s">
         <v>10</v>
@@ -9194,7 +9194,7 @@
         <v>67</v>
       </c>
       <c r="H306" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I306" s="1" t="s">
         <v>10</v>
@@ -9223,7 +9223,7 @@
         <v>67</v>
       </c>
       <c r="H307" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I307" s="1" t="s">
         <v>10</v>
@@ -9252,7 +9252,7 @@
         <v>76</v>
       </c>
       <c r="H308" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I308" s="1" t="s">
         <v>10</v>
@@ -9281,7 +9281,7 @@
         <v>58</v>
       </c>
       <c r="H309" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I309" s="1" t="s">
         <v>10</v>
@@ -9310,7 +9310,7 @@
         <v>77</v>
       </c>
       <c r="H310" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I310" s="1" t="s">
         <v>12</v>
@@ -9334,7 +9334,7 @@
       <c r="J311" s="2"/>
       <c r="K311" s="1"/>
       <c r="M311" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="312" spans="4:13" x14ac:dyDescent="0.3">
@@ -9348,7 +9348,7 @@
         <v>60</v>
       </c>
       <c r="H312" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I312" s="1" t="s">
         <v>10</v>
@@ -9380,7 +9380,7 @@
         <v>45</v>
       </c>
       <c r="H313" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I313" s="1" t="s">
         <v>13</v>
@@ -9409,7 +9409,7 @@
         <v>62</v>
       </c>
       <c r="H314" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="I314" s="1" t="s">
         <v>10</v>
@@ -9438,7 +9438,7 @@
         <v>68</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>13</v>
@@ -9467,7 +9467,7 @@
         <v>66</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>13</v>
@@ -9496,7 +9496,7 @@
         <v>69</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -9525,7 +9525,7 @@
         <v>64</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -9554,7 +9554,7 @@
         <v>40</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>10</v>
@@ -9583,7 +9583,7 @@
         <v>70</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>10</v>
@@ -9612,7 +9612,7 @@
         <v>41</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>10</v>
@@ -9641,7 +9641,7 @@
         <v>43</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>10</v>
@@ -9673,7 +9673,7 @@
         <v>45</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>13</v>
@@ -9705,7 +9705,7 @@
         <v>45</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>13</v>
@@ -9734,7 +9734,7 @@
         <v>48</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>10</v>
@@ -9763,7 +9763,7 @@
         <v>49</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>13</v>
@@ -9792,7 +9792,7 @@
         <v>50</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>10</v>
@@ -9821,7 +9821,7 @@
         <v>52</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>10</v>
@@ -9850,7 +9850,7 @@
         <v>71</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9879,7 +9879,7 @@
         <v>72</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9911,7 +9911,7 @@
         <v>45</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9940,7 +9940,7 @@
         <v>73</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>13</v>
@@ -9969,7 +9969,7 @@
         <v>74</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>10</v>
@@ -9998,7 +9998,7 @@
         <v>75</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -10027,7 +10027,7 @@
         <v>67</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>10</v>
@@ -10056,7 +10056,7 @@
         <v>67</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -10085,7 +10085,7 @@
         <v>76</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>13</v>
@@ -10114,7 +10114,7 @@
         <v>58</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>10</v>
@@ -10143,7 +10143,7 @@
         <v>77</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>12</v>
@@ -10167,7 +10167,7 @@
       <c r="J340" s="2"/>
       <c r="K340" s="1"/>
       <c r="M340" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="341" spans="4:13" x14ac:dyDescent="0.3">
@@ -10181,7 +10181,7 @@
         <v>60</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -10213,7 +10213,7 @@
         <v>45</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>13</v>
@@ -10242,7 +10242,7 @@
         <v>62</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -10271,7 +10271,7 @@
         <v>68</v>
       </c>
       <c r="H344" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I344" s="1" t="s">
         <v>13</v>
@@ -10300,7 +10300,7 @@
         <v>66</v>
       </c>
       <c r="H345" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I345" s="1" t="s">
         <v>13</v>
@@ -10329,7 +10329,7 @@
         <v>69</v>
       </c>
       <c r="H346" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I346" s="1" t="s">
         <v>10</v>
@@ -10358,7 +10358,7 @@
         <v>64</v>
       </c>
       <c r="H347" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I347" s="1" t="s">
         <v>13</v>
@@ -10387,7 +10387,7 @@
         <v>40</v>
       </c>
       <c r="H348" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I348" s="1" t="s">
         <v>10</v>
@@ -10416,7 +10416,7 @@
         <v>70</v>
       </c>
       <c r="H349" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I349" s="1" t="s">
         <v>10</v>
@@ -10445,7 +10445,7 @@
         <v>41</v>
       </c>
       <c r="H350" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I350" s="1" t="s">
         <v>14</v>
@@ -10469,7 +10469,7 @@
       <c r="J351" s="2"/>
       <c r="K351" s="1"/>
       <c r="M351" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="352" spans="4:13" x14ac:dyDescent="0.3">
@@ -10483,7 +10483,7 @@
         <v>43</v>
       </c>
       <c r="H352" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I352" s="1" t="s">
         <v>12</v>
@@ -10507,7 +10507,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
       <c r="M353" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="354" spans="4:13" x14ac:dyDescent="0.3">
@@ -10524,7 +10524,7 @@
         <v>45</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I354" s="1" t="s">
         <v>13</v>
@@ -10556,7 +10556,7 @@
         <v>45</v>
       </c>
       <c r="H355" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I355" s="1" t="s">
         <v>13</v>
@@ -10585,7 +10585,7 @@
         <v>48</v>
       </c>
       <c r="H356" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I356" s="1" t="s">
         <v>10</v>
@@ -10614,7 +10614,7 @@
         <v>49</v>
       </c>
       <c r="H357" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I357" s="1" t="s">
         <v>13</v>
@@ -10643,7 +10643,7 @@
         <v>50</v>
       </c>
       <c r="H358" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I358" s="1" t="s">
         <v>10</v>
@@ -10672,7 +10672,7 @@
         <v>52</v>
       </c>
       <c r="H359" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I359" s="1" t="s">
         <v>12</v>
@@ -10696,7 +10696,7 @@
       <c r="J360" s="2"/>
       <c r="K360" s="1"/>
       <c r="M360" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="361" spans="4:13" x14ac:dyDescent="0.3">
@@ -10710,7 +10710,7 @@
         <v>71</v>
       </c>
       <c r="H361" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I361" s="1" t="s">
         <v>10</v>
@@ -10739,7 +10739,7 @@
         <v>72</v>
       </c>
       <c r="H362" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I362" s="1" t="s">
         <v>13</v>
@@ -10771,7 +10771,7 @@
         <v>45</v>
       </c>
       <c r="H363" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I363" s="1" t="s">
         <v>10</v>
@@ -10800,7 +10800,7 @@
         <v>73</v>
       </c>
       <c r="H364" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I364" s="1" t="s">
         <v>13</v>
@@ -10829,7 +10829,7 @@
         <v>74</v>
       </c>
       <c r="H365" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I365" s="1" t="s">
         <v>10</v>
@@ -10858,7 +10858,7 @@
         <v>75</v>
       </c>
       <c r="H366" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I366" s="1" t="s">
         <v>13</v>
@@ -10887,7 +10887,7 @@
         <v>67</v>
       </c>
       <c r="H367" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I367" s="1" t="s">
         <v>13</v>
@@ -10916,7 +10916,7 @@
         <v>67</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I368" s="1" t="s">
         <v>10</v>
@@ -10945,7 +10945,7 @@
         <v>76</v>
       </c>
       <c r="H369" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I369" s="1" t="s">
         <v>13</v>
@@ -10974,7 +10974,7 @@
         <v>58</v>
       </c>
       <c r="H370" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I370" s="1" t="s">
         <v>10</v>
@@ -11003,7 +11003,7 @@
         <v>77</v>
       </c>
       <c r="H371" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I371" s="1" t="s">
         <v>12</v>
@@ -11027,7 +11027,7 @@
       <c r="J372" s="2"/>
       <c r="K372" s="1"/>
       <c r="M372" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="373" spans="4:13" x14ac:dyDescent="0.3">
@@ -11041,7 +11041,7 @@
         <v>60</v>
       </c>
       <c r="H373" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I373" s="1" t="s">
         <v>10</v>
@@ -11073,7 +11073,7 @@
         <v>45</v>
       </c>
       <c r="H374" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I374" s="1" t="s">
         <v>13</v>
@@ -11102,7 +11102,7 @@
         <v>62</v>
       </c>
       <c r="H375" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I375" s="1" t="s">
         <v>10</v>
@@ -11131,7 +11131,7 @@
         <v>68</v>
       </c>
       <c r="H376" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I376" s="1" t="s">
         <v>13</v>
@@ -11160,7 +11160,7 @@
         <v>66</v>
       </c>
       <c r="H377" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I377" s="1" t="s">
         <v>13</v>
@@ -11189,7 +11189,7 @@
         <v>69</v>
       </c>
       <c r="H378" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I378" s="1" t="s">
         <v>10</v>
@@ -11218,7 +11218,7 @@
         <v>64</v>
       </c>
       <c r="H379" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I379" s="1" t="s">
         <v>13</v>
@@ -11247,7 +11247,7 @@
         <v>40</v>
       </c>
       <c r="H380" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I380" s="1" t="s">
         <v>10</v>
@@ -11276,7 +11276,7 @@
         <v>70</v>
       </c>
       <c r="H381" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I381" s="1" t="s">
         <v>13</v>
@@ -11305,7 +11305,7 @@
         <v>41</v>
       </c>
       <c r="H382" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I382" s="1" t="s">
         <v>13</v>
@@ -11334,7 +11334,7 @@
         <v>43</v>
       </c>
       <c r="H383" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I383" s="1" t="s">
         <v>10</v>
@@ -11366,7 +11366,7 @@
         <v>45</v>
       </c>
       <c r="H384" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I384" s="1" t="s">
         <v>13</v>
@@ -11398,7 +11398,7 @@
         <v>45</v>
       </c>
       <c r="H385" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I385" s="1" t="s">
         <v>13</v>
@@ -11427,7 +11427,7 @@
         <v>48</v>
       </c>
       <c r="H386" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I386" s="1" t="s">
         <v>10</v>
@@ -11456,7 +11456,7 @@
         <v>49</v>
       </c>
       <c r="H387" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I387" s="1" t="s">
         <v>13</v>
@@ -11485,7 +11485,7 @@
         <v>50</v>
       </c>
       <c r="H388" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I388" s="1" t="s">
         <v>10</v>
@@ -11514,7 +11514,7 @@
         <v>52</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I389" s="1" t="s">
         <v>10</v>
@@ -11543,7 +11543,7 @@
         <v>71</v>
       </c>
       <c r="H390" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I390" s="1" t="s">
         <v>10</v>
@@ -11572,7 +11572,7 @@
         <v>72</v>
       </c>
       <c r="H391" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I391" s="1" t="s">
         <v>13</v>
@@ -11604,7 +11604,7 @@
         <v>45</v>
       </c>
       <c r="H392" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I392" s="1" t="s">
         <v>10</v>
@@ -11633,7 +11633,7 @@
         <v>73</v>
       </c>
       <c r="H393" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I393" s="1" t="s">
         <v>13</v>
@@ -11662,7 +11662,7 @@
         <v>74</v>
       </c>
       <c r="H394" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I394" s="1" t="s">
         <v>10</v>
@@ -11691,7 +11691,7 @@
         <v>75</v>
       </c>
       <c r="H395" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I395" s="1" t="s">
         <v>13</v>
@@ -11720,7 +11720,7 @@
         <v>67</v>
       </c>
       <c r="H396" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I396" s="1" t="s">
         <v>10</v>
@@ -11749,7 +11749,7 @@
         <v>67</v>
       </c>
       <c r="H397" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I397" s="1" t="s">
         <v>10</v>
@@ -11778,7 +11778,7 @@
         <v>76</v>
       </c>
       <c r="H398" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I398" s="1" t="s">
         <v>13</v>
@@ -11807,7 +11807,7 @@
         <v>58</v>
       </c>
       <c r="H399" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I399" s="1" t="s">
         <v>12</v>
@@ -11831,7 +11831,7 @@
       <c r="J400" s="2"/>
       <c r="K400" s="1"/>
       <c r="M400" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="401" spans="4:13" x14ac:dyDescent="0.3">
@@ -11845,7 +11845,7 @@
         <v>77</v>
       </c>
       <c r="H401" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I401" s="1" t="s">
         <v>13</v>
@@ -11874,7 +11874,7 @@
         <v>60</v>
       </c>
       <c r="H402" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I402" s="1" t="s">
         <v>10</v>
@@ -11906,7 +11906,7 @@
         <v>45</v>
       </c>
       <c r="H403" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I403" s="1" t="s">
         <v>13</v>
@@ -11935,7 +11935,7 @@
         <v>62</v>
       </c>
       <c r="H404" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I404" s="1" t="s">
         <v>10</v>
@@ -11964,7 +11964,7 @@
         <v>68</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>13</v>
@@ -11993,7 +11993,7 @@
         <v>66</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>13</v>
@@ -12022,7 +12022,7 @@
         <v>69</v>
       </c>
       <c r="H407" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>10</v>
@@ -12051,7 +12051,7 @@
         <v>64</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I408" s="1" t="s">
         <v>13</v>
@@ -12080,7 +12080,7 @@
         <v>40</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>10</v>
@@ -12109,7 +12109,7 @@
         <v>70</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>10</v>
@@ -12138,7 +12138,7 @@
         <v>41</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>13</v>
@@ -12167,7 +12167,7 @@
         <v>43</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>10</v>
@@ -12199,7 +12199,7 @@
         <v>45</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>13</v>
@@ -12231,7 +12231,7 @@
         <v>45</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>13</v>
@@ -12260,7 +12260,7 @@
         <v>48</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>10</v>
@@ -12289,7 +12289,7 @@
         <v>49</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>10</v>
@@ -12318,7 +12318,7 @@
         <v>50</v>
       </c>
       <c r="H417" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I417" s="1" t="s">
         <v>10</v>
@@ -12347,7 +12347,7 @@
         <v>52</v>
       </c>
       <c r="H418" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I418" s="1" t="s">
         <v>10</v>
@@ -12376,7 +12376,7 @@
         <v>71</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>10</v>
@@ -12405,7 +12405,7 @@
         <v>72</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>13</v>
@@ -12437,7 +12437,7 @@
         <v>45</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I421" s="1" t="s">
         <v>10</v>
@@ -12466,7 +12466,7 @@
         <v>73</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>13</v>
@@ -12495,7 +12495,7 @@
         <v>74</v>
       </c>
       <c r="H423" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>13</v>
@@ -12524,7 +12524,7 @@
         <v>75</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>13</v>
@@ -12553,7 +12553,7 @@
         <v>67</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>10</v>
@@ -12582,7 +12582,7 @@
         <v>67</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>10</v>
@@ -12611,7 +12611,7 @@
         <v>76</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>13</v>
@@ -12640,7 +12640,7 @@
         <v>58</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>10</v>
@@ -12669,7 +12669,7 @@
         <v>77</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>13</v>
@@ -12698,7 +12698,7 @@
         <v>60</v>
       </c>
       <c r="H430" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I430" s="1" t="s">
         <v>10</v>
@@ -12730,7 +12730,7 @@
         <v>45</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>13</v>
@@ -12759,7 +12759,7 @@
         <v>62</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>12</v>
@@ -12783,7 +12783,7 @@
       <c r="J433" s="2"/>
       <c r="K433" s="1"/>
       <c r="M433" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="434" spans="4:13" x14ac:dyDescent="0.3">
@@ -12797,7 +12797,7 @@
         <v>68</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>13</v>
@@ -12826,7 +12826,7 @@
         <v>66</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>13</v>
@@ -12855,7 +12855,7 @@
         <v>69</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>13</v>
@@ -12884,7 +12884,7 @@
         <v>64</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>13</v>
@@ -12913,7 +12913,7 @@
         <v>40</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>10</v>
@@ -12942,7 +12942,7 @@
         <v>70</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I439" s="1" t="s">
         <v>10</v>
@@ -12971,7 +12971,7 @@
         <v>41</v>
       </c>
       <c r="H440" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I440" s="1" t="s">
         <v>13</v>
@@ -13000,7 +13000,7 @@
         <v>43</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>10</v>
@@ -13032,7 +13032,7 @@
         <v>45</v>
       </c>
       <c r="H442" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I442" s="1" t="s">
         <v>13</v>
@@ -13064,7 +13064,7 @@
         <v>45</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>13</v>
@@ -13093,7 +13093,7 @@
         <v>48</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>10</v>
@@ -13122,7 +13122,7 @@
         <v>49</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I445" s="1" t="s">
         <v>13</v>
@@ -13151,7 +13151,7 @@
         <v>50</v>
       </c>
       <c r="H446" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I446" s="1" t="s">
         <v>10</v>
@@ -13180,7 +13180,7 @@
         <v>52</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>10</v>
@@ -13209,7 +13209,7 @@
         <v>71</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>10</v>
@@ -13238,7 +13238,7 @@
         <v>72</v>
       </c>
       <c r="H449" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I449" s="1" t="s">
         <v>13</v>
@@ -13270,7 +13270,7 @@
         <v>45</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>10</v>
@@ -13299,7 +13299,7 @@
         <v>73</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>13</v>
@@ -13328,7 +13328,7 @@
         <v>74</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>13</v>
@@ -13357,7 +13357,7 @@
         <v>75</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>13</v>
@@ -13386,7 +13386,7 @@
         <v>67</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>10</v>
@@ -13415,7 +13415,7 @@
         <v>67</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>10</v>
@@ -13444,7 +13444,7 @@
         <v>76</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>13</v>
@@ -13473,7 +13473,7 @@
         <v>58</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>10</v>
@@ -13502,7 +13502,7 @@
         <v>77</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>13</v>
@@ -13531,7 +13531,7 @@
         <v>60</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>13</v>
@@ -13563,7 +13563,7 @@
         <v>45</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -13592,7 +13592,7 @@
         <v>62</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>10</v>
@@ -13621,7 +13621,7 @@
         <v>68</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I462" s="1" t="s">
         <v>13</v>
@@ -13650,7 +13650,7 @@
         <v>66</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>13</v>
@@ -13679,7 +13679,7 @@
         <v>69</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>10</v>
@@ -13708,7 +13708,7 @@
         <v>64</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>13</v>
@@ -13737,7 +13737,7 @@
         <v>40</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I466" s="1" t="s">
         <v>10</v>
@@ -13766,7 +13766,7 @@
         <v>70</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>10</v>
@@ -13795,7 +13795,7 @@
         <v>41</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>14</v>
@@ -13819,7 +13819,7 @@
       <c r="J469" s="2"/>
       <c r="K469" s="1"/>
       <c r="M469" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="470" spans="4:13" x14ac:dyDescent="0.3">
@@ -13833,7 +13833,7 @@
         <v>43</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -13865,7 +13865,7 @@
         <v>45</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>13</v>
@@ -13897,7 +13897,7 @@
         <v>45</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>13</v>
@@ -13926,7 +13926,7 @@
         <v>48</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I473" s="1" t="s">
         <v>10</v>
@@ -13955,7 +13955,7 @@
         <v>49</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I474" s="1" t="s">
         <v>13</v>
@@ -13984,7 +13984,7 @@
         <v>50</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>10</v>
@@ -14013,7 +14013,7 @@
         <v>52</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I476" s="1" t="s">
         <v>13</v>
@@ -14042,7 +14042,7 @@
         <v>71</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>13</v>
@@ -14071,7 +14071,7 @@
         <v>72</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>13</v>
@@ -14103,7 +14103,7 @@
         <v>45</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>10</v>
@@ -14132,7 +14132,7 @@
         <v>73</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>13</v>
@@ -14161,7 +14161,7 @@
         <v>74</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>13</v>
@@ -14190,7 +14190,7 @@
         <v>75</v>
       </c>
       <c r="H482" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I482" s="1" t="s">
         <v>12</v>
@@ -14214,7 +14214,7 @@
       <c r="J483" s="2"/>
       <c r="K483" s="1"/>
       <c r="M483" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="484" spans="4:13" x14ac:dyDescent="0.3">
@@ -14228,7 +14228,7 @@
         <v>67</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I484" s="1" t="s">
         <v>10</v>
@@ -14257,7 +14257,7 @@
         <v>67</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>10</v>
@@ -14286,7 +14286,7 @@
         <v>76</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>13</v>
@@ -14315,7 +14315,7 @@
         <v>58</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>10</v>
@@ -14344,7 +14344,7 @@
         <v>77</v>
       </c>
       <c r="H488" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I488" s="1" t="s">
         <v>13</v>
@@ -14373,7 +14373,7 @@
         <v>60</v>
       </c>
       <c r="H489" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I489" s="1" t="s">
         <v>13</v>
@@ -14405,7 +14405,7 @@
         <v>45</v>
       </c>
       <c r="H490" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I490" s="1" t="s">
         <v>13</v>
@@ -14434,7 +14434,7 @@
         <v>62</v>
       </c>
       <c r="H491" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I491" s="1" t="s">
         <v>13</v>
@@ -14463,7 +14463,7 @@
         <v>68</v>
       </c>
       <c r="H492" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I492" s="1" t="s">
         <v>13</v>
@@ -14492,7 +14492,7 @@
         <v>66</v>
       </c>
       <c r="H493" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I493" s="1" t="s">
         <v>13</v>
@@ -14521,7 +14521,7 @@
         <v>69</v>
       </c>
       <c r="H494" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I494" s="1" t="s">
         <v>10</v>
@@ -14550,7 +14550,7 @@
         <v>64</v>
       </c>
       <c r="H495" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I495" s="1" t="s">
         <v>13</v>
@@ -14579,7 +14579,7 @@
         <v>40</v>
       </c>
       <c r="H496" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I496" s="1" t="s">
         <v>10</v>
@@ -14608,7 +14608,7 @@
         <v>70</v>
       </c>
       <c r="H497" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I497" s="1" t="s">
         <v>10</v>
@@ -14637,7 +14637,7 @@
         <v>41</v>
       </c>
       <c r="H498" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I498" s="1" t="s">
         <v>13</v>
@@ -14666,7 +14666,7 @@
         <v>43</v>
       </c>
       <c r="H499" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I499" s="1" t="s">
         <v>10</v>
@@ -14698,7 +14698,7 @@
         <v>45</v>
       </c>
       <c r="H500" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I500" s="1" t="s">
         <v>13</v>
@@ -14730,7 +14730,7 @@
         <v>45</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I501" s="1" t="s">
         <v>14</v>
@@ -14754,7 +14754,7 @@
       <c r="J502" s="2"/>
       <c r="K502" s="1"/>
       <c r="M502" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="503" spans="4:13" x14ac:dyDescent="0.3">
@@ -14768,7 +14768,7 @@
         <v>48</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I503" s="1" t="s">
         <v>10</v>
@@ -14797,7 +14797,7 @@
         <v>49</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I504" s="1" t="s">
         <v>13</v>
@@ -14826,7 +14826,7 @@
         <v>50</v>
       </c>
       <c r="H505" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I505" s="1" t="s">
         <v>10</v>
@@ -14855,7 +14855,7 @@
         <v>52</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I506" s="1" t="s">
         <v>13</v>
@@ -14884,7 +14884,7 @@
         <v>71</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I507" s="1" t="s">
         <v>10</v>
@@ -14913,7 +14913,7 @@
         <v>72</v>
       </c>
       <c r="H508" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I508" s="1" t="s">
         <v>13</v>
@@ -14945,7 +14945,7 @@
         <v>45</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I509" s="1" t="s">
         <v>10</v>
@@ -14974,7 +14974,7 @@
         <v>73</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I510" s="1" t="s">
         <v>13</v>
@@ -15003,7 +15003,7 @@
         <v>74</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I511" s="1" t="s">
         <v>13</v>
@@ -15032,7 +15032,7 @@
         <v>75</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>13</v>
@@ -15061,7 +15061,7 @@
         <v>67</v>
       </c>
       <c r="H513" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>10</v>
@@ -15090,7 +15090,7 @@
         <v>67</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>10</v>
@@ -15119,7 +15119,7 @@
         <v>76</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>13</v>
@@ -15148,7 +15148,7 @@
         <v>58</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>10</v>
@@ -15177,7 +15177,7 @@
         <v>77</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>13</v>
@@ -15206,7 +15206,7 @@
         <v>60</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>13</v>
@@ -15238,7 +15238,7 @@
         <v>45</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I519" s="1" t="s">
         <v>12</v>
@@ -15262,7 +15262,7 @@
       <c r="J520" s="2"/>
       <c r="K520" s="1"/>
       <c r="M520" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="521" spans="4:13" x14ac:dyDescent="0.3">
@@ -15276,7 +15276,7 @@
         <v>62</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I521" s="1" t="s">
         <v>10</v>
@@ -15305,7 +15305,7 @@
         <v>68</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I522" s="1" t="s">
         <v>13</v>
@@ -15334,7 +15334,7 @@
         <v>66</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I523" s="1" t="s">
         <v>13</v>
@@ -15363,7 +15363,7 @@
         <v>69</v>
       </c>
       <c r="H524" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I524" s="1" t="s">
         <v>10</v>
@@ -15392,7 +15392,7 @@
         <v>64</v>
       </c>
       <c r="H525" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I525" s="1" t="s">
         <v>13</v>
@@ -15421,7 +15421,7 @@
         <v>40</v>
       </c>
       <c r="H526" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I526" s="1" t="s">
         <v>10</v>
@@ -15450,7 +15450,7 @@
         <v>70</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I527" s="1" t="s">
         <v>10</v>
@@ -15479,7 +15479,7 @@
         <v>41</v>
       </c>
       <c r="H528" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I528" s="1" t="s">
         <v>13</v>
@@ -15508,7 +15508,7 @@
         <v>43</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I529" s="1" t="s">
         <v>10</v>
@@ -15540,7 +15540,7 @@
         <v>45</v>
       </c>
       <c r="H530" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I530" s="1" t="s">
         <v>13</v>
@@ -15572,7 +15572,7 @@
         <v>45</v>
       </c>
       <c r="H531" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I531" s="1" t="s">
         <v>13</v>
@@ -15601,7 +15601,7 @@
         <v>48</v>
       </c>
       <c r="H532" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I532" s="1" t="s">
         <v>10</v>
@@ -15630,7 +15630,7 @@
         <v>49</v>
       </c>
       <c r="H533" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I533" s="1" t="s">
         <v>13</v>
@@ -15659,7 +15659,7 @@
         <v>50</v>
       </c>
       <c r="H534" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I534" s="1" t="s">
         <v>10</v>
@@ -15688,7 +15688,7 @@
         <v>52</v>
       </c>
       <c r="H535" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I535" s="1" t="s">
         <v>13</v>
@@ -15717,7 +15717,7 @@
         <v>71</v>
       </c>
       <c r="H536" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I536" s="1" t="s">
         <v>10</v>
@@ -15746,7 +15746,7 @@
         <v>72</v>
       </c>
       <c r="H537" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I537" s="1" t="s">
         <v>13</v>
@@ -15778,7 +15778,7 @@
         <v>45</v>
       </c>
       <c r="H538" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I538" s="1" t="s">
         <v>12</v>
@@ -15802,7 +15802,7 @@
       <c r="J539" s="2"/>
       <c r="K539" s="1"/>
       <c r="M539" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="540" spans="4:13" x14ac:dyDescent="0.3">
@@ -15816,7 +15816,7 @@
         <v>73</v>
       </c>
       <c r="H540" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I540" s="1" t="s">
         <v>13</v>
@@ -15845,7 +15845,7 @@
         <v>74</v>
       </c>
       <c r="H541" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I541" s="1" t="s">
         <v>13</v>
@@ -15874,7 +15874,7 @@
         <v>75</v>
       </c>
       <c r="H542" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I542" s="1" t="s">
         <v>13</v>
@@ -15903,7 +15903,7 @@
         <v>67</v>
       </c>
       <c r="H543" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I543" s="1" t="s">
         <v>14</v>
@@ -15927,7 +15927,7 @@
       <c r="J544" s="2"/>
       <c r="K544" s="1"/>
       <c r="M544" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="545" spans="4:13" x14ac:dyDescent="0.3">
@@ -15941,7 +15941,7 @@
         <v>67</v>
       </c>
       <c r="H545" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I545" s="1" t="s">
         <v>10</v>
@@ -15970,7 +15970,7 @@
         <v>76</v>
       </c>
       <c r="H546" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I546" s="1" t="s">
         <v>13</v>
@@ -15999,7 +15999,7 @@
         <v>58</v>
       </c>
       <c r="H547" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I547" s="1" t="s">
         <v>10</v>
@@ -16028,7 +16028,7 @@
         <v>77</v>
       </c>
       <c r="H548" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I548" s="1" t="s">
         <v>13</v>
@@ -16057,7 +16057,7 @@
         <v>60</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I549" s="1" t="s">
         <v>13</v>
@@ -16089,7 +16089,7 @@
         <v>45</v>
       </c>
       <c r="H550" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I550" s="1" t="s">
         <v>13</v>
@@ -16118,7 +16118,7 @@
         <v>62</v>
       </c>
       <c r="H551" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I551" s="1" t="s">
         <v>13</v>
@@ -16147,7 +16147,7 @@
         <v>68</v>
       </c>
       <c r="H552" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I552" s="1" t="s">
         <v>13</v>
@@ -16176,7 +16176,7 @@
         <v>66</v>
       </c>
       <c r="H553" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I553" s="1" t="s">
         <v>13</v>
@@ -16205,7 +16205,7 @@
         <v>69</v>
       </c>
       <c r="H554" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I554" s="1" t="s">
         <v>10</v>
@@ -16234,7 +16234,7 @@
         <v>64</v>
       </c>
       <c r="H555" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I555" s="1" t="s">
         <v>13</v>
@@ -16263,7 +16263,7 @@
         <v>40</v>
       </c>
       <c r="H556" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I556" s="1" t="s">
         <v>10</v>
@@ -16292,7 +16292,7 @@
         <v>70</v>
       </c>
       <c r="H557" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I557" s="1" t="s">
         <v>10</v>
@@ -16321,7 +16321,7 @@
         <v>41</v>
       </c>
       <c r="H558" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I558" s="1" t="s">
         <v>13</v>
@@ -16350,7 +16350,7 @@
         <v>43</v>
       </c>
       <c r="H559" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I559" s="1" t="s">
         <v>13</v>
@@ -16382,7 +16382,7 @@
         <v>45</v>
       </c>
       <c r="H560" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I560" s="1" t="s">
         <v>13</v>
@@ -16414,7 +16414,7 @@
         <v>45</v>
       </c>
       <c r="H561" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I561" s="1" t="s">
         <v>13</v>
@@ -16443,7 +16443,7 @@
         <v>48</v>
       </c>
       <c r="H562" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I562" s="1" t="s">
         <v>10</v>
@@ -16472,7 +16472,7 @@
         <v>49</v>
       </c>
       <c r="H563" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I563" s="1" t="s">
         <v>13</v>
@@ -16501,7 +16501,7 @@
         <v>50</v>
       </c>
       <c r="H564" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I564" s="1" t="s">
         <v>10</v>
@@ -16530,7 +16530,7 @@
         <v>52</v>
       </c>
       <c r="H565" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I565" s="1" t="s">
         <v>13</v>
@@ -16559,7 +16559,7 @@
         <v>71</v>
       </c>
       <c r="H566" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I566" s="1" t="s">
         <v>10</v>
@@ -16588,7 +16588,7 @@
         <v>72</v>
       </c>
       <c r="H567" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I567" s="1" t="s">
         <v>13</v>
@@ -16620,7 +16620,7 @@
         <v>45</v>
       </c>
       <c r="H568" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I568" s="1" t="s">
         <v>13</v>
@@ -16649,7 +16649,7 @@
         <v>73</v>
       </c>
       <c r="H569" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I569" s="1" t="s">
         <v>13</v>
@@ -16678,7 +16678,7 @@
         <v>74</v>
       </c>
       <c r="H570" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I570" s="1" t="s">
         <v>13</v>
@@ -16707,7 +16707,7 @@
         <v>75</v>
       </c>
       <c r="H571" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I571" s="1" t="s">
         <v>13</v>
@@ -16736,7 +16736,7 @@
         <v>67</v>
       </c>
       <c r="H572" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I572" s="1" t="s">
         <v>10</v>
@@ -16765,7 +16765,7 @@
         <v>67</v>
       </c>
       <c r="H573" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I573" s="1" t="s">
         <v>10</v>
@@ -16794,7 +16794,7 @@
         <v>76</v>
       </c>
       <c r="H574" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I574" s="1" t="s">
         <v>13</v>
@@ -16823,7 +16823,7 @@
         <v>58</v>
       </c>
       <c r="H575" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I575" s="1" t="s">
         <v>13</v>
@@ -16852,7 +16852,7 @@
         <v>77</v>
       </c>
       <c r="H576" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I576" s="1" t="s">
         <v>13</v>
@@ -16881,7 +16881,7 @@
         <v>60</v>
       </c>
       <c r="H577" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I577" s="1" t="s">
         <v>10</v>
@@ -16913,7 +16913,7 @@
         <v>45</v>
       </c>
       <c r="H578" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I578" s="1" t="s">
         <v>13</v>
@@ -16942,7 +16942,7 @@
         <v>62</v>
       </c>
       <c r="H579" s="2" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I579" s="1" t="s">
         <v>10</v>
@@ -16971,7 +16971,7 @@
         <v>68</v>
       </c>
       <c r="H580" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I580" s="1" t="s">
         <v>13</v>
@@ -17000,7 +17000,7 @@
         <v>66</v>
       </c>
       <c r="H581" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I581" s="1" t="s">
         <v>13</v>
@@ -17029,7 +17029,7 @@
         <v>69</v>
       </c>
       <c r="H582" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I582" s="1" t="s">
         <v>10</v>
@@ -17058,7 +17058,7 @@
         <v>64</v>
       </c>
       <c r="H583" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I583" s="1" t="s">
         <v>13</v>
@@ -17087,7 +17087,7 @@
         <v>40</v>
       </c>
       <c r="H584" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I584" s="1" t="s">
         <v>10</v>
@@ -17116,7 +17116,7 @@
         <v>70</v>
       </c>
       <c r="H585" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I585" s="1" t="s">
         <v>10</v>
@@ -17145,7 +17145,7 @@
         <v>41</v>
       </c>
       <c r="H586" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I586" s="1" t="s">
         <v>13</v>
@@ -17174,7 +17174,7 @@
         <v>43</v>
       </c>
       <c r="H587" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I587" s="1" t="s">
         <v>13</v>
@@ -17206,7 +17206,7 @@
         <v>45</v>
       </c>
       <c r="H588" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I588" s="1" t="s">
         <v>13</v>
@@ -17238,7 +17238,7 @@
         <v>45</v>
       </c>
       <c r="H589" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I589" s="1" t="s">
         <v>13</v>
@@ -17267,7 +17267,7 @@
         <v>48</v>
       </c>
       <c r="H590" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I590" s="1" t="s">
         <v>13</v>
@@ -17296,7 +17296,7 @@
         <v>49</v>
       </c>
       <c r="H591" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I591" s="1" t="s">
         <v>13</v>
@@ -17325,7 +17325,7 @@
         <v>50</v>
       </c>
       <c r="H592" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I592" s="1" t="s">
         <v>10</v>
@@ -17354,7 +17354,7 @@
         <v>52</v>
       </c>
       <c r="H593" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I593" s="1" t="s">
         <v>13</v>
@@ -17383,7 +17383,7 @@
         <v>71</v>
       </c>
       <c r="H594" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I594" s="1" t="s">
         <v>12</v>
@@ -17407,7 +17407,7 @@
       <c r="J595" s="2"/>
       <c r="K595" s="1"/>
       <c r="M595" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="596" spans="4:13" x14ac:dyDescent="0.3">
@@ -17421,7 +17421,7 @@
         <v>72</v>
       </c>
       <c r="H596" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I596" s="1" t="s">
         <v>13</v>
@@ -17453,7 +17453,7 @@
         <v>45</v>
       </c>
       <c r="H597" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I597" s="1" t="s">
         <v>13</v>
@@ -17482,7 +17482,7 @@
         <v>73</v>
       </c>
       <c r="H598" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I598" s="1" t="s">
         <v>13</v>
@@ -17511,7 +17511,7 @@
         <v>74</v>
       </c>
       <c r="H599" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I599" s="1" t="s">
         <v>13</v>
@@ -17540,7 +17540,7 @@
         <v>75</v>
       </c>
       <c r="H600" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I600" s="1" t="s">
         <v>13</v>
@@ -17569,7 +17569,7 @@
         <v>67</v>
       </c>
       <c r="H601" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I601" s="1" t="s">
         <v>10</v>
@@ -17598,7 +17598,7 @@
         <v>67</v>
       </c>
       <c r="H602" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I602" s="1" t="s">
         <v>13</v>
@@ -17627,7 +17627,7 @@
         <v>76</v>
       </c>
       <c r="H603" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I603" s="1" t="s">
         <v>13</v>
@@ -17656,7 +17656,7 @@
         <v>58</v>
       </c>
       <c r="H604" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I604" s="1" t="s">
         <v>13</v>
@@ -17685,7 +17685,7 @@
         <v>77</v>
       </c>
       <c r="H605" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I605" s="1" t="s">
         <v>13</v>
@@ -17714,7 +17714,7 @@
         <v>60</v>
       </c>
       <c r="H606" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I606" s="1" t="s">
         <v>13</v>
@@ -17746,7 +17746,7 @@
         <v>45</v>
       </c>
       <c r="H607" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I607" s="1" t="s">
         <v>13</v>
@@ -17775,7 +17775,7 @@
         <v>62</v>
       </c>
       <c r="H608" s="2" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="I608" s="1" t="s">
         <v>10</v>
@@ -17804,7 +17804,7 @@
         <v>68</v>
       </c>
       <c r="H609" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I609" s="1" t="s">
         <v>13</v>
@@ -17833,7 +17833,7 @@
         <v>66</v>
       </c>
       <c r="H610" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I610" s="1" t="s">
         <v>13</v>
@@ -17862,7 +17862,7 @@
         <v>69</v>
       </c>
       <c r="H611" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I611" s="1" t="s">
         <v>10</v>
@@ -17891,7 +17891,7 @@
         <v>64</v>
       </c>
       <c r="H612" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I612" s="1" t="s">
         <v>13</v>
@@ -17920,7 +17920,7 @@
         <v>40</v>
       </c>
       <c r="H613" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I613" s="1" t="s">
         <v>10</v>
@@ -17949,7 +17949,7 @@
         <v>70</v>
       </c>
       <c r="H614" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I614" s="1" t="s">
         <v>10</v>
@@ -17978,7 +17978,7 @@
         <v>41</v>
       </c>
       <c r="H615" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I615" s="1" t="s">
         <v>13</v>
@@ -18007,7 +18007,7 @@
         <v>43</v>
       </c>
       <c r="H616" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I616" s="1" t="s">
         <v>13</v>
@@ -18039,7 +18039,7 @@
         <v>45</v>
       </c>
       <c r="H617" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I617" s="1" t="s">
         <v>13</v>
@@ -18071,7 +18071,7 @@
         <v>45</v>
       </c>
       <c r="H618" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I618" s="1" t="s">
         <v>13</v>
@@ -18100,7 +18100,7 @@
         <v>48</v>
       </c>
       <c r="H619" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I619" s="1" t="s">
         <v>10</v>
@@ -18129,7 +18129,7 @@
         <v>49</v>
       </c>
       <c r="H620" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I620" s="1" t="s">
         <v>13</v>
@@ -18158,7 +18158,7 @@
         <v>50</v>
       </c>
       <c r="H621" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I621" s="1" t="s">
         <v>10</v>
@@ -18187,7 +18187,7 @@
         <v>52</v>
       </c>
       <c r="H622" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I622" s="1" t="s">
         <v>13</v>
@@ -18216,7 +18216,7 @@
         <v>71</v>
       </c>
       <c r="H623" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I623" s="1" t="s">
         <v>13</v>
@@ -18245,7 +18245,7 @@
         <v>72</v>
       </c>
       <c r="H624" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I624" s="1" t="s">
         <v>13</v>
@@ -18277,7 +18277,7 @@
         <v>45</v>
       </c>
       <c r="H625" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I625" s="1" t="s">
         <v>13</v>
@@ -18306,7 +18306,7 @@
         <v>73</v>
       </c>
       <c r="H626" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I626" s="1" t="s">
         <v>13</v>
@@ -18335,7 +18335,7 @@
         <v>74</v>
       </c>
       <c r="H627" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I627" s="1" t="s">
         <v>13</v>
@@ -18364,7 +18364,7 @@
         <v>75</v>
       </c>
       <c r="H628" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I628" s="1" t="s">
         <v>13</v>
@@ -18393,7 +18393,7 @@
         <v>67</v>
       </c>
       <c r="H629" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I629" s="1" t="s">
         <v>10</v>
@@ -18422,7 +18422,7 @@
         <v>67</v>
       </c>
       <c r="H630" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I630" s="1" t="s">
         <v>12</v>
@@ -18446,7 +18446,7 @@
       <c r="J631" s="2"/>
       <c r="K631" s="1"/>
       <c r="M631" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="632" spans="4:13" x14ac:dyDescent="0.3">
@@ -18460,7 +18460,7 @@
         <v>76</v>
       </c>
       <c r="H632" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I632" s="1" t="s">
         <v>13</v>
@@ -18489,7 +18489,7 @@
         <v>58</v>
       </c>
       <c r="H633" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I633" s="1" t="s">
         <v>13</v>
@@ -18518,7 +18518,7 @@
         <v>77</v>
       </c>
       <c r="H634" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I634" s="1" t="s">
         <v>13</v>
@@ -18547,7 +18547,7 @@
         <v>60</v>
       </c>
       <c r="H635" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I635" s="1" t="s">
         <v>13</v>
@@ -18579,7 +18579,7 @@
         <v>45</v>
       </c>
       <c r="H636" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I636" s="1" t="s">
         <v>13</v>
@@ -18608,7 +18608,7 @@
         <v>62</v>
       </c>
       <c r="H637" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I637" s="1" t="s">
         <v>13</v>
@@ -18637,7 +18637,7 @@
         <v>68</v>
       </c>
       <c r="H638" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I638" s="1" t="s">
         <v>13</v>
@@ -18666,7 +18666,7 @@
         <v>66</v>
       </c>
       <c r="H639" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I639" s="1" t="s">
         <v>13</v>
@@ -18695,7 +18695,7 @@
         <v>69</v>
       </c>
       <c r="H640" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I640" s="1" t="s">
         <v>10</v>
@@ -18724,7 +18724,7 @@
         <v>64</v>
       </c>
       <c r="H641" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I641" s="1" t="s">
         <v>10</v>
@@ -18753,7 +18753,7 @@
         <v>40</v>
       </c>
       <c r="H642" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I642" s="1" t="s">
         <v>10</v>
@@ -18782,7 +18782,7 @@
         <v>70</v>
       </c>
       <c r="H643" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I643" s="1" t="s">
         <v>10</v>
@@ -18811,7 +18811,7 @@
         <v>41</v>
       </c>
       <c r="H644" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I644" s="1" t="s">
         <v>13</v>
@@ -18840,7 +18840,7 @@
         <v>43</v>
       </c>
       <c r="H645" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I645" s="1" t="s">
         <v>13</v>
@@ -18872,7 +18872,7 @@
         <v>45</v>
       </c>
       <c r="H646" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I646" s="1" t="s">
         <v>13</v>
@@ -18904,7 +18904,7 @@
         <v>45</v>
       </c>
       <c r="H647" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I647" s="1" t="s">
         <v>13</v>
@@ -18933,7 +18933,7 @@
         <v>48</v>
       </c>
       <c r="H648" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I648" s="1" t="s">
         <v>13</v>
@@ -18962,7 +18962,7 @@
         <v>49</v>
       </c>
       <c r="H649" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I649" s="1" t="s">
         <v>10</v>
@@ -18991,7 +18991,7 @@
         <v>50</v>
       </c>
       <c r="H650" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I650" s="1" t="s">
         <v>10</v>
@@ -19020,7 +19020,7 @@
         <v>52</v>
       </c>
       <c r="H651" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I651" s="1" t="s">
         <v>13</v>
@@ -19049,7 +19049,7 @@
         <v>71</v>
       </c>
       <c r="H652" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I652" s="1" t="s">
         <v>13</v>
@@ -19078,7 +19078,7 @@
         <v>72</v>
       </c>
       <c r="H653" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I653" s="1" t="s">
         <v>13</v>
@@ -19110,7 +19110,7 @@
         <v>45</v>
       </c>
       <c r="H654" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I654" s="1" t="s">
         <v>13</v>
@@ -19139,7 +19139,7 @@
         <v>73</v>
       </c>
       <c r="H655" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I655" s="1" t="s">
         <v>13</v>
@@ -19168,7 +19168,7 @@
         <v>74</v>
       </c>
       <c r="H656" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I656" s="1" t="s">
         <v>13</v>
@@ -19197,7 +19197,7 @@
         <v>75</v>
       </c>
       <c r="H657" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I657" s="1" t="s">
         <v>13</v>
@@ -19226,7 +19226,7 @@
         <v>67</v>
       </c>
       <c r="H658" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I658" s="1" t="s">
         <v>12</v>
@@ -19250,7 +19250,7 @@
       <c r="J659" s="2"/>
       <c r="K659" s="1"/>
       <c r="M659" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="660" spans="4:13" x14ac:dyDescent="0.3">
@@ -19264,7 +19264,7 @@
         <v>67</v>
       </c>
       <c r="H660" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I660" s="1" t="s">
         <v>10</v>
@@ -19293,7 +19293,7 @@
         <v>76</v>
       </c>
       <c r="H661" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I661" s="1" t="s">
         <v>14</v>
@@ -19317,7 +19317,7 @@
       <c r="J662" s="2"/>
       <c r="K662" s="1"/>
       <c r="M662" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="663" spans="4:13" x14ac:dyDescent="0.3">
@@ -19331,7 +19331,7 @@
         <v>58</v>
       </c>
       <c r="H663" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I663" s="1" t="s">
         <v>13</v>
@@ -19360,7 +19360,7 @@
         <v>77</v>
       </c>
       <c r="H664" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I664" s="1" t="s">
         <v>13</v>
@@ -19389,7 +19389,7 @@
         <v>60</v>
       </c>
       <c r="H665" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I665" s="1" t="s">
         <v>13</v>
@@ -19421,7 +19421,7 @@
         <v>45</v>
       </c>
       <c r="H666" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I666" s="1" t="s">
         <v>13</v>
@@ -19450,7 +19450,7 @@
         <v>62</v>
       </c>
       <c r="H667" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="I667" s="1" t="s">
         <v>13</v>
@@ -19479,7 +19479,7 @@
         <v>68</v>
       </c>
       <c r="H668" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I668" s="1" t="s">
         <v>13</v>
@@ -19508,7 +19508,7 @@
         <v>66</v>
       </c>
       <c r="H669" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I669" s="1" t="s">
         <v>13</v>
@@ -19537,7 +19537,7 @@
         <v>69</v>
       </c>
       <c r="H670" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I670" s="1" t="s">
         <v>10</v>
@@ -19566,7 +19566,7 @@
         <v>64</v>
       </c>
       <c r="H671" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I671" s="1" t="s">
         <v>10</v>
@@ -19595,7 +19595,7 @@
         <v>40</v>
       </c>
       <c r="H672" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I672" s="1" t="s">
         <v>10</v>
@@ -19624,7 +19624,7 @@
         <v>70</v>
       </c>
       <c r="H673" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I673" s="1" t="s">
         <v>12</v>
@@ -19648,7 +19648,7 @@
       <c r="J674" s="2"/>
       <c r="K674" s="1"/>
       <c r="M674" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="675" spans="4:13" x14ac:dyDescent="0.3">
@@ -19662,7 +19662,7 @@
         <v>41</v>
       </c>
       <c r="H675" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I675" s="1" t="s">
         <v>13</v>
@@ -19691,7 +19691,7 @@
         <v>43</v>
       </c>
       <c r="H676" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I676" s="1" t="s">
         <v>13</v>
@@ -19723,7 +19723,7 @@
         <v>45</v>
       </c>
       <c r="H677" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I677" s="1" t="s">
         <v>13</v>
@@ -19755,7 +19755,7 @@
         <v>45</v>
       </c>
       <c r="H678" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I678" s="1" t="s">
         <v>14</v>
@@ -19779,7 +19779,7 @@
       <c r="J679" s="2"/>
       <c r="K679" s="1"/>
       <c r="M679" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="680" spans="4:13" x14ac:dyDescent="0.3">
@@ -19793,7 +19793,7 @@
         <v>48</v>
       </c>
       <c r="H680" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I680" s="1" t="s">
         <v>13</v>
@@ -19822,7 +19822,7 @@
         <v>49</v>
       </c>
       <c r="H681" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I681" s="1" t="s">
         <v>10</v>
@@ -19851,7 +19851,7 @@
         <v>50</v>
       </c>
       <c r="H682" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I682" s="1" t="s">
         <v>10</v>
@@ -19880,7 +19880,7 @@
         <v>52</v>
       </c>
       <c r="H683" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I683" s="1" t="s">
         <v>13</v>
@@ -19909,7 +19909,7 @@
         <v>71</v>
       </c>
       <c r="H684" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I684" s="1" t="s">
         <v>13</v>
@@ -19938,7 +19938,7 @@
         <v>72</v>
       </c>
       <c r="H685" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I685" s="1" t="s">
         <v>13</v>
@@ -19970,7 +19970,7 @@
         <v>45</v>
       </c>
       <c r="H686" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I686" s="1" t="s">
         <v>13</v>
@@ -19999,7 +19999,7 @@
         <v>73</v>
       </c>
       <c r="H687" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I687" s="1" t="s">
         <v>13</v>
@@ -20028,7 +20028,7 @@
         <v>74</v>
       </c>
       <c r="H688" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I688" s="1" t="s">
         <v>13</v>
@@ -20057,7 +20057,7 @@
         <v>75</v>
       </c>
       <c r="H689" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I689" s="1" t="s">
         <v>13</v>
@@ -20086,7 +20086,7 @@
         <v>67</v>
       </c>
       <c r="H690" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I690" s="1" t="s">
         <v>10</v>
@@ -20115,7 +20115,7 @@
         <v>67</v>
       </c>
       <c r="H691" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I691" s="1" t="s">
         <v>10</v>
@@ -20144,7 +20144,7 @@
         <v>76</v>
       </c>
       <c r="H692" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I692" s="1" t="s">
         <v>13</v>
@@ -20173,7 +20173,7 @@
         <v>58</v>
       </c>
       <c r="H693" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I693" s="1" t="s">
         <v>13</v>
@@ -20202,7 +20202,7 @@
         <v>77</v>
       </c>
       <c r="H694" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I694" s="1" t="s">
         <v>13</v>
@@ -20231,7 +20231,7 @@
         <v>60</v>
       </c>
       <c r="H695" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I695" s="1" t="s">
         <v>13</v>
@@ -20263,7 +20263,7 @@
         <v>45</v>
       </c>
       <c r="H696" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I696" s="1" t="s">
         <v>13</v>
@@ -20292,7 +20292,7 @@
         <v>62</v>
       </c>
       <c r="H697" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I697" s="1" t="s">
         <v>13</v>
@@ -20321,7 +20321,7 @@
         <v>68</v>
       </c>
       <c r="H698" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I698" s="1" t="s">
         <v>13</v>
@@ -20350,7 +20350,7 @@
         <v>66</v>
       </c>
       <c r="H699" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I699" s="1" t="s">
         <v>13</v>
@@ -20379,7 +20379,7 @@
         <v>69</v>
       </c>
       <c r="H700" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I700" s="1" t="s">
         <v>10</v>
@@ -20408,7 +20408,7 @@
         <v>64</v>
       </c>
       <c r="H701" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I701" s="1" t="s">
         <v>13</v>
@@ -20437,7 +20437,7 @@
         <v>40</v>
       </c>
       <c r="H702" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I702" s="1" t="s">
         <v>10</v>
@@ -20466,7 +20466,7 @@
         <v>70</v>
       </c>
       <c r="H703" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I703" s="1" t="s">
         <v>10</v>
@@ -20495,7 +20495,7 @@
         <v>41</v>
       </c>
       <c r="H704" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I704" s="1" t="s">
         <v>13</v>
@@ -20524,7 +20524,7 @@
         <v>43</v>
       </c>
       <c r="H705" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I705" s="1" t="s">
         <v>13</v>
@@ -20556,7 +20556,7 @@
         <v>45</v>
       </c>
       <c r="H706" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I706" s="1" t="s">
         <v>13</v>
@@ -20588,7 +20588,7 @@
         <v>45</v>
       </c>
       <c r="H707" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I707" s="1" t="s">
         <v>13</v>
@@ -20617,7 +20617,7 @@
         <v>48</v>
       </c>
       <c r="H708" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I708" s="1" t="s">
         <v>13</v>
@@ -20646,7 +20646,7 @@
         <v>49</v>
       </c>
       <c r="H709" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I709" s="1" t="s">
         <v>13</v>
@@ -20675,7 +20675,7 @@
         <v>50</v>
       </c>
       <c r="H710" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I710" s="1" t="s">
         <v>12</v>
@@ -20699,7 +20699,7 @@
       <c r="J711" s="2"/>
       <c r="K711" s="1"/>
       <c r="M711" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="712" spans="4:13" x14ac:dyDescent="0.3">
@@ -20713,7 +20713,7 @@
         <v>52</v>
       </c>
       <c r="H712" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I712" s="1" t="s">
         <v>13</v>
@@ -20742,7 +20742,7 @@
         <v>71</v>
       </c>
       <c r="H713" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I713" s="1" t="s">
         <v>13</v>
@@ -20771,7 +20771,7 @@
         <v>72</v>
       </c>
       <c r="H714" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I714" s="1" t="s">
         <v>13</v>
@@ -20803,7 +20803,7 @@
         <v>45</v>
       </c>
       <c r="H715" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I715" s="1" t="s">
         <v>13</v>
@@ -20832,7 +20832,7 @@
         <v>73</v>
       </c>
       <c r="H716" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I716" s="1" t="s">
         <v>13</v>
@@ -20861,7 +20861,7 @@
         <v>74</v>
       </c>
       <c r="H717" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I717" s="1" t="s">
         <v>13</v>
@@ -20890,7 +20890,7 @@
         <v>75</v>
       </c>
       <c r="H718" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I718" s="1" t="s">
         <v>13</v>
@@ -20919,7 +20919,7 @@
         <v>67</v>
       </c>
       <c r="H719" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I719" s="1" t="s">
         <v>13</v>
@@ -20948,7 +20948,7 @@
         <v>67</v>
       </c>
       <c r="H720" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I720" s="1" t="s">
         <v>10</v>
@@ -20977,7 +20977,7 @@
         <v>76</v>
       </c>
       <c r="H721" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I721" s="1" t="s">
         <v>13</v>
@@ -21006,7 +21006,7 @@
         <v>58</v>
       </c>
       <c r="H722" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I722" s="1" t="s">
         <v>13</v>
@@ -21035,7 +21035,7 @@
         <v>77</v>
       </c>
       <c r="H723" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I723" s="1" t="s">
         <v>13</v>
@@ -21064,7 +21064,7 @@
         <v>60</v>
       </c>
       <c r="H724" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I724" s="1" t="s">
         <v>13</v>
@@ -21096,7 +21096,7 @@
         <v>45</v>
       </c>
       <c r="H725" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I725" s="1" t="s">
         <v>13</v>
@@ -21125,7 +21125,7 @@
         <v>62</v>
       </c>
       <c r="H726" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="I726" s="1" t="s">
         <v>13</v>
@@ -21144,251 +21144,911 @@
       </c>
     </row>
     <row r="727" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H727" s="2"/>
-      <c r="I727" s="1"/>
-      <c r="J727" s="2"/>
-      <c r="K727" s="1"/>
+      <c r="D727" t="s">
+        <v>38</v>
+      </c>
+      <c r="E727">
+        <v>3305</v>
+      </c>
+      <c r="F727" t="s">
+        <v>68</v>
+      </c>
+      <c r="H727" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I727" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J727" s="2">
+        <v>0</v>
+      </c>
+      <c r="K727" s="1">
+        <v>46212.758680555555</v>
+      </c>
+      <c r="L727">
+        <v>0</v>
+      </c>
+      <c r="M727" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="728" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H728" s="2"/>
-      <c r="I728" s="1"/>
-      <c r="J728" s="2"/>
-      <c r="K728" s="1"/>
+      <c r="D728" t="s">
+        <v>38</v>
+      </c>
+      <c r="E728">
+        <v>2250</v>
+      </c>
+      <c r="F728" t="s">
+        <v>66</v>
+      </c>
+      <c r="H728" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I728" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J728" s="2">
+        <v>0</v>
+      </c>
+      <c r="K728" s="1">
+        <v>46212.759375000001</v>
+      </c>
+      <c r="L728">
+        <v>0</v>
+      </c>
+      <c r="M728" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="729" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H729" s="2"/>
-      <c r="I729" s="1"/>
-      <c r="J729" s="2"/>
-      <c r="K729" s="1"/>
+      <c r="D729" t="s">
+        <v>38</v>
+      </c>
+      <c r="E729">
+        <v>3300</v>
+      </c>
+      <c r="F729" t="s">
+        <v>69</v>
+      </c>
+      <c r="H729" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I729" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J729" s="2">
+        <v>0</v>
+      </c>
+      <c r="K729" s="1">
+        <v>46212.760069444441</v>
+      </c>
+      <c r="L729">
+        <v>0</v>
+      </c>
+      <c r="M729" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="730" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H730" s="2"/>
-      <c r="I730" s="1"/>
-      <c r="J730" s="2"/>
-      <c r="K730" s="1"/>
+      <c r="D730" t="s">
+        <v>38</v>
+      </c>
+      <c r="E730">
+        <v>1979</v>
+      </c>
+      <c r="F730" t="s">
+        <v>64</v>
+      </c>
+      <c r="H730" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I730" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J730" s="2">
+        <v>0</v>
+      </c>
+      <c r="K730" s="1">
+        <v>46212.760763888888</v>
+      </c>
+      <c r="L730">
+        <v>0</v>
+      </c>
+      <c r="M730" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="731" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H731" s="2"/>
-      <c r="I731" s="1"/>
-      <c r="J731" s="2"/>
-      <c r="K731" s="1"/>
+      <c r="D731" t="s">
+        <v>38</v>
+      </c>
+      <c r="E731">
+        <v>1006</v>
+      </c>
+      <c r="F731" t="s">
+        <v>40</v>
+      </c>
+      <c r="H731" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I731" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J731" s="2">
+        <v>7.1643518518518514E-3</v>
+      </c>
+      <c r="K731" s="1">
+        <v>46212.761458333334</v>
+      </c>
+      <c r="L731">
+        <v>0</v>
+      </c>
+      <c r="M731" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="732" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H732" s="2"/>
-      <c r="I732" s="1"/>
-      <c r="J732" s="2"/>
-      <c r="K732" s="1"/>
+      <c r="D732" t="s">
+        <v>38</v>
+      </c>
+      <c r="E732">
+        <v>3303</v>
+      </c>
+      <c r="F732" t="s">
+        <v>70</v>
+      </c>
+      <c r="H732" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I732" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J732" s="2">
+        <v>7.6273148148148151E-3</v>
+      </c>
+      <c r="K732" s="1">
+        <v>46212.761458333334</v>
+      </c>
+      <c r="L732">
+        <v>0</v>
+      </c>
+      <c r="M732" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="733" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H733" s="2"/>
-      <c r="I733" s="1"/>
-      <c r="J733" s="2"/>
-      <c r="K733" s="1"/>
+      <c r="D733" t="s">
+        <v>38</v>
+      </c>
+      <c r="E733">
+        <v>1004</v>
+      </c>
+      <c r="F733" t="s">
+        <v>41</v>
+      </c>
+      <c r="H733" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I733" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J733" s="2">
+        <v>0</v>
+      </c>
+      <c r="K733" s="1">
+        <v>46212.762152777781</v>
+      </c>
+      <c r="L733">
+        <v>0</v>
+      </c>
+      <c r="M733" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="734" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H734" s="2"/>
-      <c r="I734" s="1"/>
-      <c r="J734" s="2"/>
-      <c r="K734" s="1"/>
+      <c r="D734" t="s">
+        <v>38</v>
+      </c>
+      <c r="E734">
+        <v>1002</v>
+      </c>
+      <c r="F734" t="s">
+        <v>43</v>
+      </c>
+      <c r="H734" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I734" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J734" s="2">
+        <v>0</v>
+      </c>
+      <c r="K734" s="1">
+        <v>46212.76284722222</v>
+      </c>
+      <c r="L734">
+        <v>0</v>
+      </c>
+      <c r="M734" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="735" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H735" s="2"/>
-      <c r="I735" s="1"/>
-      <c r="J735" s="2"/>
-      <c r="K735" s="1"/>
+      <c r="D735" t="s">
+        <v>38</v>
+      </c>
+      <c r="E735">
+        <v>993</v>
+      </c>
+      <c r="F735" t="s">
+        <v>44</v>
+      </c>
+      <c r="G735" t="s">
+        <v>45</v>
+      </c>
+      <c r="H735" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I735" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J735" s="2">
+        <v>0</v>
+      </c>
+      <c r="K735" s="1">
+        <v>46212.763541666667</v>
+      </c>
+      <c r="L735">
+        <v>0</v>
+      </c>
+      <c r="M735" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="736" spans="4:13" x14ac:dyDescent="0.3">
-      <c r="H736" s="2"/>
-      <c r="I736" s="1"/>
-      <c r="J736" s="2"/>
-      <c r="K736" s="1"/>
-    </row>
-    <row r="737" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H737" s="2"/>
-      <c r="I737" s="1"/>
-      <c r="J737" s="2"/>
-      <c r="K737" s="1"/>
-    </row>
-    <row r="738" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H738" s="2"/>
-      <c r="I738" s="1"/>
-      <c r="J738" s="2"/>
-      <c r="K738" s="1"/>
-    </row>
-    <row r="739" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H739" s="2"/>
-      <c r="I739" s="1"/>
-      <c r="J739" s="2"/>
-      <c r="K739" s="1"/>
-    </row>
-    <row r="740" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H740" s="2"/>
-      <c r="I740" s="1"/>
-      <c r="J740" s="2"/>
-      <c r="K740" s="1"/>
-    </row>
-    <row r="741" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H741" s="2"/>
-      <c r="I741" s="1"/>
-      <c r="J741" s="2"/>
-      <c r="K741" s="1"/>
-    </row>
-    <row r="742" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="D736" t="s">
+        <v>38</v>
+      </c>
+      <c r="E736">
+        <v>992</v>
+      </c>
+      <c r="F736" t="s">
+        <v>46</v>
+      </c>
+      <c r="G736" t="s">
+        <v>45</v>
+      </c>
+      <c r="H736" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I736" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J736" s="2">
+        <v>0</v>
+      </c>
+      <c r="K736" s="1">
+        <v>46212.764236111114</v>
+      </c>
+      <c r="L736">
+        <v>0</v>
+      </c>
+      <c r="M736" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="737" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D737" t="s">
+        <v>38</v>
+      </c>
+      <c r="E737">
+        <v>995</v>
+      </c>
+      <c r="F737" t="s">
+        <v>48</v>
+      </c>
+      <c r="H737" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I737" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J737" s="2">
+        <v>0</v>
+      </c>
+      <c r="K737" s="1">
+        <v>46212.764236111114</v>
+      </c>
+      <c r="L737">
+        <v>0</v>
+      </c>
+      <c r="M737" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="738" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D738" t="s">
+        <v>38</v>
+      </c>
+      <c r="E738">
+        <v>1008</v>
+      </c>
+      <c r="F738" t="s">
+        <v>49</v>
+      </c>
+      <c r="H738" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I738" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J738" s="2">
+        <v>0</v>
+      </c>
+      <c r="K738" s="1">
+        <v>46212.764930555553</v>
+      </c>
+      <c r="L738">
+        <v>0</v>
+      </c>
+      <c r="M738" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="739" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D739" t="s">
+        <v>38</v>
+      </c>
+      <c r="E739">
+        <v>1007</v>
+      </c>
+      <c r="F739" t="s">
+        <v>50</v>
+      </c>
+      <c r="H739" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I739" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J739" s="2">
+        <v>0</v>
+      </c>
+      <c r="K739" s="1">
+        <v>46212.765625</v>
+      </c>
+      <c r="L739">
+        <v>0</v>
+      </c>
+      <c r="M739" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="740" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D740" t="s">
+        <v>38</v>
+      </c>
+      <c r="E740">
+        <v>1005</v>
+      </c>
+      <c r="F740" t="s">
+        <v>52</v>
+      </c>
+      <c r="H740" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I740" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J740" s="2">
+        <v>0</v>
+      </c>
+      <c r="K740" s="1">
+        <v>46212.766319444447</v>
+      </c>
+      <c r="L740">
+        <v>0</v>
+      </c>
+      <c r="M740" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="741" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D741" t="s">
+        <v>38</v>
+      </c>
+      <c r="E741">
+        <v>3301</v>
+      </c>
+      <c r="F741" t="s">
+        <v>71</v>
+      </c>
+      <c r="H741" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I741" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J741" s="2">
+        <v>0</v>
+      </c>
+      <c r="K741" s="1">
+        <v>46212.767013888886</v>
+      </c>
+      <c r="L741">
+        <v>0</v>
+      </c>
+      <c r="M741" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="742" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H742" s="2"/>
       <c r="I742" s="1"/>
       <c r="J742" s="2"/>
       <c r="K742" s="1"/>
-    </row>
-    <row r="743" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H743" s="2"/>
-      <c r="I743" s="1"/>
-      <c r="J743" s="2"/>
-      <c r="K743" s="1"/>
-    </row>
-    <row r="744" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H744" s="2"/>
-      <c r="I744" s="1"/>
-      <c r="J744" s="2"/>
-      <c r="K744" s="1"/>
-    </row>
-    <row r="745" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H745" s="2"/>
-      <c r="I745" s="1"/>
-      <c r="J745" s="2"/>
-      <c r="K745" s="1"/>
-    </row>
-    <row r="746" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="I746" s="1"/>
-      <c r="J746" s="2"/>
-      <c r="K746" s="1"/>
-    </row>
-    <row r="747" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H747" s="2"/>
-      <c r="I747" s="1"/>
-      <c r="J747" s="2"/>
-      <c r="K747" s="1"/>
-    </row>
-    <row r="748" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H748" s="2"/>
-      <c r="I748" s="1"/>
-      <c r="J748" s="2"/>
-      <c r="K748" s="1"/>
-    </row>
-    <row r="749" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H749" s="2"/>
-      <c r="I749" s="1"/>
-      <c r="J749" s="2"/>
-      <c r="K749" s="1"/>
-    </row>
-    <row r="750" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H750" s="2"/>
-      <c r="I750" s="1"/>
-      <c r="J750" s="2"/>
-      <c r="K750" s="1"/>
-    </row>
-    <row r="751" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H751" s="2"/>
-      <c r="I751" s="1"/>
-      <c r="J751" s="2"/>
-      <c r="K751" s="1"/>
-    </row>
-    <row r="752" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H752" s="2"/>
-      <c r="I752" s="1"/>
-      <c r="J752" s="2"/>
-      <c r="K752" s="1"/>
-    </row>
-    <row r="753" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H753" s="2"/>
-      <c r="I753" s="1"/>
-      <c r="J753" s="2"/>
-      <c r="K753" s="1"/>
-    </row>
-    <row r="754" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H754" s="2"/>
-      <c r="I754" s="1"/>
-      <c r="J754" s="2"/>
-      <c r="K754" s="1"/>
-    </row>
-    <row r="755" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H755" s="2"/>
-      <c r="I755" s="1"/>
-      <c r="J755" s="2"/>
-      <c r="K755" s="1"/>
-    </row>
-    <row r="756" spans="8:11" x14ac:dyDescent="0.3">
+      <c r="M742" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="743" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D743" t="s">
+        <v>38</v>
+      </c>
+      <c r="E743">
+        <v>3304</v>
+      </c>
+      <c r="F743" t="s">
+        <v>72</v>
+      </c>
+      <c r="H743" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I743" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J743" s="2">
+        <v>0</v>
+      </c>
+      <c r="K743" s="1">
+        <v>46212.767013888886</v>
+      </c>
+      <c r="L743">
+        <v>0</v>
+      </c>
+      <c r="M743" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="744" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D744" t="s">
+        <v>38</v>
+      </c>
+      <c r="E744">
+        <v>991</v>
+      </c>
+      <c r="F744" t="s">
+        <v>56</v>
+      </c>
+      <c r="G744" t="s">
+        <v>45</v>
+      </c>
+      <c r="H744" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I744" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J744" s="2">
+        <v>0</v>
+      </c>
+      <c r="K744" s="1">
+        <v>46212.767708333333</v>
+      </c>
+      <c r="L744">
+        <v>0</v>
+      </c>
+      <c r="M744" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="745" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D745" t="s">
+        <v>38</v>
+      </c>
+      <c r="E745">
+        <v>3307</v>
+      </c>
+      <c r="F745" t="s">
+        <v>73</v>
+      </c>
+      <c r="H745" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I745" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J745" s="2">
+        <v>0</v>
+      </c>
+      <c r="K745" s="1">
+        <v>46212.76840277778</v>
+      </c>
+      <c r="L745">
+        <v>0</v>
+      </c>
+      <c r="M745" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="746" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D746" t="s">
+        <v>38</v>
+      </c>
+      <c r="E746">
+        <v>3306</v>
+      </c>
+      <c r="F746" t="s">
+        <v>74</v>
+      </c>
+      <c r="H746" t="s">
+        <v>20</v>
+      </c>
+      <c r="I746" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J746" s="2">
+        <v>0</v>
+      </c>
+      <c r="K746" s="1">
+        <v>46212.769097222219</v>
+      </c>
+      <c r="L746">
+        <v>0</v>
+      </c>
+      <c r="M746" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="747" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D747" t="s">
+        <v>38</v>
+      </c>
+      <c r="E747">
+        <v>3308</v>
+      </c>
+      <c r="F747" t="s">
+        <v>75</v>
+      </c>
+      <c r="H747" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I747" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J747" s="2">
+        <v>0</v>
+      </c>
+      <c r="K747" s="1">
+        <v>46212.769097222219</v>
+      </c>
+      <c r="L747">
+        <v>0</v>
+      </c>
+      <c r="M747" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="748" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D748" t="s">
+        <v>38</v>
+      </c>
+      <c r="E748">
+        <v>2238</v>
+      </c>
+      <c r="F748" t="s">
+        <v>67</v>
+      </c>
+      <c r="H748" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I748" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J748" s="2">
+        <v>0</v>
+      </c>
+      <c r="K748" s="1">
+        <v>46212.769791666666</v>
+      </c>
+      <c r="L748">
+        <v>0</v>
+      </c>
+      <c r="M748" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="749" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D749" t="s">
+        <v>38</v>
+      </c>
+      <c r="E749">
+        <v>3299</v>
+      </c>
+      <c r="F749" t="s">
+        <v>67</v>
+      </c>
+      <c r="H749" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I749" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J749" s="2">
+        <v>0</v>
+      </c>
+      <c r="K749" s="1">
+        <v>46212.770486111112</v>
+      </c>
+      <c r="L749">
+        <v>0</v>
+      </c>
+      <c r="M749" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="750" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D750" t="s">
+        <v>38</v>
+      </c>
+      <c r="E750">
+        <v>3302</v>
+      </c>
+      <c r="F750" t="s">
+        <v>76</v>
+      </c>
+      <c r="H750" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I750" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J750" s="2">
+        <v>0</v>
+      </c>
+      <c r="K750" s="1">
+        <v>46212.771180555559</v>
+      </c>
+      <c r="L750">
+        <v>0</v>
+      </c>
+      <c r="M750" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="751" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D751" t="s">
+        <v>38</v>
+      </c>
+      <c r="E751">
+        <v>1001</v>
+      </c>
+      <c r="F751" t="s">
+        <v>58</v>
+      </c>
+      <c r="H751" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I751" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J751" s="2">
+        <v>0</v>
+      </c>
+      <c r="K751" s="1">
+        <v>46212.771874999999</v>
+      </c>
+      <c r="L751">
+        <v>0</v>
+      </c>
+      <c r="M751" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="752" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D752" t="s">
+        <v>38</v>
+      </c>
+      <c r="E752">
+        <v>3298</v>
+      </c>
+      <c r="F752" t="s">
+        <v>77</v>
+      </c>
+      <c r="H752" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I752" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J752" s="2">
+        <v>0</v>
+      </c>
+      <c r="K752" s="1">
+        <v>46212.772569444445</v>
+      </c>
+      <c r="L752">
+        <v>0</v>
+      </c>
+      <c r="M752" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="753" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D753" t="s">
+        <v>38</v>
+      </c>
+      <c r="E753">
+        <v>996</v>
+      </c>
+      <c r="F753" t="s">
+        <v>60</v>
+      </c>
+      <c r="H753" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I753" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J753" s="2">
+        <v>0</v>
+      </c>
+      <c r="K753" s="1">
+        <v>46212.772569444445</v>
+      </c>
+      <c r="L753">
+        <v>0</v>
+      </c>
+      <c r="M753" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="754" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D754" t="s">
+        <v>38</v>
+      </c>
+      <c r="E754">
+        <v>990</v>
+      </c>
+      <c r="F754" t="s">
+        <v>61</v>
+      </c>
+      <c r="G754" t="s">
+        <v>45</v>
+      </c>
+      <c r="H754" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I754" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J754" s="2">
+        <v>0</v>
+      </c>
+      <c r="K754" s="1">
+        <v>46212.773263888892</v>
+      </c>
+      <c r="L754">
+        <v>0</v>
+      </c>
+      <c r="M754" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="755" spans="4:13" x14ac:dyDescent="0.3">
+      <c r="D755" t="s">
+        <v>38</v>
+      </c>
+      <c r="E755">
+        <v>1003</v>
+      </c>
+      <c r="F755" t="s">
+        <v>62</v>
+      </c>
+      <c r="H755" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I755" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J755" s="2">
+        <v>0</v>
+      </c>
+      <c r="K755" s="1">
+        <v>46212.773958333331</v>
+      </c>
+      <c r="L755">
+        <v>0</v>
+      </c>
+      <c r="M755" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="756" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H756" s="2"/>
       <c r="I756" s="1"/>
       <c r="J756" s="2"/>
       <c r="K756" s="1"/>
     </row>
-    <row r="757" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="757" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H757" s="2"/>
       <c r="I757" s="1"/>
       <c r="J757" s="2"/>
       <c r="K757" s="1"/>
     </row>
-    <row r="758" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="758" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H758" s="2"/>
       <c r="I758" s="1"/>
       <c r="J758" s="2"/>
       <c r="K758" s="1"/>
     </row>
-    <row r="759" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="759" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H759" s="2"/>
       <c r="I759" s="1"/>
       <c r="J759" s="2"/>
       <c r="K759" s="1"/>
     </row>
-    <row r="760" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="760" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H760" s="2"/>
       <c r="I760" s="1"/>
       <c r="J760" s="2"/>
       <c r="K760" s="1"/>
     </row>
-    <row r="761" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="761" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H761" s="2"/>
       <c r="I761" s="1"/>
       <c r="J761" s="2"/>
       <c r="K761" s="1"/>
     </row>
-    <row r="762" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="762" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H762" s="2"/>
       <c r="I762" s="1"/>
       <c r="J762" s="2"/>
       <c r="K762" s="1"/>
     </row>
-    <row r="763" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="763" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H763" s="2"/>
       <c r="I763" s="1"/>
       <c r="J763" s="2"/>
       <c r="K763" s="1"/>
     </row>
-    <row r="764" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="764" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H764" s="2"/>
       <c r="I764" s="1"/>
       <c r="J764" s="2"/>
       <c r="K764" s="1"/>
     </row>
-    <row r="765" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="765" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H765" s="2"/>
       <c r="I765" s="1"/>
       <c r="J765" s="2"/>
       <c r="K765" s="1"/>
     </row>
-    <row r="766" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="766" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H766" s="2"/>
       <c r="I766" s="1"/>
       <c r="J766" s="2"/>
       <c r="K766" s="1"/>
     </row>
-    <row r="767" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="767" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H767" s="2"/>
       <c r="I767" s="1"/>
       <c r="J767" s="2"/>
       <c r="K767" s="1"/>
     </row>
-    <row r="768" spans="8:11" x14ac:dyDescent="0.3">
+    <row r="768" spans="4:13" x14ac:dyDescent="0.3">
       <c r="H768" s="2"/>
       <c r="I768" s="1"/>
       <c r="J768" s="2"/>
@@ -55266,7 +55926,845 @@
       <c r="J6919" s="2"/>
       <c r="K6919" s="1"/>
     </row>
+    <row r="6920" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6920" s="2"/>
+      <c r="K6920" s="1"/>
+    </row>
+    <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6921" s="1"/>
+    </row>
+    <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6922" s="2"/>
+      <c r="K6922" s="1"/>
+    </row>
+    <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6923" s="1"/>
+    </row>
+    <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6924" s="2"/>
+      <c r="K6924" s="1"/>
+    </row>
+    <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6925" s="1"/>
+    </row>
+    <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6926" s="2"/>
+      <c r="K6926" s="1"/>
+    </row>
+    <row r="6927" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6927" s="2"/>
+      <c r="K6927" s="1"/>
+    </row>
+    <row r="6928" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6928" s="2"/>
+      <c r="K6928" s="1"/>
+    </row>
+    <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6929" s="1"/>
+    </row>
+    <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6930" s="1"/>
+    </row>
+    <row r="6931" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6931" s="1"/>
+    </row>
+    <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6932" s="1"/>
+    </row>
+    <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6933" s="2"/>
+      <c r="K6933" s="1"/>
+    </row>
+    <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6934" s="1"/>
+    </row>
+    <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6936" s="1"/>
+    </row>
+    <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6937" s="2"/>
+      <c r="K6937" s="1"/>
+    </row>
+    <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6938" s="1"/>
+    </row>
+    <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6939" s="1"/>
+    </row>
+    <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6940" s="1"/>
+    </row>
+    <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6941" s="2"/>
+      <c r="K6941" s="1"/>
+    </row>
+    <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6942" s="1"/>
+    </row>
+    <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6943" s="1"/>
+    </row>
+    <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6944" s="1"/>
+    </row>
+    <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6945" s="2"/>
+      <c r="K6945" s="1"/>
+    </row>
+    <row r="6946" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6946" s="2"/>
+      <c r="K6946" s="1"/>
+    </row>
+    <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6947" s="1"/>
+    </row>
+    <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6948" s="1"/>
+    </row>
+    <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6949" s="2"/>
+      <c r="K6949" s="1"/>
+    </row>
+    <row r="6950" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6950" s="1"/>
+    </row>
+    <row r="6951" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6951" s="2"/>
+      <c r="K6951" s="1"/>
+    </row>
+    <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6952" s="1"/>
+    </row>
+    <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6953" s="2"/>
+      <c r="K6953" s="1"/>
+    </row>
+    <row r="6954" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6954" s="2"/>
+      <c r="K6954" s="1"/>
+    </row>
+    <row r="6955" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6955" s="2"/>
+      <c r="K6955" s="1"/>
+    </row>
+    <row r="6956" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6956" s="1"/>
+    </row>
+    <row r="6957" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6957" s="2"/>
+      <c r="K6957" s="1"/>
+    </row>
+    <row r="6958" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6958" s="2"/>
+      <c r="K6958" s="1"/>
+    </row>
+    <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6959" s="1"/>
+    </row>
+    <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6960" s="2"/>
+      <c r="K6960" s="1"/>
+    </row>
+    <row r="6961" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6961" s="2"/>
+      <c r="K6961" s="1"/>
+    </row>
+    <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6963" s="1"/>
+    </row>
+    <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6964" s="2"/>
+      <c r="K6964" s="1"/>
+    </row>
+    <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6965" s="1"/>
+    </row>
+    <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6966" s="2"/>
+      <c r="K6966" s="1"/>
+    </row>
+    <row r="6967" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6967" s="2"/>
+      <c r="K6967" s="1"/>
+    </row>
+    <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6968" s="1"/>
+    </row>
+    <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6969" s="2"/>
+      <c r="K6969" s="1"/>
+    </row>
+    <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6970" s="1"/>
+    </row>
+    <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6971" s="2"/>
+      <c r="K6971" s="1"/>
+    </row>
+    <row r="6972" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6972" s="2"/>
+      <c r="K6972" s="1"/>
+    </row>
+    <row r="6973" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6973" s="1"/>
+    </row>
+    <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6974" s="1"/>
+    </row>
+    <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6975" s="2"/>
+      <c r="K6975" s="1"/>
+    </row>
+    <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6977" s="1"/>
+    </row>
+    <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6978" s="2"/>
+      <c r="K6978" s="1"/>
+    </row>
+    <row r="6979" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6979" s="1"/>
+    </row>
+    <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6980" s="1"/>
+    </row>
+    <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6981" s="1"/>
+    </row>
+    <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6982" s="1"/>
+    </row>
+    <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6983" s="1"/>
+    </row>
+    <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6984" s="2"/>
+      <c r="K6984" s="1"/>
+    </row>
+    <row r="6985" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6985" s="2"/>
+      <c r="K6985" s="1"/>
+    </row>
+    <row r="6986" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6986" s="2"/>
+      <c r="K6986" s="1"/>
+    </row>
+    <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6987" s="1"/>
+    </row>
+    <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6988" s="2"/>
+      <c r="K6988" s="1"/>
+    </row>
+    <row r="6989" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6989" s="2"/>
+      <c r="K6989" s="1"/>
+    </row>
+    <row r="6990" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6990" s="2"/>
+      <c r="K6990" s="1"/>
+    </row>
+    <row r="6991" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6991" s="1"/>
+    </row>
+    <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6992" s="1"/>
+    </row>
+    <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6993" s="2"/>
+      <c r="K6993" s="1"/>
+    </row>
+    <row r="6994" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6994" s="2"/>
+      <c r="K6994" s="1"/>
+    </row>
+    <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6995" s="1"/>
+    </row>
+    <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6996" s="2"/>
+      <c r="K6996" s="1"/>
+    </row>
+    <row r="6997" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6997" s="1"/>
+    </row>
+    <row r="6998" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K6998" s="1"/>
+    </row>
+    <row r="6999" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6999" s="2"/>
+      <c r="K6999" s="1"/>
+    </row>
+    <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7000" s="1"/>
+    </row>
+    <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7001" s="1"/>
+    </row>
+    <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7002" s="1"/>
+    </row>
+    <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7003" s="1"/>
+    </row>
+    <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7004" s="1"/>
+    </row>
+    <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7005" s="2"/>
+      <c r="K7005" s="1"/>
+    </row>
+    <row r="7006" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7006" s="1"/>
+    </row>
+    <row r="7007" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7007" s="2"/>
+      <c r="K7007" s="1"/>
+    </row>
+    <row r="7008" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7008" s="2"/>
+      <c r="K7008" s="1"/>
+    </row>
+    <row r="7009" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7009" s="1"/>
+    </row>
+    <row r="7011" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7011" s="2"/>
+      <c r="K7011" s="1"/>
+    </row>
+    <row r="7012" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7012" s="1"/>
+    </row>
+    <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7014" s="1"/>
+    </row>
+    <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7015" s="2"/>
+      <c r="K7015" s="1"/>
+    </row>
+    <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7016" s="1"/>
+    </row>
+    <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7017" s="1"/>
+    </row>
+    <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7018" s="2"/>
+      <c r="K7018" s="1"/>
+    </row>
+    <row r="7019" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7019" s="2"/>
+      <c r="K7019" s="1"/>
+    </row>
+    <row r="7020" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7020" s="2"/>
+      <c r="K7020" s="1"/>
+    </row>
+    <row r="7021" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7021" s="1"/>
+    </row>
+    <row r="7022" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7022" s="2"/>
+      <c r="K7022" s="1"/>
+    </row>
+    <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7023" s="1"/>
+    </row>
+    <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7024" s="1"/>
+    </row>
+    <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7025" s="1"/>
+    </row>
+    <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7026" s="2"/>
+      <c r="K7026" s="1"/>
+    </row>
+    <row r="7027" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7027" s="2"/>
+      <c r="K7027" s="1"/>
+    </row>
+    <row r="7028" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7028" s="1"/>
+    </row>
+    <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7030" s="1"/>
+    </row>
+    <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7031" s="1"/>
+    </row>
+    <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7032" s="2"/>
+      <c r="K7032" s="1"/>
+    </row>
+    <row r="7033" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7033" s="2"/>
+      <c r="K7033" s="1"/>
+    </row>
+    <row r="7034" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7034" s="2"/>
+      <c r="K7034" s="1"/>
+    </row>
+    <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7035" s="1"/>
+    </row>
+    <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7036" s="1"/>
+    </row>
+    <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7037" s="1"/>
+    </row>
+    <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7038" s="1"/>
+    </row>
+    <row r="7039" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7039" s="1"/>
+    </row>
+    <row r="7040" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7040" s="1"/>
+    </row>
+    <row r="7041" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7041" s="2"/>
+      <c r="K7041" s="1"/>
+    </row>
+    <row r="7042" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7042" s="2"/>
+      <c r="K7042" s="1"/>
+    </row>
+    <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7043" s="1"/>
+    </row>
+    <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7044" s="2"/>
+      <c r="K7044" s="1"/>
+    </row>
+    <row r="7045" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7045" s="2"/>
+      <c r="K7045" s="1"/>
+    </row>
+    <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7046" s="1"/>
+    </row>
+    <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7047" s="1"/>
+    </row>
+    <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7048" s="2"/>
+      <c r="K7048" s="1"/>
+    </row>
+    <row r="7049" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7049" s="2"/>
+      <c r="K7049" s="1"/>
+    </row>
+    <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7050" s="1"/>
+    </row>
+    <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7051" s="2"/>
+      <c r="K7051" s="1"/>
+    </row>
+    <row r="7052" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7052" s="2"/>
+      <c r="K7052" s="1"/>
+    </row>
+    <row r="7053" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7053" s="2"/>
+      <c r="K7053" s="1"/>
+    </row>
+    <row r="7054" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7054" s="2"/>
+      <c r="K7054" s="1"/>
+    </row>
+    <row r="7055" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7055" s="2"/>
+      <c r="K7055" s="1"/>
+    </row>
+    <row r="7056" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7056" s="2"/>
+      <c r="K7056" s="1"/>
+    </row>
+    <row r="7057" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7057" s="2"/>
+      <c r="K7057" s="1"/>
+    </row>
+    <row r="7058" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7058" s="2"/>
+      <c r="K7058" s="1"/>
+    </row>
+    <row r="7059" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7059" s="2"/>
+      <c r="K7059" s="1"/>
+    </row>
+    <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7060" s="1"/>
+    </row>
+    <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7061" s="1"/>
+    </row>
+    <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7062" s="2"/>
+      <c r="K7062" s="1"/>
+    </row>
+    <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7063" s="1"/>
+    </row>
+    <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7064" s="1"/>
+    </row>
+    <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7065" s="1"/>
+    </row>
+    <row r="7066" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7066" s="2"/>
+      <c r="K7066" s="1"/>
+    </row>
+    <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7067" s="1"/>
+    </row>
+    <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7068" s="2"/>
+      <c r="K7068" s="1"/>
+    </row>
+    <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7069" s="1"/>
+    </row>
+    <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7071" s="1"/>
+    </row>
+    <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7072" s="1"/>
+    </row>
+    <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7073" s="1"/>
+    </row>
+    <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7074" s="1"/>
+    </row>
+    <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7075" s="2"/>
+      <c r="K7075" s="1"/>
+    </row>
+    <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7076" s="1"/>
+    </row>
+    <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7077" s="2"/>
+      <c r="K7077" s="1"/>
+    </row>
+    <row r="7078" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7078" s="1"/>
+    </row>
+    <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7079" s="1"/>
+    </row>
+    <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7080" s="2"/>
+      <c r="K7080" s="1"/>
+    </row>
+    <row r="7081" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7081" s="2"/>
+      <c r="K7081" s="1"/>
+    </row>
+    <row r="7082" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7082" s="1"/>
+    </row>
+    <row r="7083" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7083" s="2"/>
+      <c r="K7083" s="1"/>
+    </row>
+    <row r="7084" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7084" s="2"/>
+      <c r="K7084" s="1"/>
+    </row>
+    <row r="7085" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7085" s="2"/>
+      <c r="K7085" s="1"/>
+    </row>
+    <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7086" s="1"/>
+    </row>
+    <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7087" s="1"/>
+    </row>
+    <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7088" s="1"/>
+    </row>
+    <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7089" s="1"/>
+    </row>
+    <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7090" s="1"/>
+    </row>
+    <row r="7091" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7091" s="1"/>
+    </row>
+    <row r="7092" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7092" s="2"/>
+      <c r="K7092" s="1"/>
+    </row>
+    <row r="7093" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7093" s="2"/>
+      <c r="K7093" s="1"/>
+    </row>
+    <row r="7094" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7094" s="2"/>
+      <c r="K7094" s="1"/>
+    </row>
+    <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7095" s="1"/>
+    </row>
+    <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7096" s="2"/>
+      <c r="K7096" s="1"/>
+    </row>
+    <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7097" s="1"/>
+    </row>
+    <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7098" s="1"/>
+    </row>
+    <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7099" s="2"/>
+      <c r="K7099" s="1"/>
+    </row>
+    <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7100" s="1"/>
+    </row>
+    <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7101" s="2"/>
+      <c r="K7101" s="1"/>
+    </row>
+    <row r="7102" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7102" s="2"/>
+      <c r="K7102" s="1"/>
+    </row>
+    <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7103" s="1"/>
+    </row>
+    <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7104" s="2"/>
+      <c r="K7104" s="1"/>
+    </row>
+    <row r="7105" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7105" s="2"/>
+      <c r="K7105" s="1"/>
+    </row>
+    <row r="7106" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7106" s="2"/>
+      <c r="K7106" s="1"/>
+    </row>
+    <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7108" s="2"/>
+      <c r="K7108" s="1"/>
+    </row>
+    <row r="7109" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7109" s="2"/>
+      <c r="K7109" s="1"/>
+    </row>
+    <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7110" s="1"/>
+    </row>
+    <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7111" s="2"/>
+      <c r="K7111" s="1"/>
+    </row>
+    <row r="7112" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7112" s="2"/>
+      <c r="K7112" s="1"/>
+    </row>
+    <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7113" s="1"/>
+    </row>
+    <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7114" s="2"/>
+      <c r="K7114" s="1"/>
+    </row>
+    <row r="7115" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7115" s="2"/>
+      <c r="K7115" s="1"/>
+    </row>
+    <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7117" s="1"/>
+    </row>
+    <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7118" s="1"/>
+    </row>
+    <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7119" s="2"/>
+      <c r="K7119" s="1"/>
+    </row>
+    <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7120" s="1"/>
+    </row>
+    <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7121" s="2"/>
+      <c r="K7121" s="1"/>
+    </row>
+    <row r="7122" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7122" s="2"/>
+      <c r="K7122" s="1"/>
+    </row>
+    <row r="7123" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7123" s="1"/>
+    </row>
+    <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7124" s="1"/>
+    </row>
+    <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7125" s="2"/>
+      <c r="K7125" s="1"/>
+    </row>
+    <row r="7126" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7126" s="2"/>
+      <c r="K7126" s="1"/>
+    </row>
+    <row r="7127" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7127" s="1"/>
+    </row>
+    <row r="7128" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7128" s="2"/>
+      <c r="K7128" s="1"/>
+    </row>
+    <row r="7129" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7129" s="2"/>
+      <c r="K7129" s="1"/>
+    </row>
+    <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7130" s="1"/>
+    </row>
+    <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7131" s="2"/>
+      <c r="K7131" s="1"/>
+    </row>
+    <row r="7132" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7132" s="2"/>
+      <c r="K7132" s="1"/>
+    </row>
+    <row r="7133" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7133" s="2"/>
+      <c r="K7133" s="1"/>
+    </row>
+    <row r="7134" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7134" s="2"/>
+      <c r="K7134" s="1"/>
+    </row>
+    <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7135" s="1"/>
+    </row>
+    <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7136" s="1"/>
+    </row>
+    <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7137" s="1"/>
+    </row>
+    <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7138" s="2"/>
+      <c r="K7138" s="1"/>
+    </row>
+    <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7140" s="1"/>
+    </row>
+    <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7141" s="2"/>
+      <c r="K7141" s="1"/>
+    </row>
+    <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7143" s="1"/>
+    </row>
+    <row r="7144" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7144" s="1"/>
+    </row>
+    <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7145" s="1"/>
+    </row>
+    <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7146" s="2"/>
+      <c r="K7146" s="1"/>
+    </row>
+    <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7147" s="1"/>
+    </row>
+    <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7148" s="1"/>
+    </row>
+    <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7150" s="1"/>
+    </row>
+    <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7151" s="1"/>
+    </row>
+    <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7152" s="2"/>
+      <c r="K7152" s="1"/>
+    </row>
+    <row r="7153" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7153" s="1"/>
+    </row>
+    <row r="7154" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7154" s="1"/>
+    </row>
+    <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7155" s="1"/>
+    </row>
+    <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7156" s="2"/>
+      <c r="K7156" s="1"/>
+    </row>
+    <row r="7157" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7157" s="1"/>
+    </row>
+    <row r="7158" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7158" s="2"/>
+      <c r="K7158" s="1"/>
+    </row>
+    <row r="7159" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7159" s="2"/>
+      <c r="K7159" s="1"/>
+    </row>
+    <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7160" s="1"/>
+    </row>
+    <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7161" s="1"/>
+    </row>
+    <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7162" s="2"/>
+      <c r="K7162" s="1"/>
+    </row>
+    <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7163" s="1"/>
+    </row>
+    <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7164" s="1"/>
+    </row>
+    <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7165" s="2"/>
+      <c r="K7165" s="1"/>
+    </row>
+    <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7166" s="1"/>
+    </row>
+    <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7167" s="1"/>
+    </row>
+    <row r="7168" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7168" s="1"/>
+    </row>
+    <row r="7169" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7169" s="1"/>
+    </row>
+    <row r="7170" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7170" s="2"/>
+      <c r="K7170" s="1"/>
+    </row>
+    <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7171" s="1"/>
+    </row>
+    <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7172" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/training.xlsx
+++ b/training.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\Synergy Safety Group\DEN\Dashboard\Weekly Dashboards\Salt-Creek-Logistics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E68F706-A8CD-4C47-B291-ECAB29266EE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD339A08-C426-47C6-A184-307856CC7C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{5CACA9A1-03A8-4E05-97D6-00ACC1325A4A}"/>
   </bookViews>
@@ -86,7 +86,22 @@
     <t>UNKNOWN</t>
   </si>
   <si>
+    <t>Mark Complete</t>
+  </si>
+  <si>
+    <t>DNU-Driver Health</t>
+  </si>
+  <si>
+    <t>DNU-Scene of an Accident</t>
+  </si>
+  <si>
+    <t>DNU-NEW-Vehicle Inspections</t>
+  </si>
+  <si>
     <t>Vehicle Inspections</t>
+  </si>
+  <si>
+    <t>Work Zone Safety</t>
   </si>
   <si>
     <t>Winter Weather</t>
@@ -101,13 +116,10 @@
     <t>Distracted Driving</t>
   </si>
   <si>
-    <t>Driver Health</t>
+    <t>Micro-Learn Speed</t>
   </si>
   <si>
-    <t>Drowsy Driving</t>
-  </si>
-  <si>
-    <t>Mark Complete</t>
+    <t>Driver Health</t>
   </si>
   <si>
     <t>Fire Extinguisher Training for CDL</t>
@@ -116,28 +128,16 @@
     <t>Alert Driving: Big Three</t>
   </si>
   <si>
+    <t>Safe Lifting for Commercial Drivers</t>
+  </si>
+  <si>
+    <t>Drowsy Driving</t>
+  </si>
+  <si>
     <t>Space Management for Commercial Vehicles</t>
   </si>
   <si>
     <t>Speed Mangement-C</t>
-  </si>
-  <si>
-    <t>DNU-Driver Health</t>
-  </si>
-  <si>
-    <t>DNU-Scene of an Accident</t>
-  </si>
-  <si>
-    <t>DNU-NEW-Vehicle Inspections</t>
-  </si>
-  <si>
-    <t>Work Zone Safety</t>
-  </si>
-  <si>
-    <t>Micro-Learn Speed</t>
-  </si>
-  <si>
-    <t>Safe Lifting for Commercial Drivers</t>
   </si>
   <si>
     <t>Dangers of Aggressive Driving for CMV Drivers</t>
@@ -646,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79F75797-B237-43B3-82D5-68EF721AABF0}">
-  <dimension ref="D1:M7172"/>
+  <dimension ref="D1:M7173"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -704,7 +704,7 @@
         <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>10</v>
@@ -733,7 +733,7 @@
         <v>40</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>10</v>
@@ -762,7 +762,7 @@
         <v>41</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>10</v>
@@ -791,7 +791,7 @@
         <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>10</v>
@@ -820,7 +820,7 @@
         <v>43</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>10</v>
@@ -852,7 +852,7 @@
         <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>10</v>
@@ -884,7 +884,7 @@
         <v>45</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>10</v>
@@ -916,7 +916,7 @@
         <v>45</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>10</v>
@@ -945,7 +945,7 @@
         <v>48</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>10</v>
@@ -974,7 +974,7 @@
         <v>49</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>10</v>
@@ -1003,7 +1003,7 @@
         <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>10</v>
@@ -1035,7 +1035,7 @@
         <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>10</v>
@@ -1064,7 +1064,7 @@
         <v>52</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>10</v>
@@ -1093,7 +1093,7 @@
         <v>53</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>12</v>
@@ -1117,7 +1117,7 @@
       <c r="J16" s="2"/>
       <c r="K16" s="1"/>
       <c r="M16" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="4:13" x14ac:dyDescent="0.3">
@@ -1131,7 +1131,7 @@
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>10</v>
@@ -1160,7 +1160,7 @@
         <v>55</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>10</v>
@@ -1192,7 +1192,7 @@
         <v>45</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>10</v>
@@ -1221,7 +1221,7 @@
         <v>57</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>10</v>
@@ -1250,7 +1250,7 @@
         <v>58</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>10</v>
@@ -1279,7 +1279,7 @@
         <v>59</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>10</v>
@@ -1308,7 +1308,7 @@
         <v>60</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>10</v>
@@ -1340,7 +1340,7 @@
         <v>45</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>10</v>
@@ -1369,7 +1369,7 @@
         <v>62</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       <c r="J38" s="2"/>
       <c r="K38" s="1"/>
       <c r="M38" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="39" spans="4:13" x14ac:dyDescent="0.3">
@@ -1820,7 +1820,7 @@
       <c r="J41" s="2"/>
       <c r="K41" s="1"/>
       <c r="M41" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="4:13" x14ac:dyDescent="0.3">
@@ -1977,7 +1977,7 @@
       <c r="J47" s="2"/>
       <c r="K47" s="1"/>
       <c r="M47" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="4:13" x14ac:dyDescent="0.3">
@@ -2044,7 +2044,7 @@
       <c r="J50" s="2"/>
       <c r="K50" s="1"/>
       <c r="M50" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="4:13" x14ac:dyDescent="0.3">
@@ -2119,7 +2119,7 @@
         <v>39</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>12</v>
@@ -2143,7 +2143,7 @@
       <c r="J54" s="2"/>
       <c r="K54" s="1"/>
       <c r="M54" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="4:13" x14ac:dyDescent="0.3">
@@ -2157,7 +2157,7 @@
         <v>40</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>10</v>
@@ -2186,7 +2186,7 @@
         <v>41</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>10</v>
@@ -2215,7 +2215,7 @@
         <v>42</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>10</v>
@@ -2244,7 +2244,7 @@
         <v>43</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>12</v>
@@ -2268,7 +2268,7 @@
       <c r="J59" s="2"/>
       <c r="K59" s="1"/>
       <c r="M59" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="4:13" x14ac:dyDescent="0.3">
@@ -2285,7 +2285,7 @@
         <v>45</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>13</v>
@@ -2317,7 +2317,7 @@
         <v>45</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>13</v>
@@ -2346,7 +2346,7 @@
         <v>48</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>12</v>
@@ -2370,7 +2370,7 @@
       <c r="J63" s="2"/>
       <c r="K63" s="1"/>
       <c r="M63" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="4:13" x14ac:dyDescent="0.3">
@@ -2384,7 +2384,7 @@
         <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I64" s="1" t="s">
         <v>13</v>
@@ -2413,7 +2413,7 @@
         <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>10</v>
@@ -2445,7 +2445,7 @@
         <v>45</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>12</v>
@@ -2469,7 +2469,7 @@
       <c r="J67" s="2"/>
       <c r="K67" s="1"/>
       <c r="M67" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="4:13" x14ac:dyDescent="0.3">
@@ -2483,7 +2483,7 @@
         <v>52</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I68" s="1" t="s">
         <v>12</v>
@@ -2507,7 +2507,7 @@
       <c r="J69" s="2"/>
       <c r="K69" s="1"/>
       <c r="M69" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="4:13" x14ac:dyDescent="0.3">
@@ -2521,7 +2521,7 @@
         <v>53</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I70" s="1" t="s">
         <v>10</v>
@@ -2550,7 +2550,7 @@
         <v>55</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>12</v>
@@ -2574,7 +2574,7 @@
       <c r="J72" s="2"/>
       <c r="K72" s="1"/>
       <c r="M72" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="4:13" x14ac:dyDescent="0.3">
@@ -2591,7 +2591,7 @@
         <v>45</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>10</v>
@@ -2620,7 +2620,7 @@
         <v>57</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I74" s="1" t="s">
         <v>10</v>
@@ -2649,7 +2649,7 @@
         <v>58</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I75" s="1" t="s">
         <v>13</v>
@@ -2678,7 +2678,7 @@
         <v>59</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I76" s="1" t="s">
         <v>10</v>
@@ -2707,7 +2707,7 @@
         <v>60</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I77" s="1" t="s">
         <v>12</v>
@@ -2731,7 +2731,7 @@
       <c r="J78" s="2"/>
       <c r="K78" s="1"/>
       <c r="M78" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="79" spans="4:13" x14ac:dyDescent="0.3">
@@ -2748,7 +2748,7 @@
         <v>45</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I79" s="1" t="s">
         <v>13</v>
@@ -2777,7 +2777,7 @@
         <v>63</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I80" s="1" t="s">
         <v>13</v>
@@ -2806,7 +2806,7 @@
         <v>62</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I81" s="1" t="s">
         <v>12</v>
@@ -2830,7 +2830,7 @@
       <c r="J82" s="2"/>
       <c r="K82" s="1"/>
       <c r="M82" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="4:13" x14ac:dyDescent="0.3">
@@ -2844,7 +2844,7 @@
         <v>39</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I83" s="1" t="s">
         <v>13</v>
@@ -2873,7 +2873,7 @@
         <v>64</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I84" s="1" t="s">
         <v>10</v>
@@ -2902,7 +2902,7 @@
         <v>40</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>10</v>
@@ -2931,7 +2931,7 @@
         <v>41</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I86" s="1" t="s">
         <v>10</v>
@@ -2960,7 +2960,7 @@
         <v>42</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>10</v>
@@ -2989,7 +2989,7 @@
         <v>43</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I88" s="1" t="s">
         <v>13</v>
@@ -3021,7 +3021,7 @@
         <v>45</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I89" s="1" t="s">
         <v>13</v>
@@ -3053,7 +3053,7 @@
         <v>45</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>13</v>
@@ -3082,7 +3082,7 @@
         <v>48</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I91" s="1" t="s">
         <v>13</v>
@@ -3111,7 +3111,7 @@
         <v>49</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>13</v>
@@ -3140,7 +3140,7 @@
         <v>50</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I93" s="1" t="s">
         <v>10</v>
@@ -3172,7 +3172,7 @@
         <v>45</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I94" s="1" t="s">
         <v>10</v>
@@ -3201,7 +3201,7 @@
         <v>52</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>10</v>
@@ -3230,7 +3230,7 @@
         <v>53</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>12</v>
@@ -3254,7 +3254,7 @@
       <c r="J97" s="2"/>
       <c r="K97" s="1"/>
       <c r="M97" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="4:13" x14ac:dyDescent="0.3">
@@ -3268,7 +3268,7 @@
         <v>65</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>10</v>
@@ -3297,7 +3297,7 @@
         <v>55</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I99" s="1" t="s">
         <v>10</v>
@@ -3329,7 +3329,7 @@
         <v>45</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>10</v>
@@ -3358,7 +3358,7 @@
         <v>57</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I101" s="1" t="s">
         <v>10</v>
@@ -3387,7 +3387,7 @@
         <v>58</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I102" s="1" t="s">
         <v>13</v>
@@ -3416,7 +3416,7 @@
         <v>59</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I103" s="1" t="s">
         <v>13</v>
@@ -3445,7 +3445,7 @@
         <v>60</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>13</v>
@@ -3477,7 +3477,7 @@
         <v>45</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I105" s="1" t="s">
         <v>13</v>
@@ -3506,7 +3506,7 @@
         <v>63</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>13</v>
@@ -3535,7 +3535,7 @@
         <v>62</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>10</v>
@@ -3564,7 +3564,7 @@
         <v>39</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>13</v>
@@ -3593,7 +3593,7 @@
         <v>43</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I109" s="1" t="s">
         <v>10</v>
@@ -3625,7 +3625,7 @@
         <v>45</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>10</v>
@@ -3657,7 +3657,7 @@
         <v>45</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>12</v>
@@ -3681,7 +3681,7 @@
       <c r="J112" s="2"/>
       <c r="K112" s="1"/>
       <c r="M112" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113" spans="4:13" x14ac:dyDescent="0.3">
@@ -3695,7 +3695,7 @@
         <v>48</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>13</v>
@@ -3724,7 +3724,7 @@
         <v>49</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>13</v>
@@ -3753,7 +3753,7 @@
         <v>53</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>13</v>
@@ -3782,7 +3782,7 @@
         <v>58</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>10</v>
@@ -3811,7 +3811,7 @@
         <v>59</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>10</v>
@@ -3840,7 +3840,7 @@
         <v>60</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>10</v>
@@ -3872,7 +3872,7 @@
         <v>45</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>13</v>
@@ -3901,7 +3901,7 @@
         <v>63</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>13</v>
@@ -3930,7 +3930,7 @@
         <v>66</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>10</v>
@@ -3959,7 +3959,7 @@
         <v>64</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>10</v>
@@ -3988,7 +3988,7 @@
         <v>40</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>10</v>
@@ -4017,7 +4017,7 @@
         <v>41</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I124" s="1" t="s">
         <v>10</v>
@@ -4046,7 +4046,7 @@
         <v>42</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I125" s="1" t="s">
         <v>10</v>
@@ -4075,7 +4075,7 @@
         <v>43</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I126" s="1" t="s">
         <v>10</v>
@@ -4107,7 +4107,7 @@
         <v>45</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>13</v>
@@ -4139,7 +4139,7 @@
         <v>45</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>13</v>
@@ -4168,7 +4168,7 @@
         <v>48</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>13</v>
@@ -4197,7 +4197,7 @@
         <v>49</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I130" s="1" t="s">
         <v>13</v>
@@ -4226,7 +4226,7 @@
         <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>10</v>
@@ -4258,7 +4258,7 @@
         <v>45</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>10</v>
@@ -4287,7 +4287,7 @@
         <v>52</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>10</v>
@@ -4316,7 +4316,7 @@
         <v>53</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>13</v>
@@ -4345,7 +4345,7 @@
         <v>65</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>10</v>
@@ -4374,7 +4374,7 @@
         <v>55</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I136" s="1" t="s">
         <v>10</v>
@@ -4406,7 +4406,7 @@
         <v>45</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>10</v>
@@ -4435,7 +4435,7 @@
         <v>67</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>10</v>
@@ -4464,7 +4464,7 @@
         <v>57</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>10</v>
@@ -4493,7 +4493,7 @@
         <v>58</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>13</v>
@@ -4522,7 +4522,7 @@
         <v>59</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>10</v>
@@ -4551,7 +4551,7 @@
         <v>60</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>10</v>
@@ -4583,7 +4583,7 @@
         <v>45</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>13</v>
@@ -4612,7 +4612,7 @@
         <v>63</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>12</v>
@@ -4636,7 +4636,7 @@
       <c r="J145" s="2"/>
       <c r="K145" s="1"/>
       <c r="M145" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146" spans="4:13" x14ac:dyDescent="0.3">
@@ -4650,7 +4650,7 @@
         <v>62</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>10</v>
@@ -4679,7 +4679,7 @@
         <v>66</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>10</v>
@@ -4708,7 +4708,7 @@
         <v>64</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>10</v>
@@ -4737,7 +4737,7 @@
         <v>40</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>10</v>
@@ -4766,7 +4766,7 @@
         <v>41</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I150" s="1" t="s">
         <v>12</v>
@@ -4790,7 +4790,7 @@
       <c r="J151" s="2"/>
       <c r="K151" s="1"/>
       <c r="M151" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" spans="4:13" x14ac:dyDescent="0.3">
@@ -4804,7 +4804,7 @@
         <v>42</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>10</v>
@@ -4833,7 +4833,7 @@
         <v>43</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>12</v>
@@ -4857,7 +4857,7 @@
       <c r="J154" s="2"/>
       <c r="K154" s="1"/>
       <c r="M154" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155" spans="4:13" x14ac:dyDescent="0.3">
@@ -4874,7 +4874,7 @@
         <v>45</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>12</v>
@@ -4898,7 +4898,7 @@
       <c r="J156" s="2"/>
       <c r="K156" s="1"/>
       <c r="M156" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="4:13" x14ac:dyDescent="0.3">
@@ -4915,7 +4915,7 @@
         <v>45</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>13</v>
@@ -4944,7 +4944,7 @@
         <v>48</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>13</v>
@@ -4973,7 +4973,7 @@
         <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>13</v>
@@ -5002,7 +5002,7 @@
         <v>50</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>10</v>
@@ -5034,7 +5034,7 @@
         <v>45</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I161" s="1" t="s">
         <v>13</v>
@@ -5063,7 +5063,7 @@
         <v>52</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>12</v>
@@ -5087,7 +5087,7 @@
       <c r="J163" s="2"/>
       <c r="K163" s="1"/>
       <c r="M163" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="4:13" x14ac:dyDescent="0.3">
@@ -5101,7 +5101,7 @@
         <v>53</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I164" s="1" t="s">
         <v>12</v>
@@ -5125,7 +5125,7 @@
       <c r="J165" s="2"/>
       <c r="K165" s="1"/>
       <c r="M165" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="166" spans="4:13" x14ac:dyDescent="0.3">
@@ -5139,7 +5139,7 @@
         <v>65</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I166" s="1" t="s">
         <v>13</v>
@@ -5168,7 +5168,7 @@
         <v>55</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>10</v>
@@ -5200,7 +5200,7 @@
         <v>45</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I168" s="1" t="s">
         <v>10</v>
@@ -5229,7 +5229,7 @@
         <v>67</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I169" s="1" t="s">
         <v>10</v>
@@ -5258,7 +5258,7 @@
         <v>57</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I170" s="1" t="s">
         <v>13</v>
@@ -5287,7 +5287,7 @@
         <v>58</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>10</v>
@@ -5316,7 +5316,7 @@
         <v>59</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>10</v>
@@ -5345,7 +5345,7 @@
         <v>60</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I173" s="1" t="s">
         <v>12</v>
@@ -5369,7 +5369,7 @@
       <c r="J174" s="2"/>
       <c r="K174" s="1"/>
       <c r="M174" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="175" spans="4:13" x14ac:dyDescent="0.3">
@@ -5386,7 +5386,7 @@
         <v>45</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>13</v>
@@ -5415,7 +5415,7 @@
         <v>63</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I176" s="1" t="s">
         <v>13</v>
@@ -5444,7 +5444,7 @@
         <v>62</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I177" s="1" t="s">
         <v>10</v>
@@ -5473,7 +5473,7 @@
         <v>66</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I178" s="1" t="s">
         <v>13</v>
@@ -5502,7 +5502,7 @@
         <v>64</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>10</v>
@@ -5531,7 +5531,7 @@
         <v>40</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>10</v>
@@ -5560,7 +5560,7 @@
         <v>41</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I181" s="1" t="s">
         <v>10</v>
@@ -5589,7 +5589,7 @@
         <v>42</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I182" s="1" t="s">
         <v>10</v>
@@ -5618,7 +5618,7 @@
         <v>43</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I183" s="1" t="s">
         <v>10</v>
@@ -5650,7 +5650,7 @@
         <v>45</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>13</v>
@@ -5682,7 +5682,7 @@
         <v>45</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>13</v>
@@ -5711,7 +5711,7 @@
         <v>48</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>13</v>
@@ -5740,7 +5740,7 @@
         <v>49</v>
       </c>
       <c r="H187" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I187" s="1" t="s">
         <v>13</v>
@@ -5769,7 +5769,7 @@
         <v>50</v>
       </c>
       <c r="H188" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>12</v>
@@ -5793,7 +5793,7 @@
       <c r="J189" s="2"/>
       <c r="K189" s="1"/>
       <c r="M189" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="190" spans="4:13" x14ac:dyDescent="0.3">
@@ -5807,7 +5807,7 @@
         <v>52</v>
       </c>
       <c r="H190" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I190" s="1" t="s">
         <v>10</v>
@@ -5836,7 +5836,7 @@
         <v>53</v>
       </c>
       <c r="H191" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I191" s="1" t="s">
         <v>12</v>
@@ -5860,7 +5860,7 @@
       <c r="J192" s="2"/>
       <c r="K192" s="1"/>
       <c r="M192" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="193" spans="4:13" x14ac:dyDescent="0.3">
@@ -5874,7 +5874,7 @@
         <v>55</v>
       </c>
       <c r="H193" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>10</v>
@@ -5906,7 +5906,7 @@
         <v>45</v>
       </c>
       <c r="H194" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>10</v>
@@ -5935,7 +5935,7 @@
         <v>67</v>
       </c>
       <c r="H195" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>10</v>
@@ -5964,7 +5964,7 @@
         <v>58</v>
       </c>
       <c r="H196" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I196" s="1" t="s">
         <v>10</v>
@@ -5993,7 +5993,7 @@
         <v>60</v>
       </c>
       <c r="H197" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>10</v>
@@ -6025,7 +6025,7 @@
         <v>45</v>
       </c>
       <c r="H198" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I198" s="1" t="s">
         <v>10</v>
@@ -6054,7 +6054,7 @@
         <v>63</v>
       </c>
       <c r="H199" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I199" s="1" t="s">
         <v>10</v>
@@ -6083,7 +6083,7 @@
         <v>62</v>
       </c>
       <c r="H200" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I200" s="1" t="s">
         <v>10</v>
@@ -6112,7 +6112,7 @@
         <v>66</v>
       </c>
       <c r="H201" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I201" s="1" t="s">
         <v>13</v>
@@ -6141,7 +6141,7 @@
         <v>64</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I202" s="1" t="s">
         <v>10</v>
@@ -6170,7 +6170,7 @@
         <v>40</v>
       </c>
       <c r="H203" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I203" s="1" t="s">
         <v>10</v>
@@ -6199,7 +6199,7 @@
         <v>41</v>
       </c>
       <c r="H204" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>10</v>
@@ -6228,7 +6228,7 @@
         <v>42</v>
       </c>
       <c r="H205" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I205" s="1" t="s">
         <v>10</v>
@@ -6257,7 +6257,7 @@
         <v>43</v>
       </c>
       <c r="H206" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I206" s="1" t="s">
         <v>10</v>
@@ -6289,7 +6289,7 @@
         <v>45</v>
       </c>
       <c r="H207" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I207" s="1" t="s">
         <v>13</v>
@@ -6321,7 +6321,7 @@
         <v>45</v>
       </c>
       <c r="H208" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I208" s="1" t="s">
         <v>13</v>
@@ -6350,7 +6350,7 @@
         <v>48</v>
       </c>
       <c r="H209" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I209" s="1" t="s">
         <v>10</v>
@@ -6379,7 +6379,7 @@
         <v>49</v>
       </c>
       <c r="H210" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I210" s="1" t="s">
         <v>13</v>
@@ -6408,7 +6408,7 @@
         <v>50</v>
       </c>
       <c r="H211" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I211" s="1" t="s">
         <v>10</v>
@@ -6437,7 +6437,7 @@
         <v>52</v>
       </c>
       <c r="H212" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I212" s="1" t="s">
         <v>10</v>
@@ -6466,7 +6466,7 @@
         <v>53</v>
       </c>
       <c r="H213" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I213" s="1" t="s">
         <v>13</v>
@@ -6495,7 +6495,7 @@
         <v>55</v>
       </c>
       <c r="H214" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I214" s="1" t="s">
         <v>10</v>
@@ -6527,7 +6527,7 @@
         <v>45</v>
       </c>
       <c r="H215" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I215" s="1" t="s">
         <v>10</v>
@@ -6556,7 +6556,7 @@
         <v>67</v>
       </c>
       <c r="H216" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I216" s="1" t="s">
         <v>10</v>
@@ -6585,7 +6585,7 @@
         <v>58</v>
       </c>
       <c r="H217" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I217" s="1" t="s">
         <v>13</v>
@@ -6614,7 +6614,7 @@
         <v>60</v>
       </c>
       <c r="H218" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I218" s="1" t="s">
         <v>13</v>
@@ -6646,7 +6646,7 @@
         <v>45</v>
       </c>
       <c r="H219" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I219" s="1" t="s">
         <v>13</v>
@@ -6675,7 +6675,7 @@
         <v>63</v>
       </c>
       <c r="H220" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I220" s="1" t="s">
         <v>13</v>
@@ -6704,7 +6704,7 @@
         <v>62</v>
       </c>
       <c r="H221" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I221" s="1" t="s">
         <v>10</v>
@@ -7354,7 +7354,7 @@
         <v>66</v>
       </c>
       <c r="H243" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I243" s="1" t="s">
         <v>13</v>
@@ -7383,7 +7383,7 @@
         <v>64</v>
       </c>
       <c r="H244" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I244" s="1" t="s">
         <v>13</v>
@@ -7412,7 +7412,7 @@
         <v>40</v>
       </c>
       <c r="H245" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I245" s="1" t="s">
         <v>10</v>
@@ -7441,7 +7441,7 @@
         <v>41</v>
       </c>
       <c r="H246" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I246" s="1" t="s">
         <v>13</v>
@@ -7470,7 +7470,7 @@
         <v>42</v>
       </c>
       <c r="H247" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I247" s="1" t="s">
         <v>13</v>
@@ -7499,7 +7499,7 @@
         <v>43</v>
       </c>
       <c r="H248" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I248" s="1" t="s">
         <v>10</v>
@@ -7531,7 +7531,7 @@
         <v>45</v>
       </c>
       <c r="H249" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I249" s="1" t="s">
         <v>13</v>
@@ -7563,7 +7563,7 @@
         <v>45</v>
       </c>
       <c r="H250" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I250" s="1" t="s">
         <v>13</v>
@@ -7592,7 +7592,7 @@
         <v>48</v>
       </c>
       <c r="H251" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I251" s="1" t="s">
         <v>10</v>
@@ -7621,7 +7621,7 @@
         <v>49</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I252" s="1" t="s">
         <v>13</v>
@@ -7650,7 +7650,7 @@
         <v>50</v>
       </c>
       <c r="H253" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I253" s="1" t="s">
         <v>10</v>
@@ -7679,7 +7679,7 @@
         <v>52</v>
       </c>
       <c r="H254" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I254" s="1" t="s">
         <v>10</v>
@@ -7708,7 +7708,7 @@
         <v>53</v>
       </c>
       <c r="H255" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I255" s="1" t="s">
         <v>13</v>
@@ -7737,7 +7737,7 @@
         <v>55</v>
       </c>
       <c r="H256" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I256" s="1" t="s">
         <v>10</v>
@@ -7769,7 +7769,7 @@
         <v>45</v>
       </c>
       <c r="H257" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I257" s="1" t="s">
         <v>10</v>
@@ -7798,7 +7798,7 @@
         <v>67</v>
       </c>
       <c r="H258" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I258" s="1" t="s">
         <v>10</v>
@@ -7827,7 +7827,7 @@
         <v>58</v>
       </c>
       <c r="H259" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I259" s="1" t="s">
         <v>10</v>
@@ -7856,7 +7856,7 @@
         <v>60</v>
       </c>
       <c r="H260" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I260" s="1" t="s">
         <v>10</v>
@@ -7888,7 +7888,7 @@
         <v>45</v>
       </c>
       <c r="H261" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I261" s="1" t="s">
         <v>13</v>
@@ -7917,7 +7917,7 @@
         <v>63</v>
       </c>
       <c r="H262" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I262" s="1" t="s">
         <v>13</v>
@@ -7946,7 +7946,7 @@
         <v>62</v>
       </c>
       <c r="H263" s="2" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I263" s="1" t="s">
         <v>10</v>
@@ -8736,7 +8736,7 @@
       <c r="J290" s="2"/>
       <c r="K290" s="1"/>
       <c r="M290" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="291" spans="4:13" x14ac:dyDescent="0.3">
@@ -9334,7 +9334,7 @@
       <c r="J311" s="2"/>
       <c r="K311" s="1"/>
       <c r="M311" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="312" spans="4:13" x14ac:dyDescent="0.3">
@@ -9438,7 +9438,7 @@
         <v>68</v>
       </c>
       <c r="H315" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I315" s="1" t="s">
         <v>13</v>
@@ -9467,7 +9467,7 @@
         <v>66</v>
       </c>
       <c r="H316" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I316" s="1" t="s">
         <v>13</v>
@@ -9496,7 +9496,7 @@
         <v>69</v>
       </c>
       <c r="H317" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I317" s="1" t="s">
         <v>10</v>
@@ -9525,7 +9525,7 @@
         <v>64</v>
       </c>
       <c r="H318" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I318" s="1" t="s">
         <v>10</v>
@@ -9554,7 +9554,7 @@
         <v>40</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I319" s="1" t="s">
         <v>10</v>
@@ -9583,7 +9583,7 @@
         <v>70</v>
       </c>
       <c r="H320" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I320" s="1" t="s">
         <v>10</v>
@@ -9612,7 +9612,7 @@
         <v>41</v>
       </c>
       <c r="H321" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I321" s="1" t="s">
         <v>10</v>
@@ -9641,7 +9641,7 @@
         <v>43</v>
       </c>
       <c r="H322" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I322" s="1" t="s">
         <v>10</v>
@@ -9673,7 +9673,7 @@
         <v>45</v>
       </c>
       <c r="H323" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I323" s="1" t="s">
         <v>13</v>
@@ -9705,7 +9705,7 @@
         <v>45</v>
       </c>
       <c r="H324" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I324" s="1" t="s">
         <v>13</v>
@@ -9734,7 +9734,7 @@
         <v>48</v>
       </c>
       <c r="H325" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I325" s="1" t="s">
         <v>10</v>
@@ -9763,7 +9763,7 @@
         <v>49</v>
       </c>
       <c r="H326" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I326" s="1" t="s">
         <v>13</v>
@@ -9792,7 +9792,7 @@
         <v>50</v>
       </c>
       <c r="H327" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I327" s="1" t="s">
         <v>10</v>
@@ -9821,7 +9821,7 @@
         <v>52</v>
       </c>
       <c r="H328" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I328" s="1" t="s">
         <v>10</v>
@@ -9850,7 +9850,7 @@
         <v>71</v>
       </c>
       <c r="H329" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I329" s="1" t="s">
         <v>10</v>
@@ -9879,7 +9879,7 @@
         <v>72</v>
       </c>
       <c r="H330" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I330" s="1" t="s">
         <v>10</v>
@@ -9911,7 +9911,7 @@
         <v>45</v>
       </c>
       <c r="H331" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I331" s="1" t="s">
         <v>10</v>
@@ -9940,7 +9940,7 @@
         <v>73</v>
       </c>
       <c r="H332" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I332" s="1" t="s">
         <v>13</v>
@@ -9969,7 +9969,7 @@
         <v>74</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I333" s="1" t="s">
         <v>10</v>
@@ -9998,7 +9998,7 @@
         <v>75</v>
       </c>
       <c r="H334" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I334" s="1" t="s">
         <v>10</v>
@@ -10027,7 +10027,7 @@
         <v>67</v>
       </c>
       <c r="H335" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I335" s="1" t="s">
         <v>10</v>
@@ -10056,7 +10056,7 @@
         <v>67</v>
       </c>
       <c r="H336" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I336" s="1" t="s">
         <v>10</v>
@@ -10085,7 +10085,7 @@
         <v>76</v>
       </c>
       <c r="H337" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I337" s="1" t="s">
         <v>13</v>
@@ -10114,7 +10114,7 @@
         <v>58</v>
       </c>
       <c r="H338" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I338" s="1" t="s">
         <v>10</v>
@@ -10143,7 +10143,7 @@
         <v>77</v>
       </c>
       <c r="H339" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I339" s="1" t="s">
         <v>12</v>
@@ -10167,7 +10167,7 @@
       <c r="J340" s="2"/>
       <c r="K340" s="1"/>
       <c r="M340" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="341" spans="4:13" x14ac:dyDescent="0.3">
@@ -10181,7 +10181,7 @@
         <v>60</v>
       </c>
       <c r="H341" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I341" s="1" t="s">
         <v>13</v>
@@ -10213,7 +10213,7 @@
         <v>45</v>
       </c>
       <c r="H342" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I342" s="1" t="s">
         <v>13</v>
@@ -10242,7 +10242,7 @@
         <v>62</v>
       </c>
       <c r="H343" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I343" s="1" t="s">
         <v>10</v>
@@ -10469,7 +10469,7 @@
       <c r="J351" s="2"/>
       <c r="K351" s="1"/>
       <c r="M351" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="352" spans="4:13" x14ac:dyDescent="0.3">
@@ -10507,7 +10507,7 @@
       <c r="J353" s="2"/>
       <c r="K353" s="1"/>
       <c r="M353" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="354" spans="4:13" x14ac:dyDescent="0.3">
@@ -10696,7 +10696,7 @@
       <c r="J360" s="2"/>
       <c r="K360" s="1"/>
       <c r="M360" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="361" spans="4:13" x14ac:dyDescent="0.3">
@@ -11027,7 +11027,7 @@
       <c r="J372" s="2"/>
       <c r="K372" s="1"/>
       <c r="M372" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="373" spans="4:13" x14ac:dyDescent="0.3">
@@ -11831,7 +11831,7 @@
       <c r="J400" s="2"/>
       <c r="K400" s="1"/>
       <c r="M400" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="401" spans="4:13" x14ac:dyDescent="0.3">
@@ -11964,7 +11964,7 @@
         <v>68</v>
       </c>
       <c r="H405" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I405" s="1" t="s">
         <v>13</v>
@@ -11993,7 +11993,7 @@
         <v>66</v>
       </c>
       <c r="H406" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I406" s="1" t="s">
         <v>13</v>
@@ -12022,7 +12022,7 @@
         <v>69</v>
       </c>
       <c r="H407" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I407" s="1" t="s">
         <v>10</v>
@@ -12051,7 +12051,7 @@
         <v>64</v>
       </c>
       <c r="H408" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I408" s="1" t="s">
         <v>13</v>
@@ -12080,7 +12080,7 @@
         <v>40</v>
       </c>
       <c r="H409" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I409" s="1" t="s">
         <v>10</v>
@@ -12109,7 +12109,7 @@
         <v>70</v>
       </c>
       <c r="H410" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I410" s="1" t="s">
         <v>10</v>
@@ -12138,7 +12138,7 @@
         <v>41</v>
       </c>
       <c r="H411" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I411" s="1" t="s">
         <v>13</v>
@@ -12167,7 +12167,7 @@
         <v>43</v>
       </c>
       <c r="H412" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I412" s="1" t="s">
         <v>10</v>
@@ -12199,7 +12199,7 @@
         <v>45</v>
       </c>
       <c r="H413" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I413" s="1" t="s">
         <v>13</v>
@@ -12231,7 +12231,7 @@
         <v>45</v>
       </c>
       <c r="H414" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I414" s="1" t="s">
         <v>13</v>
@@ -12260,7 +12260,7 @@
         <v>48</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I415" s="1" t="s">
         <v>10</v>
@@ -12289,7 +12289,7 @@
         <v>49</v>
       </c>
       <c r="H416" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I416" s="1" t="s">
         <v>10</v>
@@ -12318,7 +12318,7 @@
         <v>50</v>
       </c>
       <c r="H417" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I417" s="1" t="s">
         <v>10</v>
@@ -12347,7 +12347,7 @@
         <v>52</v>
       </c>
       <c r="H418" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I418" s="1" t="s">
         <v>10</v>
@@ -12376,7 +12376,7 @@
         <v>71</v>
       </c>
       <c r="H419" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I419" s="1" t="s">
         <v>10</v>
@@ -12405,7 +12405,7 @@
         <v>72</v>
       </c>
       <c r="H420" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I420" s="1" t="s">
         <v>13</v>
@@ -12437,7 +12437,7 @@
         <v>45</v>
       </c>
       <c r="H421" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I421" s="1" t="s">
         <v>10</v>
@@ -12466,7 +12466,7 @@
         <v>73</v>
       </c>
       <c r="H422" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I422" s="1" t="s">
         <v>13</v>
@@ -12495,7 +12495,7 @@
         <v>74</v>
       </c>
       <c r="H423" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I423" s="1" t="s">
         <v>13</v>
@@ -12524,7 +12524,7 @@
         <v>75</v>
       </c>
       <c r="H424" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I424" s="1" t="s">
         <v>13</v>
@@ -12553,7 +12553,7 @@
         <v>67</v>
       </c>
       <c r="H425" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I425" s="1" t="s">
         <v>10</v>
@@ -12582,7 +12582,7 @@
         <v>67</v>
       </c>
       <c r="H426" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I426" s="1" t="s">
         <v>10</v>
@@ -12611,7 +12611,7 @@
         <v>76</v>
       </c>
       <c r="H427" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I427" s="1" t="s">
         <v>13</v>
@@ -12640,7 +12640,7 @@
         <v>58</v>
       </c>
       <c r="H428" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I428" s="1" t="s">
         <v>10</v>
@@ -12669,7 +12669,7 @@
         <v>77</v>
       </c>
       <c r="H429" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I429" s="1" t="s">
         <v>13</v>
@@ -12698,7 +12698,7 @@
         <v>60</v>
       </c>
       <c r="H430" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I430" s="1" t="s">
         <v>10</v>
@@ -12730,7 +12730,7 @@
         <v>45</v>
       </c>
       <c r="H431" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I431" s="1" t="s">
         <v>13</v>
@@ -12759,7 +12759,7 @@
         <v>62</v>
       </c>
       <c r="H432" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="I432" s="1" t="s">
         <v>12</v>
@@ -12783,7 +12783,7 @@
       <c r="J433" s="2"/>
       <c r="K433" s="1"/>
       <c r="M433" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="434" spans="4:13" x14ac:dyDescent="0.3">
@@ -12797,7 +12797,7 @@
         <v>68</v>
       </c>
       <c r="H434" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I434" s="1" t="s">
         <v>13</v>
@@ -12826,7 +12826,7 @@
         <v>66</v>
       </c>
       <c r="H435" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I435" s="1" t="s">
         <v>13</v>
@@ -12855,7 +12855,7 @@
         <v>69</v>
       </c>
       <c r="H436" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I436" s="1" t="s">
         <v>13</v>
@@ -12884,7 +12884,7 @@
         <v>64</v>
       </c>
       <c r="H437" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I437" s="1" t="s">
         <v>13</v>
@@ -12913,7 +12913,7 @@
         <v>40</v>
       </c>
       <c r="H438" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I438" s="1" t="s">
         <v>10</v>
@@ -12942,7 +12942,7 @@
         <v>70</v>
       </c>
       <c r="H439" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I439" s="1" t="s">
         <v>10</v>
@@ -12971,7 +12971,7 @@
         <v>41</v>
       </c>
       <c r="H440" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I440" s="1" t="s">
         <v>13</v>
@@ -13000,7 +13000,7 @@
         <v>43</v>
       </c>
       <c r="H441" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I441" s="1" t="s">
         <v>10</v>
@@ -13032,7 +13032,7 @@
         <v>45</v>
       </c>
       <c r="H442" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I442" s="1" t="s">
         <v>13</v>
@@ -13064,7 +13064,7 @@
         <v>45</v>
       </c>
       <c r="H443" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I443" s="1" t="s">
         <v>13</v>
@@ -13093,7 +13093,7 @@
         <v>48</v>
       </c>
       <c r="H444" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I444" s="1" t="s">
         <v>10</v>
@@ -13122,7 +13122,7 @@
         <v>49</v>
       </c>
       <c r="H445" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I445" s="1" t="s">
         <v>13</v>
@@ -13151,7 +13151,7 @@
         <v>50</v>
       </c>
       <c r="H446" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I446" s="1" t="s">
         <v>10</v>
@@ -13180,7 +13180,7 @@
         <v>52</v>
       </c>
       <c r="H447" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I447" s="1" t="s">
         <v>10</v>
@@ -13209,7 +13209,7 @@
         <v>71</v>
       </c>
       <c r="H448" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I448" s="1" t="s">
         <v>10</v>
@@ -13238,7 +13238,7 @@
         <v>72</v>
       </c>
       <c r="H449" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I449" s="1" t="s">
         <v>13</v>
@@ -13270,7 +13270,7 @@
         <v>45</v>
       </c>
       <c r="H450" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I450" s="1" t="s">
         <v>10</v>
@@ -13299,7 +13299,7 @@
         <v>73</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I451" s="1" t="s">
         <v>13</v>
@@ -13328,7 +13328,7 @@
         <v>74</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I452" s="1" t="s">
         <v>13</v>
@@ -13357,7 +13357,7 @@
         <v>75</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I453" s="1" t="s">
         <v>13</v>
@@ -13386,7 +13386,7 @@
         <v>67</v>
       </c>
       <c r="H454" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I454" s="1" t="s">
         <v>10</v>
@@ -13415,7 +13415,7 @@
         <v>67</v>
       </c>
       <c r="H455" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I455" s="1" t="s">
         <v>10</v>
@@ -13444,7 +13444,7 @@
         <v>76</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I456" s="1" t="s">
         <v>13</v>
@@ -13473,7 +13473,7 @@
         <v>58</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I457" s="1" t="s">
         <v>10</v>
@@ -13502,7 +13502,7 @@
         <v>77</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I458" s="1" t="s">
         <v>13</v>
@@ -13531,7 +13531,7 @@
         <v>60</v>
       </c>
       <c r="H459" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I459" s="1" t="s">
         <v>13</v>
@@ -13563,7 +13563,7 @@
         <v>45</v>
       </c>
       <c r="H460" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I460" s="1" t="s">
         <v>13</v>
@@ -13592,7 +13592,7 @@
         <v>62</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="I461" s="1" t="s">
         <v>10</v>
@@ -13621,7 +13621,7 @@
         <v>68</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I462" s="1" t="s">
         <v>13</v>
@@ -13650,7 +13650,7 @@
         <v>66</v>
       </c>
       <c r="H463" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I463" s="1" t="s">
         <v>13</v>
@@ -13679,7 +13679,7 @@
         <v>69</v>
       </c>
       <c r="H464" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I464" s="1" t="s">
         <v>10</v>
@@ -13708,7 +13708,7 @@
         <v>64</v>
       </c>
       <c r="H465" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I465" s="1" t="s">
         <v>13</v>
@@ -13737,7 +13737,7 @@
         <v>40</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I466" s="1" t="s">
         <v>10</v>
@@ -13766,7 +13766,7 @@
         <v>70</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I467" s="1" t="s">
         <v>10</v>
@@ -13795,7 +13795,7 @@
         <v>41</v>
       </c>
       <c r="H468" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I468" s="1" t="s">
         <v>14</v>
@@ -13819,7 +13819,7 @@
       <c r="J469" s="2"/>
       <c r="K469" s="1"/>
       <c r="M469" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="470" spans="4:13" x14ac:dyDescent="0.3">
@@ -13833,7 +13833,7 @@
         <v>43</v>
       </c>
       <c r="H470" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I470" s="1" t="s">
         <v>10</v>
@@ -13865,7 +13865,7 @@
         <v>45</v>
       </c>
       <c r="H471" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I471" s="1" t="s">
         <v>13</v>
@@ -13897,7 +13897,7 @@
         <v>45</v>
       </c>
       <c r="H472" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I472" s="1" t="s">
         <v>13</v>
@@ -13926,7 +13926,7 @@
         <v>48</v>
       </c>
       <c r="H473" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I473" s="1" t="s">
         <v>10</v>
@@ -13955,7 +13955,7 @@
         <v>49</v>
       </c>
       <c r="H474" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I474" s="1" t="s">
         <v>13</v>
@@ -13984,7 +13984,7 @@
         <v>50</v>
       </c>
       <c r="H475" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I475" s="1" t="s">
         <v>10</v>
@@ -14013,7 +14013,7 @@
         <v>52</v>
       </c>
       <c r="H476" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I476" s="1" t="s">
         <v>13</v>
@@ -14042,7 +14042,7 @@
         <v>71</v>
       </c>
       <c r="H477" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I477" s="1" t="s">
         <v>13</v>
@@ -14071,7 +14071,7 @@
         <v>72</v>
       </c>
       <c r="H478" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I478" s="1" t="s">
         <v>13</v>
@@ -14103,7 +14103,7 @@
         <v>45</v>
       </c>
       <c r="H479" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I479" s="1" t="s">
         <v>10</v>
@@ -14132,7 +14132,7 @@
         <v>73</v>
       </c>
       <c r="H480" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I480" s="1" t="s">
         <v>13</v>
@@ -14161,7 +14161,7 @@
         <v>74</v>
       </c>
       <c r="H481" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I481" s="1" t="s">
         <v>13</v>
@@ -14190,7 +14190,7 @@
         <v>75</v>
       </c>
       <c r="H482" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I482" s="1" t="s">
         <v>12</v>
@@ -14214,7 +14214,7 @@
       <c r="J483" s="2"/>
       <c r="K483" s="1"/>
       <c r="M483" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="484" spans="4:13" x14ac:dyDescent="0.3">
@@ -14228,7 +14228,7 @@
         <v>67</v>
       </c>
       <c r="H484" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I484" s="1" t="s">
         <v>10</v>
@@ -14257,7 +14257,7 @@
         <v>67</v>
       </c>
       <c r="H485" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I485" s="1" t="s">
         <v>10</v>
@@ -14286,7 +14286,7 @@
         <v>76</v>
       </c>
       <c r="H486" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I486" s="1" t="s">
         <v>13</v>
@@ -14315,7 +14315,7 @@
         <v>58</v>
       </c>
       <c r="H487" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I487" s="1" t="s">
         <v>10</v>
@@ -14344,7 +14344,7 @@
         <v>77</v>
       </c>
       <c r="H488" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I488" s="1" t="s">
         <v>13</v>
@@ -14373,7 +14373,7 @@
         <v>60</v>
       </c>
       <c r="H489" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I489" s="1" t="s">
         <v>13</v>
@@ -14405,7 +14405,7 @@
         <v>45</v>
       </c>
       <c r="H490" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I490" s="1" t="s">
         <v>13</v>
@@ -14434,7 +14434,7 @@
         <v>62</v>
       </c>
       <c r="H491" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I491" s="1" t="s">
         <v>13</v>
@@ -14463,7 +14463,7 @@
         <v>68</v>
       </c>
       <c r="H492" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I492" s="1" t="s">
         <v>13</v>
@@ -14492,7 +14492,7 @@
         <v>66</v>
       </c>
       <c r="H493" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I493" s="1" t="s">
         <v>13</v>
@@ -14521,7 +14521,7 @@
         <v>69</v>
       </c>
       <c r="H494" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I494" s="1" t="s">
         <v>10</v>
@@ -14550,7 +14550,7 @@
         <v>64</v>
       </c>
       <c r="H495" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I495" s="1" t="s">
         <v>13</v>
@@ -14579,7 +14579,7 @@
         <v>40</v>
       </c>
       <c r="H496" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I496" s="1" t="s">
         <v>10</v>
@@ -14608,7 +14608,7 @@
         <v>70</v>
       </c>
       <c r="H497" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I497" s="1" t="s">
         <v>10</v>
@@ -14637,7 +14637,7 @@
         <v>41</v>
       </c>
       <c r="H498" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I498" s="1" t="s">
         <v>13</v>
@@ -14666,7 +14666,7 @@
         <v>43</v>
       </c>
       <c r="H499" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I499" s="1" t="s">
         <v>10</v>
@@ -14698,7 +14698,7 @@
         <v>45</v>
       </c>
       <c r="H500" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I500" s="1" t="s">
         <v>13</v>
@@ -14730,7 +14730,7 @@
         <v>45</v>
       </c>
       <c r="H501" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I501" s="1" t="s">
         <v>14</v>
@@ -14754,7 +14754,7 @@
       <c r="J502" s="2"/>
       <c r="K502" s="1"/>
       <c r="M502" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="503" spans="4:13" x14ac:dyDescent="0.3">
@@ -14768,7 +14768,7 @@
         <v>48</v>
       </c>
       <c r="H503" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I503" s="1" t="s">
         <v>10</v>
@@ -14797,7 +14797,7 @@
         <v>49</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I504" s="1" t="s">
         <v>13</v>
@@ -14826,7 +14826,7 @@
         <v>50</v>
       </c>
       <c r="H505" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I505" s="1" t="s">
         <v>10</v>
@@ -14855,7 +14855,7 @@
         <v>52</v>
       </c>
       <c r="H506" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I506" s="1" t="s">
         <v>13</v>
@@ -14884,7 +14884,7 @@
         <v>71</v>
       </c>
       <c r="H507" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I507" s="1" t="s">
         <v>10</v>
@@ -14913,7 +14913,7 @@
         <v>72</v>
       </c>
       <c r="H508" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I508" s="1" t="s">
         <v>13</v>
@@ -14945,7 +14945,7 @@
         <v>45</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I509" s="1" t="s">
         <v>10</v>
@@ -14974,7 +14974,7 @@
         <v>73</v>
       </c>
       <c r="H510" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I510" s="1" t="s">
         <v>13</v>
@@ -15003,7 +15003,7 @@
         <v>74</v>
       </c>
       <c r="H511" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I511" s="1" t="s">
         <v>13</v>
@@ -15032,7 +15032,7 @@
         <v>75</v>
       </c>
       <c r="H512" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I512" s="1" t="s">
         <v>13</v>
@@ -15061,7 +15061,7 @@
         <v>67</v>
       </c>
       <c r="H513" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I513" s="1" t="s">
         <v>10</v>
@@ -15090,7 +15090,7 @@
         <v>67</v>
       </c>
       <c r="H514" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I514" s="1" t="s">
         <v>10</v>
@@ -15119,7 +15119,7 @@
         <v>76</v>
       </c>
       <c r="H515" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I515" s="1" t="s">
         <v>13</v>
@@ -15148,7 +15148,7 @@
         <v>58</v>
       </c>
       <c r="H516" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I516" s="1" t="s">
         <v>10</v>
@@ -15177,7 +15177,7 @@
         <v>77</v>
       </c>
       <c r="H517" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I517" s="1" t="s">
         <v>13</v>
@@ -15206,7 +15206,7 @@
         <v>60</v>
       </c>
       <c r="H518" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I518" s="1" t="s">
         <v>13</v>
@@ -15238,7 +15238,7 @@
         <v>45</v>
       </c>
       <c r="H519" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I519" s="1" t="s">
         <v>12</v>
@@ -15262,7 +15262,7 @@
       <c r="J520" s="2"/>
       <c r="K520" s="1"/>
       <c r="M520" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="521" spans="4:13" x14ac:dyDescent="0.3">
@@ -15276,7 +15276,7 @@
         <v>62</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I521" s="1" t="s">
         <v>10</v>
@@ -15305,7 +15305,7 @@
         <v>68</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I522" s="1" t="s">
         <v>13</v>
@@ -15334,7 +15334,7 @@
         <v>66</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I523" s="1" t="s">
         <v>13</v>
@@ -15363,7 +15363,7 @@
         <v>69</v>
       </c>
       <c r="H524" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I524" s="1" t="s">
         <v>10</v>
@@ -15392,7 +15392,7 @@
         <v>64</v>
       </c>
       <c r="H525" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I525" s="1" t="s">
         <v>13</v>
@@ -15421,7 +15421,7 @@
         <v>40</v>
       </c>
       <c r="H526" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I526" s="1" t="s">
         <v>10</v>
@@ -15450,7 +15450,7 @@
         <v>70</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I527" s="1" t="s">
         <v>10</v>
@@ -15479,7 +15479,7 @@
         <v>41</v>
       </c>
       <c r="H528" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I528" s="1" t="s">
         <v>13</v>
@@ -15508,7 +15508,7 @@
         <v>43</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I529" s="1" t="s">
         <v>10</v>
@@ -15540,7 +15540,7 @@
         <v>45</v>
       </c>
       <c r="H530" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I530" s="1" t="s">
         <v>13</v>
@@ -15572,7 +15572,7 @@
         <v>45</v>
       </c>
       <c r="H531" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I531" s="1" t="s">
         <v>13</v>
@@ -15601,7 +15601,7 @@
         <v>48</v>
       </c>
       <c r="H532" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I532" s="1" t="s">
         <v>10</v>
@@ -15630,7 +15630,7 @@
         <v>49</v>
       </c>
       <c r="H533" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I533" s="1" t="s">
         <v>13</v>
@@ -15659,7 +15659,7 @@
         <v>50</v>
       </c>
       <c r="H534" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I534" s="1" t="s">
         <v>10</v>
@@ -15688,7 +15688,7 @@
         <v>52</v>
       </c>
       <c r="H535" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I535" s="1" t="s">
         <v>13</v>
@@ -15717,7 +15717,7 @@
         <v>71</v>
       </c>
       <c r="H536" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I536" s="1" t="s">
         <v>10</v>
@@ -15746,7 +15746,7 @@
         <v>72</v>
       </c>
       <c r="H537" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I537" s="1" t="s">
         <v>13</v>
@@ -15778,7 +15778,7 @@
         <v>45</v>
       </c>
       <c r="H538" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I538" s="1" t="s">
         <v>12</v>
@@ -15802,7 +15802,7 @@
       <c r="J539" s="2"/>
       <c r="K539" s="1"/>
       <c r="M539" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="540" spans="4:13" x14ac:dyDescent="0.3">
@@ -15816,7 +15816,7 @@
         <v>73</v>
       </c>
       <c r="H540" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I540" s="1" t="s">
         <v>13</v>
@@ -15845,7 +15845,7 @@
         <v>74</v>
       </c>
       <c r="H541" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I541" s="1" t="s">
         <v>13</v>
@@ -15874,7 +15874,7 @@
         <v>75</v>
       </c>
       <c r="H542" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I542" s="1" t="s">
         <v>13</v>
@@ -15903,7 +15903,7 @@
         <v>67</v>
       </c>
       <c r="H543" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I543" s="1" t="s">
         <v>14</v>
@@ -15927,7 +15927,7 @@
       <c r="J544" s="2"/>
       <c r="K544" s="1"/>
       <c r="M544" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="545" spans="4:13" x14ac:dyDescent="0.3">
@@ -15941,7 +15941,7 @@
         <v>67</v>
       </c>
       <c r="H545" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I545" s="1" t="s">
         <v>10</v>
@@ -15970,7 +15970,7 @@
         <v>76</v>
       </c>
       <c r="H546" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I546" s="1" t="s">
         <v>13</v>
@@ -15999,7 +15999,7 @@
         <v>58</v>
       </c>
       <c r="H547" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I547" s="1" t="s">
         <v>10</v>
@@ -16028,7 +16028,7 @@
         <v>77</v>
       </c>
       <c r="H548" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I548" s="1" t="s">
         <v>13</v>
@@ -16057,7 +16057,7 @@
         <v>60</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I549" s="1" t="s">
         <v>13</v>
@@ -16089,7 +16089,7 @@
         <v>45</v>
       </c>
       <c r="H550" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I550" s="1" t="s">
         <v>13</v>
@@ -16118,7 +16118,7 @@
         <v>62</v>
       </c>
       <c r="H551" s="2" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I551" s="1" t="s">
         <v>13</v>
@@ -16147,7 +16147,7 @@
         <v>68</v>
       </c>
       <c r="H552" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I552" s="1" t="s">
         <v>13</v>
@@ -16176,7 +16176,7 @@
         <v>66</v>
       </c>
       <c r="H553" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I553" s="1" t="s">
         <v>13</v>
@@ -16205,7 +16205,7 @@
         <v>69</v>
       </c>
       <c r="H554" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I554" s="1" t="s">
         <v>10</v>
@@ -16234,7 +16234,7 @@
         <v>64</v>
       </c>
       <c r="H555" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I555" s="1" t="s">
         <v>13</v>
@@ -16263,7 +16263,7 @@
         <v>40</v>
       </c>
       <c r="H556" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I556" s="1" t="s">
         <v>10</v>
@@ -16292,7 +16292,7 @@
         <v>70</v>
       </c>
       <c r="H557" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I557" s="1" t="s">
         <v>10</v>
@@ -16321,7 +16321,7 @@
         <v>41</v>
       </c>
       <c r="H558" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I558" s="1" t="s">
         <v>13</v>
@@ -16350,7 +16350,7 @@
         <v>43</v>
       </c>
       <c r="H559" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I559" s="1" t="s">
         <v>13</v>
@@ -16382,7 +16382,7 @@
         <v>45</v>
       </c>
       <c r="H560" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I560" s="1" t="s">
         <v>13</v>
@@ -16414,7 +16414,7 @@
         <v>45</v>
       </c>
       <c r="H561" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I561" s="1" t="s">
         <v>13</v>
@@ -16443,7 +16443,7 @@
         <v>48</v>
       </c>
       <c r="H562" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I562" s="1" t="s">
         <v>10</v>
@@ -16472,7 +16472,7 @@
         <v>49</v>
       </c>
       <c r="H563" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I563" s="1" t="s">
         <v>13</v>
@@ -16501,7 +16501,7 @@
         <v>50</v>
       </c>
       <c r="H564" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I564" s="1" t="s">
         <v>10</v>
@@ -16530,7 +16530,7 @@
         <v>52</v>
       </c>
       <c r="H565" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I565" s="1" t="s">
         <v>13</v>
@@ -16559,7 +16559,7 @@
         <v>71</v>
       </c>
       <c r="H566" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I566" s="1" t="s">
         <v>10</v>
@@ -16588,7 +16588,7 @@
         <v>72</v>
       </c>
       <c r="H567" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I567" s="1" t="s">
         <v>13</v>
@@ -16620,7 +16620,7 @@
         <v>45</v>
       </c>
       <c r="H568" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I568" s="1" t="s">
         <v>13</v>
@@ -16649,7 +16649,7 @@
         <v>73</v>
       </c>
       <c r="H569" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I569" s="1" t="s">
         <v>13</v>
@@ -16678,7 +16678,7 @@
         <v>74</v>
       </c>
       <c r="H570" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I570" s="1" t="s">
         <v>13</v>
@@ -16707,7 +16707,7 @@
         <v>75</v>
       </c>
       <c r="H571" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I571" s="1" t="s">
         <v>13</v>
@@ -16736,7 +16736,7 @@
         <v>67</v>
       </c>
       <c r="H572" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I572" s="1" t="s">
         <v>10</v>
@@ -16765,7 +16765,7 @@
         <v>67</v>
       </c>
       <c r="H573" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I573" s="1" t="s">
         <v>10</v>
@@ -16794,7 +16794,7 @@
         <v>76</v>
       </c>
       <c r="H574" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I574" s="1" t="s">
         <v>13</v>
@@ -16823,7 +16823,7 @@
         <v>58</v>
       </c>
       <c r="H575" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I575" s="1" t="s">
         <v>13</v>
@@ -16852,7 +16852,7 @@
         <v>77</v>
       </c>
       <c r="H576" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I576" s="1" t="s">
         <v>13</v>
@@ -16881,7 +16881,7 @@
         <v>60</v>
       </c>
       <c r="H577" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I577" s="1" t="s">
         <v>10</v>
@@ -16913,7 +16913,7 @@
         <v>45</v>
       </c>
       <c r="H578" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I578" s="1" t="s">
         <v>13</v>
@@ -16942,7 +16942,7 @@
         <v>62</v>
       </c>
       <c r="H579" s="2" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I579" s="1" t="s">
         <v>10</v>
@@ -16971,7 +16971,7 @@
         <v>68</v>
       </c>
       <c r="H580" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I580" s="1" t="s">
         <v>13</v>
@@ -17000,7 +17000,7 @@
         <v>66</v>
       </c>
       <c r="H581" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I581" s="1" t="s">
         <v>13</v>
@@ -17029,7 +17029,7 @@
         <v>69</v>
       </c>
       <c r="H582" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I582" s="1" t="s">
         <v>10</v>
@@ -17058,7 +17058,7 @@
         <v>64</v>
       </c>
       <c r="H583" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I583" s="1" t="s">
         <v>13</v>
@@ -17087,7 +17087,7 @@
         <v>40</v>
       </c>
       <c r="H584" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I584" s="1" t="s">
         <v>10</v>
@@ -17116,7 +17116,7 @@
         <v>70</v>
       </c>
       <c r="H585" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I585" s="1" t="s">
         <v>10</v>
@@ -17145,7 +17145,7 @@
         <v>41</v>
       </c>
       <c r="H586" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I586" s="1" t="s">
         <v>13</v>
@@ -17174,7 +17174,7 @@
         <v>43</v>
       </c>
       <c r="H587" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I587" s="1" t="s">
         <v>13</v>
@@ -17206,7 +17206,7 @@
         <v>45</v>
       </c>
       <c r="H588" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I588" s="1" t="s">
         <v>13</v>
@@ -17238,7 +17238,7 @@
         <v>45</v>
       </c>
       <c r="H589" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I589" s="1" t="s">
         <v>13</v>
@@ -17267,7 +17267,7 @@
         <v>48</v>
       </c>
       <c r="H590" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I590" s="1" t="s">
         <v>13</v>
@@ -17296,7 +17296,7 @@
         <v>49</v>
       </c>
       <c r="H591" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I591" s="1" t="s">
         <v>13</v>
@@ -17325,7 +17325,7 @@
         <v>50</v>
       </c>
       <c r="H592" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I592" s="1" t="s">
         <v>10</v>
@@ -17354,7 +17354,7 @@
         <v>52</v>
       </c>
       <c r="H593" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I593" s="1" t="s">
         <v>13</v>
@@ -17383,7 +17383,7 @@
         <v>71</v>
       </c>
       <c r="H594" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I594" s="1" t="s">
         <v>12</v>
@@ -17407,7 +17407,7 @@
       <c r="J595" s="2"/>
       <c r="K595" s="1"/>
       <c r="M595" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="596" spans="4:13" x14ac:dyDescent="0.3">
@@ -17421,7 +17421,7 @@
         <v>72</v>
       </c>
       <c r="H596" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I596" s="1" t="s">
         <v>13</v>
@@ -17453,7 +17453,7 @@
         <v>45</v>
       </c>
       <c r="H597" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I597" s="1" t="s">
         <v>13</v>
@@ -17482,7 +17482,7 @@
         <v>73</v>
       </c>
       <c r="H598" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I598" s="1" t="s">
         <v>13</v>
@@ -17511,7 +17511,7 @@
         <v>74</v>
       </c>
       <c r="H599" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I599" s="1" t="s">
         <v>13</v>
@@ -17540,7 +17540,7 @@
         <v>75</v>
       </c>
       <c r="H600" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I600" s="1" t="s">
         <v>13</v>
@@ -17569,7 +17569,7 @@
         <v>67</v>
       </c>
       <c r="H601" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I601" s="1" t="s">
         <v>10</v>
@@ -17598,7 +17598,7 @@
         <v>67</v>
       </c>
       <c r="H602" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I602" s="1" t="s">
         <v>13</v>
@@ -17627,7 +17627,7 @@
         <v>76</v>
       </c>
       <c r="H603" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I603" s="1" t="s">
         <v>13</v>
@@ -17656,7 +17656,7 @@
         <v>58</v>
       </c>
       <c r="H604" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I604" s="1" t="s">
         <v>13</v>
@@ -17685,7 +17685,7 @@
         <v>77</v>
       </c>
       <c r="H605" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I605" s="1" t="s">
         <v>13</v>
@@ -17714,7 +17714,7 @@
         <v>60</v>
       </c>
       <c r="H606" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I606" s="1" t="s">
         <v>13</v>
@@ -17746,7 +17746,7 @@
         <v>45</v>
       </c>
       <c r="H607" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I607" s="1" t="s">
         <v>13</v>
@@ -17775,7 +17775,7 @@
         <v>62</v>
       </c>
       <c r="H608" s="2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I608" s="1" t="s">
         <v>10</v>
@@ -17804,7 +17804,7 @@
         <v>68</v>
       </c>
       <c r="H609" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I609" s="1" t="s">
         <v>13</v>
@@ -17833,7 +17833,7 @@
         <v>66</v>
       </c>
       <c r="H610" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I610" s="1" t="s">
         <v>13</v>
@@ -17862,7 +17862,7 @@
         <v>69</v>
       </c>
       <c r="H611" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I611" s="1" t="s">
         <v>10</v>
@@ -17891,7 +17891,7 @@
         <v>64</v>
       </c>
       <c r="H612" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I612" s="1" t="s">
         <v>13</v>
@@ -17920,7 +17920,7 @@
         <v>40</v>
       </c>
       <c r="H613" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I613" s="1" t="s">
         <v>10</v>
@@ -17949,7 +17949,7 @@
         <v>70</v>
       </c>
       <c r="H614" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I614" s="1" t="s">
         <v>10</v>
@@ -17978,7 +17978,7 @@
         <v>41</v>
       </c>
       <c r="H615" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I615" s="1" t="s">
         <v>13</v>
@@ -18007,7 +18007,7 @@
         <v>43</v>
       </c>
       <c r="H616" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I616" s="1" t="s">
         <v>13</v>
@@ -18039,7 +18039,7 @@
         <v>45</v>
       </c>
       <c r="H617" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I617" s="1" t="s">
         <v>13</v>
@@ -18071,7 +18071,7 @@
         <v>45</v>
       </c>
       <c r="H618" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I618" s="1" t="s">
         <v>13</v>
@@ -18100,7 +18100,7 @@
         <v>48</v>
       </c>
       <c r="H619" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I619" s="1" t="s">
         <v>10</v>
@@ -18129,7 +18129,7 @@
         <v>49</v>
       </c>
       <c r="H620" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I620" s="1" t="s">
         <v>13</v>
@@ -18158,7 +18158,7 @@
         <v>50</v>
       </c>
       <c r="H621" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I621" s="1" t="s">
         <v>10</v>
@@ -18187,7 +18187,7 @@
         <v>52</v>
       </c>
       <c r="H622" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I622" s="1" t="s">
         <v>13</v>
@@ -18216,7 +18216,7 @@
         <v>71</v>
       </c>
       <c r="H623" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I623" s="1" t="s">
         <v>13</v>
@@ -18245,7 +18245,7 @@
         <v>72</v>
       </c>
       <c r="H624" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I624" s="1" t="s">
         <v>13</v>
@@ -18277,7 +18277,7 @@
         <v>45</v>
       </c>
       <c r="H625" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I625" s="1" t="s">
         <v>13</v>
@@ -18306,7 +18306,7 @@
         <v>73</v>
       </c>
       <c r="H626" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I626" s="1" t="s">
         <v>13</v>
@@ -18335,7 +18335,7 @@
         <v>74</v>
       </c>
       <c r="H627" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I627" s="1" t="s">
         <v>13</v>
@@ -18364,7 +18364,7 @@
         <v>75</v>
       </c>
       <c r="H628" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I628" s="1" t="s">
         <v>13</v>
@@ -18393,7 +18393,7 @@
         <v>67</v>
       </c>
       <c r="H629" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I629" s="1" t="s">
         <v>10</v>
@@ -18422,7 +18422,7 @@
         <v>67</v>
       </c>
       <c r="H630" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I630" s="1" t="s">
         <v>12</v>
@@ -18446,7 +18446,7 @@
       <c r="J631" s="2"/>
       <c r="K631" s="1"/>
       <c r="M631" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="632" spans="4:13" x14ac:dyDescent="0.3">
@@ -18460,7 +18460,7 @@
         <v>76</v>
       </c>
       <c r="H632" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I632" s="1" t="s">
         <v>13</v>
@@ -18489,7 +18489,7 @@
         <v>58</v>
       </c>
       <c r="H633" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I633" s="1" t="s">
         <v>13</v>
@@ -18518,7 +18518,7 @@
         <v>77</v>
       </c>
       <c r="H634" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I634" s="1" t="s">
         <v>13</v>
@@ -18547,7 +18547,7 @@
         <v>60</v>
       </c>
       <c r="H635" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I635" s="1" t="s">
         <v>13</v>
@@ -18579,7 +18579,7 @@
         <v>45</v>
       </c>
       <c r="H636" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I636" s="1" t="s">
         <v>13</v>
@@ -18608,7 +18608,7 @@
         <v>62</v>
       </c>
       <c r="H637" s="2" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="I637" s="1" t="s">
         <v>13</v>
@@ -18637,7 +18637,7 @@
         <v>68</v>
       </c>
       <c r="H638" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I638" s="1" t="s">
         <v>13</v>
@@ -18666,7 +18666,7 @@
         <v>66</v>
       </c>
       <c r="H639" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I639" s="1" t="s">
         <v>13</v>
@@ -18695,7 +18695,7 @@
         <v>69</v>
       </c>
       <c r="H640" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I640" s="1" t="s">
         <v>10</v>
@@ -18724,7 +18724,7 @@
         <v>64</v>
       </c>
       <c r="H641" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I641" s="1" t="s">
         <v>10</v>
@@ -18753,7 +18753,7 @@
         <v>40</v>
       </c>
       <c r="H642" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I642" s="1" t="s">
         <v>10</v>
@@ -18782,7 +18782,7 @@
         <v>70</v>
       </c>
       <c r="H643" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I643" s="1" t="s">
         <v>10</v>
@@ -18811,7 +18811,7 @@
         <v>41</v>
       </c>
       <c r="H644" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I644" s="1" t="s">
         <v>13</v>
@@ -18840,7 +18840,7 @@
         <v>43</v>
       </c>
       <c r="H645" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I645" s="1" t="s">
         <v>13</v>
@@ -18872,7 +18872,7 @@
         <v>45</v>
       </c>
       <c r="H646" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I646" s="1" t="s">
         <v>13</v>
@@ -18904,7 +18904,7 @@
         <v>45</v>
       </c>
       <c r="H647" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I647" s="1" t="s">
         <v>13</v>
@@ -18933,7 +18933,7 @@
         <v>48</v>
       </c>
       <c r="H648" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I648" s="1" t="s">
         <v>13</v>
@@ -18962,7 +18962,7 @@
         <v>49</v>
       </c>
       <c r="H649" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I649" s="1" t="s">
         <v>10</v>
@@ -18991,7 +18991,7 @@
         <v>50</v>
       </c>
       <c r="H650" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I650" s="1" t="s">
         <v>10</v>
@@ -19020,7 +19020,7 @@
         <v>52</v>
       </c>
       <c r="H651" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I651" s="1" t="s">
         <v>13</v>
@@ -19049,7 +19049,7 @@
         <v>71</v>
       </c>
       <c r="H652" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I652" s="1" t="s">
         <v>13</v>
@@ -19078,7 +19078,7 @@
         <v>72</v>
       </c>
       <c r="H653" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I653" s="1" t="s">
         <v>13</v>
@@ -19110,7 +19110,7 @@
         <v>45</v>
       </c>
       <c r="H654" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I654" s="1" t="s">
         <v>13</v>
@@ -19139,7 +19139,7 @@
         <v>73</v>
       </c>
       <c r="H655" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I655" s="1" t="s">
         <v>13</v>
@@ -19168,7 +19168,7 @@
         <v>74</v>
       </c>
       <c r="H656" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I656" s="1" t="s">
         <v>13</v>
@@ -19197,7 +19197,7 @@
         <v>75</v>
       </c>
       <c r="H657" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I657" s="1" t="s">
         <v>13</v>
@@ -19226,7 +19226,7 @@
         <v>67</v>
       </c>
       <c r="H658" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I658" s="1" t="s">
         <v>12</v>
@@ -19250,7 +19250,7 @@
       <c r="J659" s="2"/>
       <c r="K659" s="1"/>
       <c r="M659" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="660" spans="4:13" x14ac:dyDescent="0.3">
@@ -19264,7 +19264,7 @@
         <v>67</v>
       </c>
       <c r="H660" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I660" s="1" t="s">
         <v>10</v>
@@ -19293,7 +19293,7 @@
         <v>76</v>
       </c>
       <c r="H661" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I661" s="1" t="s">
         <v>14</v>
@@ -19317,7 +19317,7 @@
       <c r="J662" s="2"/>
       <c r="K662" s="1"/>
       <c r="M662" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="663" spans="4:13" x14ac:dyDescent="0.3">
@@ -19331,7 +19331,7 @@
         <v>58</v>
       </c>
       <c r="H663" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I663" s="1" t="s">
         <v>13</v>
@@ -19360,7 +19360,7 @@
         <v>77</v>
       </c>
       <c r="H664" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I664" s="1" t="s">
         <v>13</v>
@@ -19389,7 +19389,7 @@
         <v>60</v>
       </c>
       <c r="H665" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I665" s="1" t="s">
         <v>13</v>
@@ -19421,7 +19421,7 @@
         <v>45</v>
       </c>
       <c r="H666" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I666" s="1" t="s">
         <v>13</v>
@@ -19450,7 +19450,7 @@
         <v>62</v>
       </c>
       <c r="H667" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I667" s="1" t="s">
         <v>13</v>
@@ -19479,7 +19479,7 @@
         <v>68</v>
       </c>
       <c r="H668" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I668" s="1" t="s">
         <v>13</v>
@@ -19508,7 +19508,7 @@
         <v>66</v>
       </c>
       <c r="H669" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I669" s="1" t="s">
         <v>13</v>
@@ -19537,7 +19537,7 @@
         <v>69</v>
       </c>
       <c r="H670" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I670" s="1" t="s">
         <v>10</v>
@@ -19566,7 +19566,7 @@
         <v>64</v>
       </c>
       <c r="H671" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I671" s="1" t="s">
         <v>10</v>
@@ -19595,7 +19595,7 @@
         <v>40</v>
       </c>
       <c r="H672" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I672" s="1" t="s">
         <v>10</v>
@@ -19624,7 +19624,7 @@
         <v>70</v>
       </c>
       <c r="H673" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I673" s="1" t="s">
         <v>12</v>
@@ -19648,7 +19648,7 @@
       <c r="J674" s="2"/>
       <c r="K674" s="1"/>
       <c r="M674" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="675" spans="4:13" x14ac:dyDescent="0.3">
@@ -19662,7 +19662,7 @@
         <v>41</v>
       </c>
       <c r="H675" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I675" s="1" t="s">
         <v>13</v>
@@ -19691,7 +19691,7 @@
         <v>43</v>
       </c>
       <c r="H676" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I676" s="1" t="s">
         <v>13</v>
@@ -19723,7 +19723,7 @@
         <v>45</v>
       </c>
       <c r="H677" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I677" s="1" t="s">
         <v>13</v>
@@ -19755,7 +19755,7 @@
         <v>45</v>
       </c>
       <c r="H678" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I678" s="1" t="s">
         <v>14</v>
@@ -19779,7 +19779,7 @@
       <c r="J679" s="2"/>
       <c r="K679" s="1"/>
       <c r="M679" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="680" spans="4:13" x14ac:dyDescent="0.3">
@@ -19793,7 +19793,7 @@
         <v>48</v>
       </c>
       <c r="H680" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I680" s="1" t="s">
         <v>13</v>
@@ -19822,7 +19822,7 @@
         <v>49</v>
       </c>
       <c r="H681" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I681" s="1" t="s">
         <v>10</v>
@@ -19851,7 +19851,7 @@
         <v>50</v>
       </c>
       <c r="H682" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I682" s="1" t="s">
         <v>10</v>
@@ -19880,7 +19880,7 @@
         <v>52</v>
       </c>
       <c r="H683" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I683" s="1" t="s">
         <v>13</v>
@@ -19909,7 +19909,7 @@
         <v>71</v>
       </c>
       <c r="H684" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I684" s="1" t="s">
         <v>13</v>
@@ -19938,7 +19938,7 @@
         <v>72</v>
       </c>
       <c r="H685" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I685" s="1" t="s">
         <v>13</v>
@@ -19970,7 +19970,7 @@
         <v>45</v>
       </c>
       <c r="H686" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I686" s="1" t="s">
         <v>13</v>
@@ -19999,7 +19999,7 @@
         <v>73</v>
       </c>
       <c r="H687" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I687" s="1" t="s">
         <v>13</v>
@@ -20028,7 +20028,7 @@
         <v>74</v>
       </c>
       <c r="H688" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I688" s="1" t="s">
         <v>13</v>
@@ -20057,7 +20057,7 @@
         <v>75</v>
       </c>
       <c r="H689" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I689" s="1" t="s">
         <v>13</v>
@@ -20086,7 +20086,7 @@
         <v>67</v>
       </c>
       <c r="H690" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I690" s="1" t="s">
         <v>10</v>
@@ -20115,7 +20115,7 @@
         <v>67</v>
       </c>
       <c r="H691" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I691" s="1" t="s">
         <v>10</v>
@@ -20144,7 +20144,7 @@
         <v>76</v>
       </c>
       <c r="H692" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I692" s="1" t="s">
         <v>13</v>
@@ -20173,7 +20173,7 @@
         <v>58</v>
       </c>
       <c r="H693" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I693" s="1" t="s">
         <v>13</v>
@@ -20202,7 +20202,7 @@
         <v>77</v>
       </c>
       <c r="H694" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I694" s="1" t="s">
         <v>13</v>
@@ -20231,7 +20231,7 @@
         <v>60</v>
       </c>
       <c r="H695" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I695" s="1" t="s">
         <v>13</v>
@@ -20263,7 +20263,7 @@
         <v>45</v>
       </c>
       <c r="H696" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I696" s="1" t="s">
         <v>13</v>
@@ -20292,7 +20292,7 @@
         <v>62</v>
       </c>
       <c r="H697" s="2" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="I697" s="1" t="s">
         <v>13</v>
@@ -20321,7 +20321,7 @@
         <v>68</v>
       </c>
       <c r="H698" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I698" s="1" t="s">
         <v>13</v>
@@ -20350,7 +20350,7 @@
         <v>66</v>
       </c>
       <c r="H699" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I699" s="1" t="s">
         <v>13</v>
@@ -20379,7 +20379,7 @@
         <v>69</v>
       </c>
       <c r="H700" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I700" s="1" t="s">
         <v>10</v>
@@ -20408,7 +20408,7 @@
         <v>64</v>
       </c>
       <c r="H701" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I701" s="1" t="s">
         <v>13</v>
@@ -20437,7 +20437,7 @@
         <v>40</v>
       </c>
       <c r="H702" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I702" s="1" t="s">
         <v>10</v>
@@ -20466,7 +20466,7 @@
         <v>70</v>
       </c>
       <c r="H703" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I703" s="1" t="s">
         <v>10</v>
@@ -20495,7 +20495,7 @@
         <v>41</v>
       </c>
       <c r="H704" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I704" s="1" t="s">
         <v>13</v>
@@ -20524,7 +20524,7 @@
         <v>43</v>
       </c>
       <c r="H705" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I705" s="1" t="s">
         <v>13</v>
@@ -20556,7 +20556,7 @@
         <v>45</v>
       </c>
       <c r="H706" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I706" s="1" t="s">
         <v>13</v>
@@ -20588,7 +20588,7 @@
         <v>45</v>
       </c>
       <c r="H707" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I707" s="1" t="s">
         <v>13</v>
@@ -20617,7 +20617,7 @@
         <v>48</v>
       </c>
       <c r="H708" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I708" s="1" t="s">
         <v>13</v>
@@ -20646,7 +20646,7 @@
         <v>49</v>
       </c>
       <c r="H709" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I709" s="1" t="s">
         <v>13</v>
@@ -20675,7 +20675,7 @@
         <v>50</v>
       </c>
       <c r="H710" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I710" s="1" t="s">
         <v>12</v>
@@ -20699,7 +20699,7 @@
       <c r="J711" s="2"/>
       <c r="K711" s="1"/>
       <c r="M711" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="712" spans="4:13" x14ac:dyDescent="0.3">
@@ -20713,7 +20713,7 @@
         <v>52</v>
       </c>
       <c r="H712" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I712" s="1" t="s">
         <v>13</v>
@@ -20742,7 +20742,7 @@
         <v>71</v>
       </c>
       <c r="H713" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I713" s="1" t="s">
         <v>13</v>
@@ -20771,7 +20771,7 @@
         <v>72</v>
       </c>
       <c r="H714" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I714" s="1" t="s">
         <v>13</v>
@@ -20803,7 +20803,7 @@
         <v>45</v>
       </c>
       <c r="H715" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I715" s="1" t="s">
         <v>13</v>
@@ -20832,7 +20832,7 @@
         <v>73</v>
       </c>
       <c r="H716" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I716" s="1" t="s">
         <v>13</v>
@@ -20861,7 +20861,7 @@
         <v>74</v>
       </c>
       <c r="H717" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I717" s="1" t="s">
         <v>13</v>
@@ -20890,7 +20890,7 @@
         <v>75</v>
       </c>
       <c r="H718" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I718" s="1" t="s">
         <v>13</v>
@@ -20919,7 +20919,7 @@
         <v>67</v>
       </c>
       <c r="H719" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I719" s="1" t="s">
         <v>13</v>
@@ -20948,7 +20948,7 @@
         <v>67</v>
       </c>
       <c r="H720" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I720" s="1" t="s">
         <v>10</v>
@@ -20977,7 +20977,7 @@
         <v>76</v>
       </c>
       <c r="H721" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I721" s="1" t="s">
         <v>13</v>
@@ -21006,7 +21006,7 @@
         <v>58</v>
       </c>
       <c r="H722" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I722" s="1" t="s">
         <v>13</v>
@@ -21035,7 +21035,7 @@
         <v>77</v>
       </c>
       <c r="H723" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I723" s="1" t="s">
         <v>13</v>
@@ -21064,7 +21064,7 @@
         <v>60</v>
       </c>
       <c r="H724" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I724" s="1" t="s">
         <v>13</v>
@@ -21096,7 +21096,7 @@
         <v>45</v>
       </c>
       <c r="H725" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I725" s="1" t="s">
         <v>13</v>
@@ -21125,7 +21125,7 @@
         <v>62</v>
       </c>
       <c r="H726" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="I726" s="1" t="s">
         <v>13</v>
@@ -21154,7 +21154,7 @@
         <v>68</v>
       </c>
       <c r="H727" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I727" s="1" t="s">
         <v>13</v>
@@ -21183,7 +21183,7 @@
         <v>66</v>
       </c>
       <c r="H728" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I728" s="1" t="s">
         <v>13</v>
@@ -21212,7 +21212,7 @@
         <v>69</v>
       </c>
       <c r="H729" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I729" s="1" t="s">
         <v>13</v>
@@ -21241,7 +21241,7 @@
         <v>64</v>
       </c>
       <c r="H730" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I730" s="1" t="s">
         <v>13</v>
@@ -21270,7 +21270,7 @@
         <v>40</v>
       </c>
       <c r="H731" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I731" s="1" t="s">
         <v>10</v>
@@ -21299,7 +21299,7 @@
         <v>70</v>
       </c>
       <c r="H732" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I732" s="1" t="s">
         <v>10</v>
@@ -21328,7 +21328,7 @@
         <v>41</v>
       </c>
       <c r="H733" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I733" s="1" t="s">
         <v>13</v>
@@ -21357,7 +21357,7 @@
         <v>43</v>
       </c>
       <c r="H734" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I734" s="1" t="s">
         <v>13</v>
@@ -21389,7 +21389,7 @@
         <v>45</v>
       </c>
       <c r="H735" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I735" s="1" t="s">
         <v>13</v>
@@ -21421,7 +21421,7 @@
         <v>45</v>
       </c>
       <c r="H736" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I736" s="1" t="s">
         <v>13</v>
@@ -21450,7 +21450,7 @@
         <v>48</v>
       </c>
       <c r="H737" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I737" s="1" t="s">
         <v>13</v>
@@ -21479,7 +21479,7 @@
         <v>49</v>
       </c>
       <c r="H738" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I738" s="1" t="s">
         <v>13</v>
@@ -21508,7 +21508,7 @@
         <v>50</v>
       </c>
       <c r="H739" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I739" s="1" t="s">
         <v>13</v>
@@ -21537,7 +21537,7 @@
         <v>52</v>
       </c>
       <c r="H740" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I740" s="1" t="s">
         <v>13</v>
@@ -21566,7 +21566,7 @@
         <v>71</v>
       </c>
       <c r="H741" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I741" s="1" t="s">
         <v>12</v>
@@ -21590,7 +21590,7 @@
       <c r="J742" s="2"/>
       <c r="K742" s="1"/>
       <c r="M742" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="743" spans="4:13" x14ac:dyDescent="0.3">
@@ -21604,7 +21604,7 @@
         <v>72</v>
       </c>
       <c r="H743" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I743" s="1" t="s">
         <v>13</v>
@@ -21636,7 +21636,7 @@
         <v>45</v>
       </c>
       <c r="H744" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I744" s="1" t="s">
         <v>13</v>
@@ -21665,7 +21665,7 @@
         <v>73</v>
       </c>
       <c r="H745" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I745" s="1" t="s">
         <v>13</v>
@@ -21694,7 +21694,7 @@
         <v>74</v>
       </c>
       <c r="H746" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I746" s="1" t="s">
         <v>13</v>
@@ -21723,7 +21723,7 @@
         <v>75</v>
       </c>
       <c r="H747" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I747" s="1" t="s">
         <v>13</v>
@@ -21752,7 +21752,7 @@
         <v>67</v>
       </c>
       <c r="H748" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I748" s="1" t="s">
         <v>13</v>
@@ -21781,7 +21781,7 @@
         <v>67</v>
       </c>
       <c r="H749" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I749" s="1" t="s">
         <v>13</v>
@@ -21810,7 +21810,7 @@
         <v>76</v>
       </c>
       <c r="H750" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I750" s="1" t="s">
         <v>13</v>
@@ -21839,7 +21839,7 @@
         <v>58</v>
       </c>
       <c r="H751" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I751" s="1" t="s">
         <v>13</v>
@@ -21868,7 +21868,7 @@
         <v>77</v>
       </c>
       <c r="H752" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I752" s="1" t="s">
         <v>13</v>
@@ -21897,7 +21897,7 @@
         <v>60</v>
       </c>
       <c r="H753" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I753" s="1" t="s">
         <v>13</v>
@@ -21929,7 +21929,7 @@
         <v>45</v>
       </c>
       <c r="H754" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I754" s="1" t="s">
         <v>13</v>
@@ -21958,7 +21958,7 @@
         <v>62</v>
       </c>
       <c r="H755" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="I755" s="1" t="s">
         <v>13</v>
@@ -25616,6 +25616,7 @@
     <row r="1367" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1367" s="2"/>
       <c r="I1367" s="1"/>
+      <c r="J1367" s="2"/>
       <c r="K1367" s="1"/>
     </row>
     <row r="1368" spans="8:11" x14ac:dyDescent="0.3">
@@ -28939,6 +28940,7 @@
     </row>
     <row r="1934" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1934" s="1"/>
+      <c r="J1934" s="2"/>
       <c r="K1934" s="1"/>
     </row>
     <row r="1935" spans="8:11" x14ac:dyDescent="0.3">
@@ -28949,14 +28951,17 @@
     <row r="1936" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1936" s="2"/>
       <c r="I1936" s="1"/>
+      <c r="K1936" s="1"/>
     </row>
     <row r="1937" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1937" s="2"/>
       <c r="I1937" s="1"/>
+      <c r="J1937" s="2"/>
       <c r="K1937" s="1"/>
     </row>
     <row r="1938" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1938" s="1"/>
+      <c r="J1938" s="2"/>
       <c r="K1938" s="1"/>
     </row>
     <row r="1939" spans="8:11" x14ac:dyDescent="0.3">
@@ -28982,6 +28987,7 @@
     <row r="1943" spans="8:11" x14ac:dyDescent="0.3">
       <c r="H1943" s="2"/>
       <c r="I1943" s="1"/>
+      <c r="J1943" s="2"/>
       <c r="K1943" s="1"/>
     </row>
     <row r="1944" spans="8:11" x14ac:dyDescent="0.3">
@@ -28991,9 +28997,11 @@
     </row>
     <row r="1945" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1945" s="1"/>
+      <c r="K1945" s="1"/>
     </row>
     <row r="1946" spans="8:11" x14ac:dyDescent="0.3">
       <c r="I1946" s="1"/>
+      <c r="J1946" s="2"/>
       <c r="K1946" s="1"/>
     </row>
     <row r="1947" spans="8:11" x14ac:dyDescent="0.3">
@@ -55931,6 +55939,7 @@
       <c r="K6920" s="1"/>
     </row>
     <row r="6921" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6921" s="2"/>
       <c r="K6921" s="1"/>
     </row>
     <row r="6922" spans="10:11" x14ac:dyDescent="0.3">
@@ -55938,6 +55947,7 @@
       <c r="K6922" s="1"/>
     </row>
     <row r="6923" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6923" s="2"/>
       <c r="K6923" s="1"/>
     </row>
     <row r="6924" spans="10:11" x14ac:dyDescent="0.3">
@@ -55945,6 +55955,7 @@
       <c r="K6924" s="1"/>
     </row>
     <row r="6925" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6925" s="2"/>
       <c r="K6925" s="1"/>
     </row>
     <row r="6926" spans="10:11" x14ac:dyDescent="0.3">
@@ -55960,6 +55971,7 @@
       <c r="K6928" s="1"/>
     </row>
     <row r="6929" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6929" s="2"/>
       <c r="K6929" s="1"/>
     </row>
     <row r="6930" spans="10:11" x14ac:dyDescent="0.3">
@@ -55969,6 +55981,7 @@
       <c r="K6931" s="1"/>
     </row>
     <row r="6932" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6932" s="2"/>
       <c r="K6932" s="1"/>
     </row>
     <row r="6933" spans="10:11" x14ac:dyDescent="0.3">
@@ -55976,9 +55989,15 @@
       <c r="K6933" s="1"/>
     </row>
     <row r="6934" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6934" s="2"/>
       <c r="K6934" s="1"/>
     </row>
+    <row r="6935" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6935" s="2"/>
+      <c r="K6935" s="1"/>
+    </row>
     <row r="6936" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6936" s="2"/>
       <c r="K6936" s="1"/>
     </row>
     <row r="6937" spans="10:11" x14ac:dyDescent="0.3">
@@ -55986,12 +56005,15 @@
       <c r="K6937" s="1"/>
     </row>
     <row r="6938" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6938" s="2"/>
       <c r="K6938" s="1"/>
     </row>
     <row r="6939" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6939" s="2"/>
       <c r="K6939" s="1"/>
     </row>
     <row r="6940" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6940" s="2"/>
       <c r="K6940" s="1"/>
     </row>
     <row r="6941" spans="10:11" x14ac:dyDescent="0.3">
@@ -55999,12 +56021,15 @@
       <c r="K6941" s="1"/>
     </row>
     <row r="6942" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6942" s="2"/>
       <c r="K6942" s="1"/>
     </row>
     <row r="6943" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6943" s="2"/>
       <c r="K6943" s="1"/>
     </row>
     <row r="6944" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6944" s="2"/>
       <c r="K6944" s="1"/>
     </row>
     <row r="6945" spans="10:11" x14ac:dyDescent="0.3">
@@ -56016,9 +56041,11 @@
       <c r="K6946" s="1"/>
     </row>
     <row r="6947" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6947" s="2"/>
       <c r="K6947" s="1"/>
     </row>
     <row r="6948" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6948" s="2"/>
       <c r="K6948" s="1"/>
     </row>
     <row r="6949" spans="10:11" x14ac:dyDescent="0.3">
@@ -56033,6 +56060,7 @@
       <c r="K6951" s="1"/>
     </row>
     <row r="6952" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6952" s="2"/>
       <c r="K6952" s="1"/>
     </row>
     <row r="6953" spans="10:11" x14ac:dyDescent="0.3">
@@ -56059,6 +56087,7 @@
       <c r="K6958" s="1"/>
     </row>
     <row r="6959" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6959" s="2"/>
       <c r="K6959" s="1"/>
     </row>
     <row r="6960" spans="10:11" x14ac:dyDescent="0.3">
@@ -56069,7 +56098,12 @@
       <c r="J6961" s="2"/>
       <c r="K6961" s="1"/>
     </row>
+    <row r="6962" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6962" s="2"/>
+      <c r="K6962" s="1"/>
+    </row>
     <row r="6963" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6963" s="2"/>
       <c r="K6963" s="1"/>
     </row>
     <row r="6964" spans="10:11" x14ac:dyDescent="0.3">
@@ -56077,6 +56111,7 @@
       <c r="K6964" s="1"/>
     </row>
     <row r="6965" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6965" s="2"/>
       <c r="K6965" s="1"/>
     </row>
     <row r="6966" spans="10:11" x14ac:dyDescent="0.3">
@@ -56088,6 +56123,7 @@
       <c r="K6967" s="1"/>
     </row>
     <row r="6968" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6968" s="2"/>
       <c r="K6968" s="1"/>
     </row>
     <row r="6969" spans="10:11" x14ac:dyDescent="0.3">
@@ -56095,6 +56131,7 @@
       <c r="K6969" s="1"/>
     </row>
     <row r="6970" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6970" s="2"/>
       <c r="K6970" s="1"/>
     </row>
     <row r="6971" spans="10:11" x14ac:dyDescent="0.3">
@@ -56109,13 +56146,19 @@
       <c r="K6973" s="1"/>
     </row>
     <row r="6974" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6974" s="2"/>
       <c r="K6974" s="1"/>
     </row>
     <row r="6975" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J6975" s="2"/>
       <c r="K6975" s="1"/>
     </row>
+    <row r="6976" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6976" s="2"/>
+      <c r="K6976" s="1"/>
+    </row>
     <row r="6977" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6977" s="2"/>
       <c r="K6977" s="1"/>
     </row>
     <row r="6978" spans="10:11" x14ac:dyDescent="0.3">
@@ -56126,15 +56169,18 @@
       <c r="K6979" s="1"/>
     </row>
     <row r="6980" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6980" s="2"/>
       <c r="K6980" s="1"/>
     </row>
     <row r="6981" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6981" s="2"/>
       <c r="K6981" s="1"/>
     </row>
     <row r="6982" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K6982" s="1"/>
     </row>
     <row r="6983" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6983" s="2"/>
       <c r="K6983" s="1"/>
     </row>
     <row r="6984" spans="10:11" x14ac:dyDescent="0.3">
@@ -56150,6 +56196,7 @@
       <c r="K6986" s="1"/>
     </row>
     <row r="6987" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6987" s="2"/>
       <c r="K6987" s="1"/>
     </row>
     <row r="6988" spans="10:11" x14ac:dyDescent="0.3">
@@ -56168,6 +56215,7 @@
       <c r="K6991" s="1"/>
     </row>
     <row r="6992" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6992" s="2"/>
       <c r="K6992" s="1"/>
     </row>
     <row r="6993" spans="10:11" x14ac:dyDescent="0.3">
@@ -56179,6 +56227,7 @@
       <c r="K6994" s="1"/>
     </row>
     <row r="6995" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J6995" s="2"/>
       <c r="K6995" s="1"/>
     </row>
     <row r="6996" spans="10:11" x14ac:dyDescent="0.3">
@@ -56196,18 +56245,23 @@
       <c r="K6999" s="1"/>
     </row>
     <row r="7000" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7000" s="2"/>
       <c r="K7000" s="1"/>
     </row>
     <row r="7001" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7001" s="2"/>
       <c r="K7001" s="1"/>
     </row>
     <row r="7002" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7002" s="2"/>
       <c r="K7002" s="1"/>
     </row>
     <row r="7003" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7003" s="2"/>
       <c r="K7003" s="1"/>
     </row>
     <row r="7004" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7004" s="2"/>
       <c r="K7004" s="1"/>
     </row>
     <row r="7005" spans="10:11" x14ac:dyDescent="0.3">
@@ -56236,6 +56290,7 @@
       <c r="K7012" s="1"/>
     </row>
     <row r="7014" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7014" s="2"/>
       <c r="K7014" s="1"/>
     </row>
     <row r="7015" spans="10:11" x14ac:dyDescent="0.3">
@@ -56243,9 +56298,11 @@
       <c r="K7015" s="1"/>
     </row>
     <row r="7016" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7016" s="2"/>
       <c r="K7016" s="1"/>
     </row>
     <row r="7017" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7017" s="2"/>
       <c r="K7017" s="1"/>
     </row>
     <row r="7018" spans="10:11" x14ac:dyDescent="0.3">
@@ -56268,12 +56325,15 @@
       <c r="K7022" s="1"/>
     </row>
     <row r="7023" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7023" s="2"/>
       <c r="K7023" s="1"/>
     </row>
     <row r="7024" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7024" s="2"/>
       <c r="K7024" s="1"/>
     </row>
     <row r="7025" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7025" s="2"/>
       <c r="K7025" s="1"/>
     </row>
     <row r="7026" spans="10:11" x14ac:dyDescent="0.3">
@@ -56288,9 +56348,11 @@
       <c r="K7028" s="1"/>
     </row>
     <row r="7030" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7030" s="2"/>
       <c r="K7030" s="1"/>
     </row>
     <row r="7031" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7031" s="2"/>
       <c r="K7031" s="1"/>
     </row>
     <row r="7032" spans="10:11" x14ac:dyDescent="0.3">
@@ -56306,12 +56368,14 @@
       <c r="K7034" s="1"/>
     </row>
     <row r="7035" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7035" s="2"/>
       <c r="K7035" s="1"/>
     </row>
     <row r="7036" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7036" s="1"/>
     </row>
     <row r="7037" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7037" s="2"/>
       <c r="K7037" s="1"/>
     </row>
     <row r="7038" spans="10:11" x14ac:dyDescent="0.3">
@@ -56332,6 +56396,7 @@
       <c r="K7042" s="1"/>
     </row>
     <row r="7043" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7043" s="2"/>
       <c r="K7043" s="1"/>
     </row>
     <row r="7044" spans="10:11" x14ac:dyDescent="0.3">
@@ -56343,9 +56408,11 @@
       <c r="K7045" s="1"/>
     </row>
     <row r="7046" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7046" s="2"/>
       <c r="K7046" s="1"/>
     </row>
     <row r="7047" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7047" s="2"/>
       <c r="K7047" s="1"/>
     </row>
     <row r="7048" spans="10:11" x14ac:dyDescent="0.3">
@@ -56357,6 +56424,7 @@
       <c r="K7049" s="1"/>
     </row>
     <row r="7050" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7050" s="2"/>
       <c r="K7050" s="1"/>
     </row>
     <row r="7051" spans="10:11" x14ac:dyDescent="0.3">
@@ -56396,9 +56464,11 @@
       <c r="K7059" s="1"/>
     </row>
     <row r="7060" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7060" s="2"/>
       <c r="K7060" s="1"/>
     </row>
     <row r="7061" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7061" s="2"/>
       <c r="K7061" s="1"/>
     </row>
     <row r="7062" spans="10:11" x14ac:dyDescent="0.3">
@@ -56406,9 +56476,11 @@
       <c r="K7062" s="1"/>
     </row>
     <row r="7063" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7063" s="2"/>
       <c r="K7063" s="1"/>
     </row>
     <row r="7064" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7064" s="2"/>
       <c r="K7064" s="1"/>
     </row>
     <row r="7065" spans="10:11" x14ac:dyDescent="0.3">
@@ -56419,6 +56491,7 @@
       <c r="K7066" s="1"/>
     </row>
     <row r="7067" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7067" s="2"/>
       <c r="K7067" s="1"/>
     </row>
     <row r="7068" spans="10:11" x14ac:dyDescent="0.3">
@@ -56426,18 +56499,26 @@
       <c r="K7068" s="1"/>
     </row>
     <row r="7069" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7069" s="2"/>
       <c r="K7069" s="1"/>
     </row>
+    <row r="7070" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7070" s="2"/>
+      <c r="K7070" s="1"/>
+    </row>
     <row r="7071" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7071" s="2"/>
       <c r="K7071" s="1"/>
     </row>
     <row r="7072" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7072" s="2"/>
       <c r="K7072" s="1"/>
     </row>
     <row r="7073" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7073" s="1"/>
     </row>
     <row r="7074" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7074" s="2"/>
       <c r="K7074" s="1"/>
     </row>
     <row r="7075" spans="10:11" x14ac:dyDescent="0.3">
@@ -56445,6 +56526,7 @@
       <c r="K7075" s="1"/>
     </row>
     <row r="7076" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7076" s="2"/>
       <c r="K7076" s="1"/>
     </row>
     <row r="7077" spans="10:11" x14ac:dyDescent="0.3">
@@ -56455,6 +56537,7 @@
       <c r="K7078" s="1"/>
     </row>
     <row r="7079" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7079" s="2"/>
       <c r="K7079" s="1"/>
     </row>
     <row r="7080" spans="10:11" x14ac:dyDescent="0.3">
@@ -56481,15 +56564,19 @@
       <c r="K7085" s="1"/>
     </row>
     <row r="7086" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7086" s="2"/>
       <c r="K7086" s="1"/>
     </row>
     <row r="7087" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7087" s="2"/>
       <c r="K7087" s="1"/>
     </row>
     <row r="7088" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7088" s="2"/>
       <c r="K7088" s="1"/>
     </row>
     <row r="7089" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7089" s="2"/>
       <c r="K7089" s="1"/>
     </row>
     <row r="7090" spans="10:11" x14ac:dyDescent="0.3">
@@ -56511,6 +56598,7 @@
       <c r="K7094" s="1"/>
     </row>
     <row r="7095" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7095" s="2"/>
       <c r="K7095" s="1"/>
     </row>
     <row r="7096" spans="10:11" x14ac:dyDescent="0.3">
@@ -56518,9 +56606,11 @@
       <c r="K7096" s="1"/>
     </row>
     <row r="7097" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7097" s="2"/>
       <c r="K7097" s="1"/>
     </row>
     <row r="7098" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7098" s="2"/>
       <c r="K7098" s="1"/>
     </row>
     <row r="7099" spans="10:11" x14ac:dyDescent="0.3">
@@ -56528,6 +56618,7 @@
       <c r="K7099" s="1"/>
     </row>
     <row r="7100" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7100" s="2"/>
       <c r="K7100" s="1"/>
     </row>
     <row r="7101" spans="10:11" x14ac:dyDescent="0.3">
@@ -56539,6 +56630,7 @@
       <c r="K7102" s="1"/>
     </row>
     <row r="7103" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7103" s="2"/>
       <c r="K7103" s="1"/>
     </row>
     <row r="7104" spans="10:11" x14ac:dyDescent="0.3">
@@ -56553,6 +56645,10 @@
       <c r="J7106" s="2"/>
       <c r="K7106" s="1"/>
     </row>
+    <row r="7107" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7107" s="2"/>
+      <c r="K7107" s="1"/>
+    </row>
     <row r="7108" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7108" s="2"/>
       <c r="K7108" s="1"/>
@@ -56562,6 +56658,7 @@
       <c r="K7109" s="1"/>
     </row>
     <row r="7110" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7110" s="2"/>
       <c r="K7110" s="1"/>
     </row>
     <row r="7111" spans="10:11" x14ac:dyDescent="0.3">
@@ -56573,6 +56670,7 @@
       <c r="K7112" s="1"/>
     </row>
     <row r="7113" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7113" s="2"/>
       <c r="K7113" s="1"/>
     </row>
     <row r="7114" spans="10:11" x14ac:dyDescent="0.3">
@@ -56583,10 +56681,15 @@
       <c r="J7115" s="2"/>
       <c r="K7115" s="1"/>
     </row>
+    <row r="7116" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7116" s="1"/>
+    </row>
     <row r="7117" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7117" s="2"/>
       <c r="K7117" s="1"/>
     </row>
     <row r="7118" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7118" s="2"/>
       <c r="K7118" s="1"/>
     </row>
     <row r="7119" spans="10:11" x14ac:dyDescent="0.3">
@@ -56594,6 +56697,7 @@
       <c r="K7119" s="1"/>
     </row>
     <row r="7120" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7120" s="2"/>
       <c r="K7120" s="1"/>
     </row>
     <row r="7121" spans="10:11" x14ac:dyDescent="0.3">
@@ -56608,6 +56712,7 @@
       <c r="K7123" s="1"/>
     </row>
     <row r="7124" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7124" s="2"/>
       <c r="K7124" s="1"/>
     </row>
     <row r="7125" spans="10:11" x14ac:dyDescent="0.3">
@@ -56630,6 +56735,7 @@
       <c r="K7129" s="1"/>
     </row>
     <row r="7130" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7130" s="2"/>
       <c r="K7130" s="1"/>
     </row>
     <row r="7131" spans="10:11" x14ac:dyDescent="0.3">
@@ -56649,25 +56755,37 @@
       <c r="K7134" s="1"/>
     </row>
     <row r="7135" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7135" s="2"/>
       <c r="K7135" s="1"/>
     </row>
     <row r="7136" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7136" s="2"/>
       <c r="K7136" s="1"/>
     </row>
     <row r="7137" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7137" s="2"/>
       <c r="K7137" s="1"/>
     </row>
     <row r="7138" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7138" s="2"/>
       <c r="K7138" s="1"/>
     </row>
+    <row r="7139" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7139" s="2"/>
+      <c r="K7139" s="1"/>
+    </row>
     <row r="7140" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7140" s="2"/>
       <c r="K7140" s="1"/>
     </row>
     <row r="7141" spans="10:11" x14ac:dyDescent="0.3">
       <c r="J7141" s="2"/>
       <c r="K7141" s="1"/>
     </row>
+    <row r="7142" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7142" s="2"/>
+      <c r="K7142" s="1"/>
+    </row>
     <row r="7143" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7143" s="1"/>
     </row>
@@ -56675,6 +56793,7 @@
       <c r="K7144" s="1"/>
     </row>
     <row r="7145" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7145" s="2"/>
       <c r="K7145" s="1"/>
     </row>
     <row r="7146" spans="10:11" x14ac:dyDescent="0.3">
@@ -56682,15 +56801,22 @@
       <c r="K7146" s="1"/>
     </row>
     <row r="7147" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7147" s="2"/>
       <c r="K7147" s="1"/>
     </row>
     <row r="7148" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7148" s="1"/>
     </row>
+    <row r="7149" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7149" s="2"/>
+      <c r="K7149" s="1"/>
+    </row>
     <row r="7150" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7150" s="2"/>
       <c r="K7150" s="1"/>
     </row>
     <row r="7151" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7151" s="2"/>
       <c r="K7151" s="1"/>
     </row>
     <row r="7152" spans="10:11" x14ac:dyDescent="0.3">
@@ -56704,6 +56830,7 @@
       <c r="K7154" s="1"/>
     </row>
     <row r="7155" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7155" s="2"/>
       <c r="K7155" s="1"/>
     </row>
     <row r="7156" spans="10:11" x14ac:dyDescent="0.3">
@@ -56722,9 +56849,11 @@
       <c r="K7159" s="1"/>
     </row>
     <row r="7160" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7160" s="2"/>
       <c r="K7160" s="1"/>
     </row>
     <row r="7161" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7161" s="2"/>
       <c r="K7161" s="1"/>
     </row>
     <row r="7162" spans="10:11" x14ac:dyDescent="0.3">
@@ -56732,9 +56861,11 @@
       <c r="K7162" s="1"/>
     </row>
     <row r="7163" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7163" s="2"/>
       <c r="K7163" s="1"/>
     </row>
     <row r="7164" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7164" s="2"/>
       <c r="K7164" s="1"/>
     </row>
     <row r="7165" spans="10:11" x14ac:dyDescent="0.3">
@@ -56742,6 +56873,7 @@
       <c r="K7165" s="1"/>
     </row>
     <row r="7166" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7166" s="2"/>
       <c r="K7166" s="1"/>
     </row>
     <row r="7167" spans="10:11" x14ac:dyDescent="0.3">
@@ -56758,10 +56890,14 @@
       <c r="K7170" s="1"/>
     </row>
     <row r="7171" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="J7171" s="2"/>
       <c r="K7171" s="1"/>
     </row>
     <row r="7172" spans="10:11" x14ac:dyDescent="0.3">
       <c r="K7172" s="1"/>
+    </row>
+    <row r="7173" spans="10:11" x14ac:dyDescent="0.3">
+      <c r="K7173" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
